--- a/database/event/5604/event_5604_evp_summary.xlsx
+++ b/database/event/5604/event_5604_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.4025</v>
+        <v>5.2866</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5449</v>
+        <v>1.5117</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7611</v>
+        <v>1.6623</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4025</v>
+        <v>5.2866</v>
       </c>
       <c r="F2" t="n">
-        <v>5.4025</v>
+        <v>5.2866</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6.168</v>
+        <v>5.9863</v>
       </c>
       <c r="I2" t="n">
         <v>6.4014</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1081</v>
+        <v>5.0141</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4607</v>
+        <v>1.4338</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6422</v>
+        <v>1.5537</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1081</v>
+        <v>5.0141</v>
       </c>
       <c r="F3" t="n">
-        <v>5.1081</v>
+        <v>5.0141</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7064</v>
+        <v>5.5591</v>
       </c>
       <c r="I3" t="n">
         <v>5.895</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8065</v>
+        <v>4.7082</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3745</v>
+        <v>1.3464</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5204</v>
+        <v>1.4318</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8065</v>
+        <v>4.7082</v>
       </c>
       <c r="F4" t="n">
-        <v>4.8065</v>
+        <v>4.7082</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2335</v>
+        <v>5.0793</v>
       </c>
       <c r="I4" t="n">
         <v>5.4316</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4982</v>
+        <v>4.4089</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2863</v>
+        <v>1.2608</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3958</v>
+        <v>1.3126</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4982</v>
+        <v>4.4089</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4982</v>
+        <v>4.4089</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7501</v>
+        <v>4.6101</v>
       </c>
       <c r="I5" t="n">
         <v>4.9298</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8104</v>
+        <v>3.6981</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0896</v>
+        <v>1.0575</v>
       </c>
       <c r="D6" t="n">
-        <v>1.118</v>
+        <v>1.0294</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8104</v>
+        <v>3.6981</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8104</v>
+        <v>3.6981</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8104</v>
+        <v>3.6981</v>
       </c>
       <c r="I6" t="n">
         <v>3.9546</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5076</v>
+        <v>3.4171</v>
       </c>
       <c r="C7" t="n">
-        <v>1.003</v>
+        <v>0.9771</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9956</v>
+        <v>0.9175</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5076</v>
+        <v>3.4171</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5076</v>
+        <v>3.4171</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5076</v>
+        <v>3.4171</v>
       </c>
       <c r="I7" t="n">
         <v>3.6235</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2301</v>
+        <v>3.1941</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9237</v>
+        <v>0.9134</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8835</v>
+        <v>0.8286</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2301</v>
+        <v>3.1941</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2301</v>
+        <v>3.1941</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2301</v>
+        <v>3.1941</v>
       </c>
       <c r="I8" t="n">
         <v>3.2754</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0852</v>
+        <v>3.028</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8822</v>
+        <v>0.8659</v>
       </c>
       <c r="D9" t="n">
-        <v>0.825</v>
+        <v>0.7624</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0852</v>
+        <v>3.028</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0852</v>
+        <v>3.028</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0852</v>
+        <v>3.028</v>
       </c>
       <c r="I9" t="n">
         <v>3.1576</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9323</v>
+        <v>2.8459</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8385</v>
+        <v>0.8138</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7632</v>
+        <v>0.6899</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9323</v>
+        <v>2.8459</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9323</v>
+        <v>2.8459</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9323</v>
+        <v>2.8459</v>
       </c>
       <c r="I10" t="n">
         <v>3.0433</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9101</v>
+        <v>2.8349</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8322000000000001</v>
+        <v>0.8107</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7543</v>
+        <v>0.6855</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9101</v>
+        <v>2.8349</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9101</v>
+        <v>2.8349</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9101</v>
+        <v>2.8349</v>
       </c>
       <c r="I11" t="n">
         <v>3.0062</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8297</v>
+        <v>2.7981</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8092</v>
+        <v>0.8001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7218</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8297</v>
+        <v>2.7981</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8297</v>
+        <v>2.7981</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8297</v>
+        <v>2.7981</v>
       </c>
       <c r="I12" t="n">
         <v>2.8694</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5915</v>
+        <v>2.5722</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7411</v>
+        <v>0.7355</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.5809</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5915</v>
+        <v>2.5722</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5915</v>
+        <v>2.5722</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5915</v>
+        <v>2.5722</v>
       </c>
       <c r="I13" t="n">
         <v>2.6157</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2055</v>
+        <v>2.1405</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6307</v>
+        <v>0.6121</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4696</v>
+        <v>0.4089</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2055</v>
+        <v>2.1405</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2055</v>
+        <v>2.1405</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2055</v>
+        <v>2.1405</v>
       </c>
       <c r="I14" t="n">
         <v>2.289</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5008</v>
+        <v>1.4566</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4292</v>
+        <v>0.4165</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1849</v>
+        <v>0.1364</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5008</v>
+        <v>1.4566</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5008</v>
+        <v>1.4566</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5008</v>
+        <v>1.4566</v>
       </c>
       <c r="I15" t="n">
         <v>1.5576</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4537</v>
+        <v>1.4268</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4157</v>
+        <v>0.408</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1659</v>
+        <v>0.1245</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4537</v>
+        <v>1.4268</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4537</v>
+        <v>1.4268</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4537</v>
+        <v>1.4268</v>
       </c>
       <c r="I16" t="n">
         <v>1.4879</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.349</v>
+        <v>1.3142</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3858</v>
+        <v>0.3758</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1236</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.349</v>
+        <v>1.3142</v>
       </c>
       <c r="F17" t="n">
-        <v>1.349</v>
+        <v>1.3142</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.349</v>
+        <v>1.3142</v>
       </c>
       <c r="I17" t="n">
         <v>1.3936</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3132</v>
+        <v>1.3035</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3755</v>
+        <v>0.3727</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1091</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3132</v>
+        <v>1.3035</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3132</v>
+        <v>1.3035</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3132</v>
+        <v>1.3035</v>
       </c>
       <c r="I18" t="n">
         <v>1.3255</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2155</v>
+        <v>1.2065</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3476</v>
+        <v>0.345</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0697</v>
+        <v>0.0368</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2155</v>
+        <v>1.2065</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2155</v>
+        <v>1.2065</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2155</v>
+        <v>1.2065</v>
       </c>
       <c r="I19" t="n">
         <v>1.2269</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0902</v>
+        <v>1.07</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3118</v>
+        <v>0.306</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0191</v>
+        <v>-0.0176</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0902</v>
+        <v>1.07</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0902</v>
+        <v>1.07</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0902</v>
+        <v>1.07</v>
       </c>
       <c r="I20" t="n">
         <v>1.1158</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9379</v>
+        <v>0.9102</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2682</v>
+        <v>0.2603</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0425</v>
+        <v>-0.0813</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9379</v>
+        <v>0.9102</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9379</v>
+        <v>0.9102</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9379</v>
+        <v>0.9102</v>
       </c>
       <c r="I21" t="n">
         <v>0.9734</v>
@@ -1422,7 +1422,7 @@
         <v>0.2365</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0872</v>
+        <v>-0.1144</v>
       </c>
       <c r="E22" t="n">
         <v>0.8270999999999999</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.667</v>
+        <v>0.6596</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1907</v>
+        <v>0.1886</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1519</v>
+        <v>-0.1811</v>
       </c>
       <c r="E23" t="n">
-        <v>0.667</v>
+        <v>0.6596</v>
       </c>
       <c r="F23" t="n">
-        <v>0.667</v>
+        <v>0.6596</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.667</v>
+        <v>0.6596</v>
       </c>
       <c r="I23" t="n">
         <v>0.6764</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6485</v>
+        <v>0.6437</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1854</v>
+        <v>0.1841</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1594</v>
+        <v>-0.1875</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6485</v>
+        <v>0.6437</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6485</v>
+        <v>0.6437</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6485</v>
+        <v>0.6437</v>
       </c>
       <c r="I24" t="n">
         <v>0.6546</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2093</v>
+        <v>0.2069</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0599</v>
+        <v>0.0592</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3368</v>
+        <v>-0.3615</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2093</v>
+        <v>0.2069</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2093</v>
+        <v>0.2069</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2093</v>
+        <v>0.2069</v>
       </c>
       <c r="I25" t="n">
         <v>0.2122</v>
@@ -1606,7 +1606,7 @@
         <v>0.0472</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3547</v>
+        <v>-0.3782</v>
       </c>
       <c r="E26" t="n">
         <v>0.165</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1599</v>
+        <v>0.1587</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0457</v>
+        <v>0.0454</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3568</v>
+        <v>-0.3807</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1599</v>
+        <v>0.1587</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1599</v>
+        <v>0.1587</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1599</v>
+        <v>0.1587</v>
       </c>
       <c r="I27" t="n">
         <v>0.1614</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4721</v>
+        <v>-0.4686</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.135</v>
+        <v>-0.134</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6121</v>
+        <v>-0.6306</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4721</v>
+        <v>-0.4686</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4721</v>
+        <v>-0.4686</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4721</v>
+        <v>-0.4686</v>
       </c>
       <c r="I28" t="n">
         <v>-0.4765</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1453</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6266</v>
+        <v>-0.6463</v>
       </c>
       <c r="E29" t="n">
         <v>-0.5081</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6706</v>
+        <v>-0.6656</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1918</v>
+        <v>-0.1903</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6923</v>
+        <v>-0.7091</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6706</v>
+        <v>-0.6656</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6706</v>
+        <v>-0.6656</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6706</v>
+        <v>-0.6656</v>
       </c>
       <c r="I30" t="n">
         <v>-0.6768999999999999</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7948</v>
+        <v>-0.7801</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2273</v>
+        <v>-0.2231</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.7547</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7948</v>
+        <v>-0.7801</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7948</v>
+        <v>-0.7801</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7948</v>
+        <v>-0.7801</v>
       </c>
       <c r="I31" t="n">
         <v>-0.8135</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7975</v>
+        <v>-0.7915</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2281</v>
+        <v>-0.2263</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7435</v>
+        <v>-0.7592</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7975</v>
+        <v>-0.7915</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7975</v>
+        <v>-0.7915</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7975</v>
+        <v>-0.7915</v>
       </c>
       <c r="I32" t="n">
         <v>-0.8048999999999999</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2438</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7658</v>
+        <v>-0.7836</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8527</v>
@@ -1974,7 +1974,7 @@
         <v>-0.293</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8353</v>
+        <v>-0.8522</v>
       </c>
       <c r="E34" t="n">
         <v>-1.0247</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.8569</v>
+        <v>-1.843</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.531</v>
+        <v>-0.527</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1715</v>
+        <v>-1.1782</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.8569</v>
+        <v>-1.843</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.8569</v>
+        <v>-1.843</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.8569</v>
+        <v>-1.843</v>
       </c>
       <c r="I35" t="n">
         <v>-1.8742</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.9955</v>
+        <v>-1.9367</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5706</v>
+        <v>-0.5538</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2275</v>
+        <v>-1.2155</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.9955</v>
+        <v>-1.9367</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.9955</v>
+        <v>-1.9367</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.9955</v>
+        <v>-1.9367</v>
       </c>
       <c r="I36" t="n">
         <v>-2.071</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2.0214</v>
+        <v>-1.9989</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.578</v>
+        <v>-0.5716</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.238</v>
+        <v>-1.2403</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.0214</v>
+        <v>-1.9989</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.0214</v>
+        <v>-1.9989</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.0214</v>
+        <v>-1.9989</v>
       </c>
       <c r="I37" t="n">
         <v>-2.0498</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.2097</v>
+        <v>-2.1446</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6319</v>
+        <v>-0.6133</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.314</v>
+        <v>-1.2983</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.2097</v>
+        <v>-2.1446</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.2097</v>
+        <v>-2.1446</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.2097</v>
+        <v>-2.1446</v>
       </c>
       <c r="I38" t="n">
         <v>-2.2933</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.4497</v>
+        <v>-2.4043</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.7005</v>
+        <v>-0.6875</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.411</v>
+        <v>-1.4018</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.4497</v>
+        <v>-2.4043</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.4497</v>
+        <v>-2.4043</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.4497</v>
+        <v>-2.4043</v>
       </c>
       <c r="I39" t="n">
         <v>-2.5072</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-3.0005</v>
+        <v>-2.9782</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.858</v>
+        <v>-0.8516</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6335</v>
+        <v>-1.6304</v>
       </c>
       <c r="E40" t="n">
-        <v>-3.0005</v>
+        <v>-2.9782</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.0005</v>
+        <v>-2.9782</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.0005</v>
+        <v>-2.9782</v>
       </c>
       <c r="I40" t="n">
         <v>-3.0285</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.3588</v>
+        <v>-5.2204</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.5324</v>
+        <v>-1.4928</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.5862</v>
+        <v>-2.5237</v>
       </c>
       <c r="E41" t="n">
-        <v>-5.3588</v>
+        <v>-5.2204</v>
       </c>
       <c r="F41" t="n">
-        <v>-5.3588</v>
+        <v>-5.2204</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-5.3588</v>
+        <v>-5.2204</v>
       </c>
       <c r="I41" t="n">
         <v>-5.5358</v>

--- a/database/event/5604/event_5604_evp_summary.xlsx
+++ b/database/event/5604/event_5604_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.2866</v>
+        <v>3.814</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5117</v>
+        <v>1.0906</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6623</v>
+        <v>1.0838</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2866</v>
+        <v>3.814</v>
       </c>
       <c r="F2" t="n">
-        <v>5.2866</v>
+        <v>3.814</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.9863</v>
+        <v>5.015</v>
       </c>
       <c r="I2" t="n">
-        <v>6.4014</v>
+        <v>6.9231</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6.4014</v>
+        <v>6.9231</v>
       </c>
       <c r="N2" t="n">
         <v>405</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0141</v>
+        <v>3.6413</v>
       </c>
       <c r="C3" t="n">
-        <v>1.4338</v>
+        <v>1.0413</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5537</v>
+        <v>1.0059</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0141</v>
+        <v>3.6413</v>
       </c>
       <c r="F3" t="n">
-        <v>5.0141</v>
+        <v>3.6413</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5591</v>
+        <v>4.6358</v>
       </c>
       <c r="I3" t="n">
-        <v>5.895</v>
+        <v>6.1468</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.895</v>
+        <v>6.1468</v>
       </c>
       <c r="N3" t="n">
         <v>347</v>
@@ -584,32 +584,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7082</v>
+        <v>3.3747</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3464</v>
+        <v>0.965</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4318</v>
+        <v>0.8855</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7082</v>
+        <v>3.3747</v>
       </c>
       <c r="F4" t="n">
-        <v>4.7082</v>
+        <v>3.3747</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>5.0793</v>
+        <v>4.0505</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4316</v>
+        <v>5.5916</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4316</v>
+        <v>5.5916</v>
       </c>
       <c r="N4" t="n">
         <v>257</v>
@@ -630,32 +630,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4089</v>
+        <v>3.3407</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2608</v>
+        <v>0.9553</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3126</v>
+        <v>0.8701</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4089</v>
+        <v>3.3407</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4089</v>
+        <v>3.3407</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6101</v>
+        <v>3.9758</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9298</v>
+        <v>5.4885</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9298</v>
+        <v>5.4885</v>
       </c>
       <c r="N5" t="n">
         <v>257</v>
@@ -676,231 +676,231 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6981</v>
+        <v>3.2637</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0575</v>
+        <v>0.9333</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0294</v>
+        <v>0.8354</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6981</v>
+        <v>3.2637</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6981</v>
+        <v>3.2637</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6981</v>
+        <v>3.8067</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9546</v>
+        <v>4.2959</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>405</v>
+        <v>187</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9546</v>
+        <v>4.2959</v>
       </c>
       <c r="N6" t="n">
-        <v>405</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4171</v>
+        <v>2.9982</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9771</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9175</v>
+        <v>0.7155</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4171</v>
+        <v>2.9982</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4171</v>
+        <v>2.9982</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4171</v>
+        <v>3.2239</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6235</v>
+        <v>3.6382</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>347</v>
+        <v>187</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6235</v>
+        <v>3.6382</v>
       </c>
       <c r="N7" t="n">
-        <v>347</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1941</v>
+        <v>2.9466</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9134</v>
+        <v>0.8426</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8286</v>
+        <v>0.6922</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1941</v>
+        <v>2.9466</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1941</v>
+        <v>2.9466</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1941</v>
+        <v>3.1105</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2754</v>
+        <v>4.2939</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>187</v>
+        <v>405</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2754</v>
+        <v>4.2939</v>
       </c>
       <c r="N8" t="n">
-        <v>187</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.028</v>
+        <v>2.9425</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8659</v>
+        <v>0.8414</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7624</v>
+        <v>0.6904</v>
       </c>
       <c r="E9" t="n">
-        <v>3.028</v>
+        <v>2.9425</v>
       </c>
       <c r="F9" t="n">
-        <v>3.028</v>
+        <v>2.9425</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.028</v>
+        <v>3.1016</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1576</v>
+        <v>4.1125</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>252</v>
+        <v>347</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1576</v>
+        <v>4.1125</v>
       </c>
       <c r="N9" t="n">
-        <v>252</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8459</v>
+        <v>2.9061</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8138</v>
+        <v>0.831</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6899</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8459</v>
+        <v>2.9061</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8459</v>
+        <v>2.9061</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8459</v>
+        <v>3.0215</v>
       </c>
       <c r="I10" t="n">
-        <v>3.0433</v>
+        <v>3.6961</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0433</v>
+        <v>3.6961</v>
       </c>
       <c r="N10" t="n">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8349</v>
+        <v>2.6938</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8107</v>
+        <v>0.7703</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6855</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8349</v>
+        <v>2.6938</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8349</v>
+        <v>2.6938</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8349</v>
+        <v>2.6938</v>
       </c>
       <c r="I11" t="n">
-        <v>3.0062</v>
+        <v>3.5718</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0062</v>
+        <v>3.5718</v>
       </c>
       <c r="N11" t="n">
         <v>347</v>
@@ -952,277 +952,277 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.7981</v>
+        <v>2.6716</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8001</v>
+        <v>0.764</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.5681</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7981</v>
+        <v>2.6716</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7981</v>
+        <v>2.6716</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7981</v>
+        <v>2.6716</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8694</v>
+        <v>2.8959</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8694</v>
+        <v>2.8959</v>
       </c>
       <c r="N12" t="n">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5722</v>
+        <v>2.5805</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7355</v>
+        <v>0.7379</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5809</v>
+        <v>0.527</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5722</v>
+        <v>2.5805</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5722</v>
+        <v>2.5805</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5722</v>
+        <v>2.5805</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6157</v>
+        <v>3.5623</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>178</v>
+        <v>405</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6157</v>
+        <v>3.5623</v>
       </c>
       <c r="N13" t="n">
-        <v>178</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1405</v>
+        <v>2.0473</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6121</v>
+        <v>0.5854</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4089</v>
+        <v>0.2862</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1405</v>
+        <v>2.0473</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1405</v>
+        <v>2.0473</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1405</v>
+        <v>2.0473</v>
       </c>
       <c r="I14" t="n">
-        <v>2.289</v>
+        <v>2.8262</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>405</v>
+        <v>257</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.289</v>
+        <v>2.8262</v>
       </c>
       <c r="N14" t="n">
-        <v>405</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4566</v>
+        <v>1.6117</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4165</v>
+        <v>0.4609</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1364</v>
+        <v>0.0896</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4566</v>
+        <v>1.6117</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4566</v>
+        <v>1.6117</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4566</v>
+        <v>1.6117</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5576</v>
+        <v>1.747</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>257</v>
+        <v>178</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5576</v>
+        <v>1.747</v>
       </c>
       <c r="N15" t="n">
-        <v>257</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4268</v>
+        <v>1.5998</v>
       </c>
       <c r="C16" t="n">
-        <v>0.408</v>
+        <v>0.4575</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1245</v>
+        <v>0.0842</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4268</v>
+        <v>1.5998</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4268</v>
+        <v>1.5998</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4268</v>
+        <v>1.5998</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4879</v>
+        <v>2.1212</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>252</v>
+        <v>347</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4879</v>
+        <v>2.1212</v>
       </c>
       <c r="N16" t="n">
-        <v>252</v>
+        <v>347</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3142</v>
+        <v>1.4809</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3758</v>
+        <v>0.4235</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0305</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3142</v>
+        <v>1.4809</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3142</v>
+        <v>1.4809</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3142</v>
+        <v>1.4809</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3936</v>
+        <v>2.0444</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>347</v>
+        <v>257</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3936</v>
+        <v>2.0444</v>
       </c>
       <c r="N17" t="n">
-        <v>347</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3035</v>
+        <v>1.4588</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3727</v>
+        <v>0.4172</v>
       </c>
       <c r="D18" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0206</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3035</v>
+        <v>1.4588</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3035</v>
+        <v>1.4588</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3035</v>
+        <v>1.4588</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3255</v>
+        <v>1.5813</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3255</v>
+        <v>1.5813</v>
       </c>
       <c r="N18" t="n">
         <v>160</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2065</v>
+        <v>1.4344</v>
       </c>
       <c r="C19" t="n">
-        <v>0.345</v>
+        <v>0.4102</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0368</v>
+        <v>0.0095</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2065</v>
+        <v>1.4344</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2065</v>
+        <v>1.4344</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2065</v>
+        <v>1.4344</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2269</v>
+        <v>1.9802</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>178</v>
+        <v>405</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2269</v>
+        <v>1.9802</v>
       </c>
       <c r="N19" t="n">
-        <v>178</v>
+        <v>405</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.07</v>
+        <v>1.417</v>
       </c>
       <c r="C20" t="n">
-        <v>0.306</v>
+        <v>0.4052</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0176</v>
+        <v>0.0017</v>
       </c>
       <c r="E20" t="n">
-        <v>1.07</v>
+        <v>1.417</v>
       </c>
       <c r="F20" t="n">
-        <v>1.07</v>
+        <v>1.417</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.07</v>
+        <v>1.417</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1158</v>
+        <v>1.7333</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1158</v>
+        <v>1.7333</v>
       </c>
       <c r="N20" t="n">
         <v>252</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9102</v>
+        <v>1.2958</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2603</v>
+        <v>0.3705</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0813</v>
+        <v>-0.053</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9102</v>
+        <v>1.2958</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9102</v>
+        <v>1.2958</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9102</v>
+        <v>1.2958</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9734</v>
+        <v>1.5851</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>405</v>
+        <v>252</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.9734</v>
+        <v>1.5851</v>
       </c>
       <c r="N21" t="n">
-        <v>405</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8270999999999999</v>
+        <v>1.148</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2365</v>
+        <v>0.3283</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1144</v>
+        <v>-0.1197</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8270999999999999</v>
+        <v>1.148</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8270999999999999</v>
+        <v>1.148</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8270999999999999</v>
+        <v>1.148</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8270999999999999</v>
+        <v>1.148</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8270999999999999</v>
+        <v>1.148</v>
       </c>
       <c r="N22" t="n">
         <v>124</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6596</v>
+        <v>0.9175</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1886</v>
+        <v>0.2624</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1811</v>
+        <v>-0.2238</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6596</v>
+        <v>0.9175</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6596</v>
+        <v>0.9175</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6596</v>
+        <v>0.9175</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6764</v>
+        <v>1.0354</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6764</v>
+        <v>1.0354</v>
       </c>
       <c r="N23" t="n">
         <v>187</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6437</v>
+        <v>0.8678</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1841</v>
+        <v>0.2482</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1875</v>
+        <v>-0.2462</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6437</v>
+        <v>0.8678</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6437</v>
+        <v>0.8678</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6437</v>
+        <v>0.8678</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6546</v>
+        <v>0.9406</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6546</v>
+        <v>0.9406</v>
       </c>
       <c r="N24" t="n">
         <v>178</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2069</v>
+        <v>0.4866</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0592</v>
+        <v>0.1391</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3615</v>
+        <v>-0.4183</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2069</v>
+        <v>0.4866</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2069</v>
+        <v>0.4866</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2069</v>
+        <v>0.4866</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2122</v>
+        <v>0.5491</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2122</v>
+        <v>0.5491</v>
       </c>
       <c r="N25" t="n">
         <v>187</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.165</v>
+        <v>0.3643</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0472</v>
+        <v>0.1042</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3782</v>
+        <v>-0.4736</v>
       </c>
       <c r="E26" t="n">
-        <v>0.165</v>
+        <v>0.3643</v>
       </c>
       <c r="F26" t="n">
-        <v>0.165</v>
+        <v>0.3643</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.165</v>
+        <v>0.3643</v>
       </c>
       <c r="I26" t="n">
-        <v>0.165</v>
+        <v>0.3643</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.165</v>
+        <v>0.3643</v>
       </c>
       <c r="N26" t="n">
         <v>124</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1587</v>
+        <v>0.3497</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0454</v>
+        <v>0.1</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3807</v>
+        <v>-0.4801</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1587</v>
+        <v>0.3497</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1587</v>
+        <v>0.3497</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1587</v>
+        <v>0.3497</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1614</v>
+        <v>0.3791</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1614</v>
+        <v>0.3791</v>
       </c>
       <c r="N27" t="n">
         <v>160</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4686</v>
+        <v>0.2005</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.134</v>
+        <v>0.0573</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6306</v>
+        <v>-0.5475</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4686</v>
+        <v>0.2005</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.4686</v>
+        <v>0.2005</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4686</v>
+        <v>0.2005</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.4765</v>
+        <v>0.2173</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4765</v>
+        <v>0.2173</v>
       </c>
       <c r="N28" t="n">
         <v>160</v>
@@ -1734,170 +1734,170 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5081</v>
+        <v>-0.032</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1453</v>
+        <v>-0.0092</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6463</v>
+        <v>-0.6525</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5081</v>
+        <v>-0.032</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5081</v>
+        <v>-0.032</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5081</v>
+        <v>-0.032</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5081</v>
+        <v>-0.0392</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>124</v>
+        <v>252</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5081</v>
+        <v>-0.0392</v>
       </c>
       <c r="N29" t="n">
-        <v>124</v>
+        <v>252</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6656</v>
+        <v>-0.1917</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1903</v>
+        <v>-0.0548</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7091</v>
+        <v>-0.7246</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6656</v>
+        <v>-0.1917</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6656</v>
+        <v>-0.1917</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6656</v>
+        <v>-0.1917</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.1917</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.1917</v>
       </c>
       <c r="N30" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7801</v>
+        <v>-0.2817</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2231</v>
+        <v>-0.0806</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7547</v>
+        <v>-0.7652</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7801</v>
+        <v>-0.2817</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7801</v>
+        <v>-0.2817</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7801</v>
+        <v>-0.2817</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8135</v>
+        <v>-0.3054</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8135</v>
+        <v>-0.3054</v>
       </c>
       <c r="N31" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7915</v>
+        <v>-0.3816</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2263</v>
+        <v>-0.1091</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7592</v>
+        <v>-0.8103</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7915</v>
+        <v>-0.3816</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7915</v>
+        <v>-0.3816</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7915</v>
+        <v>-0.3816</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.4136</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.4136</v>
       </c>
       <c r="N32" t="n">
         <v>160</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8527</v>
+        <v>-0.4074</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2438</v>
+        <v>-0.1165</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7836</v>
+        <v>-0.8219</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8527</v>
+        <v>-0.4074</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8527</v>
+        <v>-0.4074</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8527</v>
+        <v>-0.4074</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8527</v>
+        <v>-0.4074</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8527</v>
+        <v>-0.4074</v>
       </c>
       <c r="N33" t="n">
         <v>124</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0247</v>
+        <v>-0.6197</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.293</v>
+        <v>-0.1772</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8522</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0247</v>
+        <v>-0.6197</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0247</v>
+        <v>-0.6197</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0247</v>
+        <v>-0.6197</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0247</v>
+        <v>-0.6197</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0247</v>
+        <v>-0.6197</v>
       </c>
       <c r="N34" t="n">
         <v>124</v>
@@ -2010,185 +2010,185 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.843</v>
+        <v>-0.884</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.527</v>
+        <v>-0.2528</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1782</v>
+        <v>-1.0371</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.843</v>
+        <v>-0.884</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.843</v>
+        <v>-0.884</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.843</v>
+        <v>-0.884</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.8742</v>
+        <v>-1.2203</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>178</v>
+        <v>405</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.8742</v>
+        <v>-1.2203</v>
       </c>
       <c r="N35" t="n">
-        <v>178</v>
+        <v>405</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.9367</v>
+        <v>-1.2544</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5538</v>
+        <v>-0.3587</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2155</v>
+        <v>-1.2043</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.9367</v>
+        <v>-1.2544</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.9367</v>
+        <v>-1.2544</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.9367</v>
+        <v>-1.2544</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.071</v>
+        <v>-1.7317</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>405</v>
+        <v>257</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-2.071</v>
+        <v>-1.7317</v>
       </c>
       <c r="N36" t="n">
-        <v>405</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.9989</v>
+        <v>-1.3333</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5716</v>
+        <v>-0.3813</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2403</v>
+        <v>-1.2399</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.9989</v>
+        <v>-1.3333</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.9989</v>
+        <v>-1.3333</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.9989</v>
+        <v>-1.3333</v>
       </c>
       <c r="I37" t="n">
-        <v>-2.0498</v>
+        <v>-1.4452</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-2.0498</v>
+        <v>-1.4452</v>
       </c>
       <c r="N37" t="n">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.1446</v>
+        <v>-1.3613</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.6133</v>
+        <v>-0.3893</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2983</v>
+        <v>-1.2526</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.1446</v>
+        <v>-1.3613</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.1446</v>
+        <v>-1.3613</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.1446</v>
+        <v>-1.3613</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.2933</v>
+        <v>-1.5363</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>257</v>
+        <v>187</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.2933</v>
+        <v>-1.5363</v>
       </c>
       <c r="N38" t="n">
-        <v>257</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.4043</v>
+        <v>-1.5304</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6875</v>
+        <v>-0.4376</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4018</v>
+        <v>-1.3289</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.4043</v>
+        <v>-1.5304</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.4043</v>
+        <v>-1.5304</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.4043</v>
+        <v>-1.5304</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.5072</v>
+        <v>-1.8721</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.5072</v>
+        <v>-1.8721</v>
       </c>
       <c r="N39" t="n">
         <v>252</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.9782</v>
+        <v>-1.9014</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.8516</v>
+        <v>-0.5437</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6304</v>
+        <v>-1.4964</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.9782</v>
+        <v>-1.9014</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.9782</v>
+        <v>-1.9014</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.9782</v>
+        <v>-1.9014</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.0285</v>
+        <v>-2.061</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.0285</v>
+        <v>-2.061</v>
       </c>
       <c r="N40" t="n">
         <v>178</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-5.2204</v>
+        <v>-3.1663</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.4928</v>
+        <v>-0.9054</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.5237</v>
+        <v>-2.0674</v>
       </c>
       <c r="E41" t="n">
-        <v>-5.2204</v>
+        <v>-3.1663</v>
       </c>
       <c r="F41" t="n">
-        <v>-5.2204</v>
+        <v>-3.1663</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-5.2204</v>
+        <v>-3.1663</v>
       </c>
       <c r="I41" t="n">
-        <v>-5.5358</v>
+        <v>-4.1984</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-5.5358</v>
+        <v>-4.1984</v>
       </c>
       <c r="N41" t="n">
         <v>347</v>
@@ -2429,10 +2429,10 @@
         <v>1.31</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9162</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>25.6536</v>
+        <v>24.8528</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6044</v>
+        <v>0.5603</v>
       </c>
       <c r="J3" t="n">
-        <v>16.9232</v>
+        <v>15.6884</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4125</v>
+        <v>0.3705</v>
       </c>
       <c r="J4" t="n">
-        <v>11.55</v>
+        <v>10.374</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3773</v>
+        <v>-0.3255</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.5644</v>
+        <v>-9.114000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1495</v>
+        <v>-1.1444</v>
       </c>
       <c r="J6" t="n">
-        <v>-32.186</v>
+        <v>-32.0432</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.6076</v>
       </c>
       <c r="J7" t="n">
-        <v>14.3248</v>
+        <v>17.0128</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4172</v>
+        <v>0.4848</v>
       </c>
       <c r="J8" t="n">
-        <v>11.6816</v>
+        <v>13.5744</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1645</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.606</v>
+        <v>-2.5424</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.87</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2846</v>
+        <v>-0.1698</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.9688</v>
+        <v>-4.7544</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.79</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4036</v>
+        <v>-0.252</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.3008</v>
+        <v>-7.056</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.452</v>
+        <v>1.2931</v>
       </c>
       <c r="J12" t="n">
-        <v>39.204</v>
+        <v>34.9137</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.32</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8118</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>21.9186</v>
+        <v>22.3317</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.27</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6879</v>
+        <v>0.7143</v>
       </c>
       <c r="J14" t="n">
-        <v>18.5733</v>
+        <v>19.2861</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0395</v>
+        <v>0.036</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.0665</v>
+        <v>0.972</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.99</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1974</v>
+        <v>-0.1149</v>
       </c>
       <c r="J16" t="n">
-        <v>-5.3298</v>
+        <v>-3.1023</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4387</v>
+        <v>0.5012</v>
       </c>
       <c r="J17" t="n">
-        <v>11.8449</v>
+        <v>13.5324</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1637</v>
+        <v>-0.1302</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.4199</v>
+        <v>-3.5154</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.83</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.285</v>
+        <v>-0.1911</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.695</v>
+        <v>-5.1597</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.7</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4859</v>
+        <v>-0.3175</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.1193</v>
+        <v>-8.5725</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.63</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5806</v>
+        <v>-0.3836</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.6762</v>
+        <v>-10.3572</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.34</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9133</v>
+        <v>0.903</v>
       </c>
       <c r="J22" t="n">
-        <v>22.8325</v>
+        <v>22.575</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.32</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8569</v>
       </c>
       <c r="J23" t="n">
-        <v>21.71</v>
+        <v>21.4225</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.08</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2052</v>
+        <v>0.2576</v>
       </c>
       <c r="J24" t="n">
-        <v>5.13</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.02</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0001</v>
+        <v>0.061</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0025</v>
+        <v>1.525</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.97</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2409</v>
+        <v>-0.1681</v>
       </c>
       <c r="J26" t="n">
-        <v>-6.0225</v>
+        <v>-4.2025</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.632</v>
+        <v>0.7681</v>
       </c>
       <c r="J27" t="n">
-        <v>15.8</v>
+        <v>19.2025</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1429</v>
+        <v>0.1315</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5725</v>
+        <v>3.2875</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3514</v>
+        <v>-0.2211</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.785</v>
+        <v>-5.5275</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.77</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4103</v>
+        <v>-0.2608</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.2575</v>
+        <v>-6.52</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.68</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5336</v>
+        <v>-0.3474</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.34</v>
+        <v>-8.685</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.52</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7664</v>
+        <v>0.732</v>
       </c>
       <c r="J32" t="n">
-        <v>22.2256</v>
+        <v>21.228</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4328</v>
+        <v>0.3897</v>
       </c>
       <c r="J33" t="n">
-        <v>12.5512</v>
+        <v>11.3013</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.93</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1937</v>
+        <v>-0.1067</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.6173</v>
+        <v>-3.0943</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2286</v>
+        <v>-0.1298</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.6294</v>
+        <v>-3.7642</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.3429</v>
       </c>
       <c r="J36" t="n">
-        <v>-15.3903</v>
+        <v>-9.944100000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.62</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8767</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>25.4243</v>
+        <v>22.9912</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.11</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2191</v>
+        <v>0.1798</v>
       </c>
       <c r="J38" t="n">
-        <v>6.3539</v>
+        <v>5.2142</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1166</v>
+        <v>0.1081</v>
       </c>
       <c r="J39" t="n">
-        <v>3.3814</v>
+        <v>3.1349</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2119</v>
+        <v>-0.1186</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.1451</v>
+        <v>-3.4394</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6424</v>
+        <v>-0.4264</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.6296</v>
+        <v>-12.3656</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.27</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7855</v>
+        <v>0.7598</v>
       </c>
       <c r="J42" t="n">
-        <v>22.7795</v>
+        <v>22.0342</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.23</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6893</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>19.9897</v>
+        <v>19.1922</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.19</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5616</v>
       </c>
       <c r="J44" t="n">
-        <v>17.0578</v>
+        <v>16.2864</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.285</v>
+        <v>-0.221</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.265000000000001</v>
+        <v>-6.409</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6989</v>
+        <v>-0.6465</v>
       </c>
       <c r="J46" t="n">
-        <v>-20.2681</v>
+        <v>-18.7485</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7207</v>
+        <v>0.8924</v>
       </c>
       <c r="J47" t="n">
-        <v>20.9003</v>
+        <v>25.8796</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.2</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3871</v>
+        <v>0.442</v>
       </c>
       <c r="J48" t="n">
-        <v>11.2259</v>
+        <v>12.818</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.96</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1099</v>
+        <v>-0.0623</v>
       </c>
       <c r="J49" t="n">
-        <v>-3.1871</v>
+        <v>-1.8067</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.72</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.492</v>
+        <v>-0.3161</v>
       </c>
       <c r="J50" t="n">
-        <v>-14.268</v>
+        <v>-9.1669</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.61</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6322</v>
+        <v>-0.419</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.3338</v>
+        <v>-12.151</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.44</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7219</v>
+        <v>0.8962</v>
       </c>
       <c r="J52" t="n">
-        <v>19.4913</v>
+        <v>24.1974</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0444</v>
+        <v>0.0153</v>
       </c>
       <c r="J53" t="n">
-        <v>1.1988</v>
+        <v>0.4131</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.82</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3316</v>
+        <v>-0.2093</v>
       </c>
       <c r="J54" t="n">
-        <v>-8.953200000000001</v>
+        <v>-5.6511</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.68</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5306</v>
+        <v>-0.3457</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.3262</v>
+        <v>-9.3339</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.66</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5568</v>
+        <v>-0.3646</v>
       </c>
       <c r="J56" t="n">
-        <v>-15.0336</v>
+        <v>-9.844200000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.44</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1337</v>
+        <v>1.0802</v>
       </c>
       <c r="J57" t="n">
-        <v>30.6099</v>
+        <v>29.1654</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5581</v>
+        <v>0.5486</v>
       </c>
       <c r="J58" t="n">
-        <v>15.0687</v>
+        <v>14.8122</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.15</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4443</v>
+        <v>0.4481</v>
       </c>
       <c r="J59" t="n">
-        <v>11.9961</v>
+        <v>12.0987</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.02</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0058</v>
+        <v>0.0641</v>
       </c>
       <c r="J60" t="n">
-        <v>0.1566</v>
+        <v>1.7307</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5366</v>
+        <v>-0.4715</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.4882</v>
+        <v>-12.7305</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.48</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6949</v>
+        <v>0.6135</v>
       </c>
       <c r="J62" t="n">
-        <v>20.1521</v>
+        <v>17.7915</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2664</v>
+        <v>0.2369</v>
       </c>
       <c r="J63" t="n">
-        <v>7.7256</v>
+        <v>6.8701</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.12</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1885</v>
+        <v>0.1857</v>
       </c>
       <c r="J64" t="n">
-        <v>5.4665</v>
+        <v>5.3853</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.12</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1885</v>
+        <v>0.1857</v>
       </c>
       <c r="J65" t="n">
-        <v>5.4665</v>
+        <v>5.3853</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3405</v>
+        <v>-0.2038</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.874499999999999</v>
+        <v>-5.9102</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.16</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3366</v>
+        <v>0.2867</v>
       </c>
       <c r="J67" t="n">
-        <v>9.7614</v>
+        <v>8.314299999999999</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.01</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0589</v>
+        <v>0.0333</v>
       </c>
       <c r="J68" t="n">
-        <v>1.7081</v>
+        <v>0.9657</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0958</v>
+        <v>-0.0604</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.7782</v>
+        <v>-1.7516</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1605</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.6545</v>
+        <v>-2.8014</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4184</v>
+        <v>-0.2647</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.1336</v>
+        <v>-7.6763</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.2</v>
       </c>
       <c r="I72" t="n">
-        <v>0.3885</v>
+        <v>0.4433</v>
       </c>
       <c r="J72" t="n">
-        <v>13.986</v>
+        <v>15.9588</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.07</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1801</v>
+        <v>0.1868</v>
       </c>
       <c r="J73" t="n">
-        <v>6.4836</v>
+        <v>6.7248</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0121</v>
+        <v>0.0016</v>
       </c>
       <c r="J74" t="n">
-        <v>0.4356</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.92</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1877</v>
+        <v>-0.1102</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.7572</v>
+        <v>-3.9672</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.74</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4644</v>
+        <v>-0.2964</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.7184</v>
+        <v>-10.6704</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.33</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9293</v>
+        <v>0.9082</v>
       </c>
       <c r="J77" t="n">
-        <v>33.4548</v>
+        <v>32.6952</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.16</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5161</v>
+        <v>0.4882</v>
       </c>
       <c r="J78" t="n">
-        <v>18.5796</v>
+        <v>17.5752</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.15</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4886</v>
+        <v>0.462</v>
       </c>
       <c r="J79" t="n">
-        <v>17.5896</v>
+        <v>16.632</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2794</v>
+        <v>-0.2177</v>
       </c>
       <c r="J80" t="n">
-        <v>-10.0584</v>
+        <v>-7.8372</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.79</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-0.6691</v>
       </c>
       <c r="J81" t="n">
-        <v>-25.8948</v>
+        <v>-24.0876</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6972</v>
+        <v>0.6508</v>
       </c>
       <c r="J82" t="n">
-        <v>20.916</v>
+        <v>19.524</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.4312</v>
+        <v>0.3805</v>
       </c>
       <c r="J83" t="n">
-        <v>12.936</v>
+        <v>11.415</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.02</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1259</v>
+        <v>0.0954</v>
       </c>
       <c r="J84" t="n">
-        <v>3.777</v>
+        <v>2.862</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.9</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.392</v>
+        <v>-0.3466</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.76</v>
+        <v>-10.398</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.8568</v>
+        <v>-0.8219</v>
       </c>
       <c r="J86" t="n">
-        <v>-25.704</v>
+        <v>-24.657</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.33</v>
       </c>
       <c r="I87" t="n">
-        <v>0.5542</v>
+        <v>0.6635</v>
       </c>
       <c r="J87" t="n">
-        <v>16.626</v>
+        <v>19.905</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.17</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3345</v>
+        <v>0.3788</v>
       </c>
       <c r="J88" t="n">
-        <v>10.035</v>
+        <v>11.364</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.99</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0485</v>
+        <v>-0.0216</v>
       </c>
       <c r="J89" t="n">
-        <v>-1.455</v>
+        <v>-0.648</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2972</v>
+        <v>-0.1791</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.916</v>
+        <v>-5.373</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.72</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4966</v>
+        <v>-0.3188</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.898</v>
+        <v>-9.564</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4062</v>
+        <v>0.3497</v>
       </c>
       <c r="J92" t="n">
-        <v>9.342599999999999</v>
+        <v>8.043100000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3293</v>
+        <v>0.2707</v>
       </c>
       <c r="J93" t="n">
-        <v>7.5739</v>
+        <v>6.2261</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.63</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.5736</v>
+        <v>-0.3798</v>
       </c>
       <c r="J94" t="n">
-        <v>-13.1928</v>
+        <v>-8.7354</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.61</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.6</v>
+        <v>-0.3985</v>
       </c>
       <c r="J95" t="n">
-        <v>-13.8</v>
+        <v>-9.1655</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.58</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6389</v>
+        <v>-0.4264</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.6947</v>
+        <v>-9.8072</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.78</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9744</v>
+        <v>0.8929</v>
       </c>
       <c r="J97" t="n">
-        <v>22.4112</v>
+        <v>20.5367</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.5</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6711</v>
+        <v>0.6034</v>
       </c>
       <c r="J98" t="n">
-        <v>15.4353</v>
+        <v>13.8782</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.27</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3587</v>
+        <v>0.3544</v>
       </c>
       <c r="J99" t="n">
-        <v>8.2501</v>
+        <v>8.151199999999999</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.05</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0249</v>
+        <v>0.0631</v>
       </c>
       <c r="J100" t="n">
-        <v>0.5727</v>
+        <v>1.4513</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.96</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1889</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J101" t="n">
-        <v>-4.3447</v>
+        <v>-2.1574</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.79</v>
       </c>
       <c r="I102" t="n">
-        <v>1.7357</v>
+        <v>1.483</v>
       </c>
       <c r="J102" t="n">
-        <v>39.9211</v>
+        <v>34.109</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.4</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9833</v>
+        <v>0.99</v>
       </c>
       <c r="J103" t="n">
-        <v>22.6159</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.24</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5809</v>
+        <v>0.6445</v>
       </c>
       <c r="J104" t="n">
-        <v>13.3607</v>
+        <v>14.8235</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.18</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4237</v>
+        <v>0.5001</v>
       </c>
       <c r="J105" t="n">
-        <v>9.745100000000001</v>
+        <v>11.5023</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.7</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9671</v>
+        <v>-0.9376</v>
       </c>
       <c r="J106" t="n">
-        <v>-22.2433</v>
+        <v>-21.5648</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3132</v>
+        <v>0.3325</v>
       </c>
       <c r="J107" t="n">
-        <v>7.2036</v>
+        <v>7.6475</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.8</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.3218</v>
+        <v>-0.2175</v>
       </c>
       <c r="J108" t="n">
-        <v>-7.4014</v>
+        <v>-5.0025</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.75</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.4034</v>
+        <v>-0.2658</v>
       </c>
       <c r="J109" t="n">
-        <v>-9.2782</v>
+        <v>-6.1134</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.73</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4336</v>
+        <v>-0.285</v>
       </c>
       <c r="J110" t="n">
-        <v>-9.972799999999999</v>
+        <v>-6.555</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.72</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4484</v>
+        <v>-0.2946</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.3132</v>
+        <v>-6.7758</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.26</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4852</v>
+        <v>0.434</v>
       </c>
       <c r="J112" t="n">
-        <v>13.1004</v>
+        <v>11.718</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.97</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0545</v>
+        <v>-0.0462</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.4715</v>
+        <v>-1.2474</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1025</v>
+        <v>-0.0716</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.7675</v>
+        <v>-1.9332</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.84</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3095</v>
+        <v>-0.1922</v>
       </c>
       <c r="J115" t="n">
-        <v>-8.3565</v>
+        <v>-5.1894</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.72</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4833</v>
+        <v>-0.3111</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.0491</v>
+        <v>-8.399699999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.6</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8118</v>
+        <v>0.7294</v>
       </c>
       <c r="J117" t="n">
-        <v>21.9186</v>
+        <v>19.6938</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.4</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5807</v>
+        <v>0.5112</v>
       </c>
       <c r="J118" t="n">
-        <v>15.6789</v>
+        <v>13.8024</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.15</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2137</v>
+        <v>0.2188</v>
       </c>
       <c r="J119" t="n">
-        <v>5.7699</v>
+        <v>5.9076</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.99</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1065</v>
+        <v>-0.0408</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.8755</v>
+        <v>-1.1016</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.91</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2594</v>
+        <v>-0.145</v>
       </c>
       <c r="J121" t="n">
-        <v>-7.0038</v>
+        <v>-3.915</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.81</v>
       </c>
       <c r="I122" t="n">
-        <v>1.8101</v>
+        <v>1.5344</v>
       </c>
       <c r="J122" t="n">
-        <v>45.2525</v>
+        <v>38.36</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.24</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6577</v>
+        <v>0.6586</v>
       </c>
       <c r="J123" t="n">
-        <v>16.4425</v>
+        <v>16.465</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2465</v>
+        <v>0.3072</v>
       </c>
       <c r="J124" t="n">
-        <v>6.1625</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.1246</v>
+        <v>0.189</v>
       </c>
       <c r="J125" t="n">
-        <v>3.115</v>
+        <v>4.725</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.9729</v>
+        <v>-0.9443</v>
       </c>
       <c r="J126" t="n">
-        <v>-24.3225</v>
+        <v>-23.6075</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.6232</v>
+        <v>0.7559</v>
       </c>
       <c r="J127" t="n">
-        <v>15.58</v>
+        <v>18.8975</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1861</v>
+        <v>0.1815</v>
       </c>
       <c r="J128" t="n">
-        <v>4.6525</v>
+        <v>4.5375</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.87</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2516</v>
+        <v>-0.1582</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.29</v>
+        <v>-3.955</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.67</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.5446</v>
+        <v>-0.3556</v>
       </c>
       <c r="J130" t="n">
-        <v>-13.615</v>
+        <v>-8.890000000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.66</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5576</v>
+        <v>-0.365</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.94</v>
+        <v>-9.125</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.34</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9187</v>
+        <v>0.9067</v>
       </c>
       <c r="J132" t="n">
-        <v>24.8049</v>
+        <v>24.4809</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6604</v>
+        <v>0.6463</v>
       </c>
       <c r="J133" t="n">
-        <v>17.8308</v>
+        <v>17.4501</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2738</v>
+        <v>0.3169</v>
       </c>
       <c r="J134" t="n">
-        <v>7.3926</v>
+        <v>8.5563</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.04</v>
       </c>
       <c r="I135" t="n">
-        <v>0.0794</v>
+        <v>0.1351</v>
       </c>
       <c r="J135" t="n">
-        <v>2.1438</v>
+        <v>3.6477</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2368</v>
+        <v>-0.1655</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.3936</v>
+        <v>-4.4685</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.15</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3265</v>
+        <v>0.36</v>
       </c>
       <c r="J137" t="n">
-        <v>8.8155</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2462</v>
+        <v>0.2597</v>
       </c>
       <c r="J138" t="n">
-        <v>6.6474</v>
+        <v>7.0119</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1355</v>
+        <v>0.1267</v>
       </c>
       <c r="J139" t="n">
-        <v>3.6585</v>
+        <v>3.4209</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.01</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0654</v>
+        <v>0.0465</v>
       </c>
       <c r="J140" t="n">
-        <v>1.7658</v>
+        <v>1.2555</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.46</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.8041</v>
+        <v>-0.5506</v>
       </c>
       <c r="J141" t="n">
-        <v>-21.7107</v>
+        <v>-14.8662</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.36</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9361</v>
+        <v>0.9333</v>
       </c>
       <c r="J142" t="n">
-        <v>24.3386</v>
+        <v>24.2658</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8233</v>
+        <v>0.8206</v>
       </c>
       <c r="J143" t="n">
-        <v>21.4058</v>
+        <v>21.3356</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.22</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6012</v>
+        <v>0.6097</v>
       </c>
       <c r="J144" t="n">
-        <v>15.6312</v>
+        <v>15.8522</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4454</v>
+        <v>0.4902</v>
       </c>
       <c r="J145" t="n">
-        <v>11.5804</v>
+        <v>12.7452</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.87</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5526</v>
+        <v>-0.4849</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.3676</v>
+        <v>-12.6074</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.2</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4195</v>
+        <v>0.4768</v>
       </c>
       <c r="J147" t="n">
-        <v>10.907</v>
+        <v>12.3968</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1356</v>
+        <v>0.1165</v>
       </c>
       <c r="J148" t="n">
-        <v>3.5256</v>
+        <v>3.029</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.02</v>
       </c>
       <c r="I149" t="n">
-        <v>0.113</v>
+        <v>0.0896</v>
       </c>
       <c r="J149" t="n">
-        <v>2.938</v>
+        <v>2.3296</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.77</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4007</v>
+        <v>-0.2565</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.4182</v>
+        <v>-6.669</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.48</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.7746</v>
+        <v>-0.5275</v>
       </c>
       <c r="J151" t="n">
-        <v>-20.1396</v>
+        <v>-13.715</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.61</v>
       </c>
       <c r="I152" t="n">
-        <v>1.4881</v>
+        <v>1.3136</v>
       </c>
       <c r="J152" t="n">
-        <v>41.6668</v>
+        <v>36.7808</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.24</v>
       </c>
       <c r="I153" t="n">
-        <v>0.7079</v>
+        <v>0.6829</v>
       </c>
       <c r="J153" t="n">
-        <v>19.8212</v>
+        <v>19.1212</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.14</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4445</v>
+        <v>0.4298</v>
       </c>
       <c r="J154" t="n">
-        <v>12.446</v>
+        <v>12.0344</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.75</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.82</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="J155" t="n">
-        <v>-22.96</v>
+        <v>-21.7476</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.82</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="J156" t="n">
-        <v>-22.96</v>
+        <v>-21.7476</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5536</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="J157" t="n">
-        <v>15.5008</v>
+        <v>18.5024</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.02</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0793</v>
+        <v>0.0699</v>
       </c>
       <c r="J158" t="n">
-        <v>2.2204</v>
+        <v>1.9572</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.96</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1036</v>
+        <v>-0.0613</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.9008</v>
+        <v>-1.7164</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.85</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3029</v>
+        <v>-0.1854</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.481199999999999</v>
+        <v>-5.1912</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.74</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4627</v>
+        <v>-0.2954</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.9556</v>
+        <v>-8.2712</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.84</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.1778</v>
+        <v>-0.1586</v>
       </c>
       <c r="J162" t="n">
-        <v>-3.2004</v>
+        <v>-2.8548</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.79</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2586</v>
+        <v>-0.2118</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.6548</v>
+        <v>-3.8124</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.75</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3238</v>
+        <v>-0.2518</v>
       </c>
       <c r="J164" t="n">
-        <v>-5.8284</v>
+        <v>-4.5324</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.61</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5642</v>
+        <v>-0.3809</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.1556</v>
+        <v>-6.8562</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.54</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.661</v>
+        <v>-0.4463</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.898</v>
+        <v>-8.0334</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.88</v>
       </c>
       <c r="I167" t="n">
-        <v>1.7998</v>
+        <v>1.5337</v>
       </c>
       <c r="J167" t="n">
-        <v>32.3964</v>
+        <v>27.6066</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.51</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1016</v>
+        <v>1.1072</v>
       </c>
       <c r="J168" t="n">
-        <v>19.8288</v>
+        <v>19.9296</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.5</v>
       </c>
       <c r="I169" t="n">
-        <v>1.0788</v>
+        <v>1.0955</v>
       </c>
       <c r="J169" t="n">
-        <v>19.4184</v>
+        <v>19.719</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.44</v>
       </c>
       <c r="I170" t="n">
-        <v>0.9271</v>
+        <v>1.0219</v>
       </c>
       <c r="J170" t="n">
-        <v>16.6878</v>
+        <v>18.3942</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.0306</v>
+        <v>0.1216</v>
       </c>
       <c r="J171" t="n">
-        <v>0.5508</v>
+        <v>2.1888</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.28</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4852</v>
+        <v>0.5729</v>
       </c>
       <c r="J172" t="n">
-        <v>14.556</v>
+        <v>17.187</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.12</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2515</v>
+        <v>0.2801</v>
       </c>
       <c r="J173" t="n">
-        <v>7.545</v>
+        <v>8.403</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.04</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1008</v>
+        <v>0.1118</v>
       </c>
       <c r="J174" t="n">
-        <v>3.024</v>
+        <v>3.354</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1248</v>
+        <v>-0.0658</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.744</v>
+        <v>-1.974</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4855</v>
+        <v>-0.3105</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.565</v>
+        <v>-9.315</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.23</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7165</v>
+        <v>0.6796</v>
       </c>
       <c r="J177" t="n">
-        <v>21.495</v>
+        <v>20.388</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.14</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4835</v>
+        <v>0.4459</v>
       </c>
       <c r="J178" t="n">
-        <v>14.505</v>
+        <v>13.377</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.08</v>
       </c>
       <c r="I179" t="n">
-        <v>0.3039</v>
+        <v>0.278</v>
       </c>
       <c r="J179" t="n">
-        <v>9.117000000000001</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2352</v>
+        <v>0.2183</v>
       </c>
       <c r="J180" t="n">
-        <v>7.056</v>
+        <v>6.549</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.7</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.8857</v>
       </c>
       <c r="J181" t="n">
-        <v>-27.534</v>
+        <v>-26.571</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9449</v>
+        <v>0.9554</v>
       </c>
       <c r="J182" t="n">
-        <v>26.4572</v>
+        <v>26.7512</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.28</v>
       </c>
       <c r="I183" t="n">
-        <v>0.7095</v>
+        <v>0.7358</v>
       </c>
       <c r="J183" t="n">
-        <v>19.866</v>
+        <v>20.6024</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5615</v>
+        <v>0.623</v>
       </c>
       <c r="J184" t="n">
-        <v>15.722</v>
+        <v>17.444</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.4815</v>
+        <v>0.5515</v>
       </c>
       <c r="J185" t="n">
-        <v>13.482</v>
+        <v>15.442</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.17</v>
       </c>
       <c r="I186" t="n">
-        <v>0.4027</v>
+        <v>0.4771</v>
       </c>
       <c r="J186" t="n">
-        <v>11.2756</v>
+        <v>13.3588</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.04</v>
       </c>
       <c r="I187" t="n">
-        <v>0.1865</v>
+        <v>0.1696</v>
       </c>
       <c r="J187" t="n">
-        <v>5.222</v>
+        <v>4.7488</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.91</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1154</v>
+        <v>-0.1042</v>
       </c>
       <c r="J188" t="n">
-        <v>-3.2312</v>
+        <v>-2.9176</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.9</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1335</v>
+        <v>-0.1157</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.738</v>
+        <v>-3.2396</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.65</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.3615</v>
       </c>
       <c r="J190" t="n">
-        <v>-15.3412</v>
+        <v>-10.122</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5747</v>
+        <v>-0.3803</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.0916</v>
+        <v>-10.6484</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.24</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7501</v>
+        <v>0.7117</v>
       </c>
       <c r="J192" t="n">
-        <v>21.7529</v>
+        <v>20.6393</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6007</v>
+        <v>0.5579</v>
       </c>
       <c r="J193" t="n">
-        <v>17.4203</v>
+        <v>16.1791</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.16</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5482</v>
+        <v>0.5051</v>
       </c>
       <c r="J194" t="n">
-        <v>15.8978</v>
+        <v>14.6479</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4101</v>
+        <v>-0.3563</v>
       </c>
       <c r="J195" t="n">
-        <v>-11.8929</v>
+        <v>-10.3327</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.65</v>
       </c>
       <c r="I196" t="n">
-        <v>-1.0235</v>
+        <v>-1.0029</v>
       </c>
       <c r="J196" t="n">
-        <v>-29.6815</v>
+        <v>-29.0841</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.45</v>
       </c>
       <c r="I197" t="n">
-        <v>0.7009</v>
+        <v>0.8646</v>
       </c>
       <c r="J197" t="n">
-        <v>20.3261</v>
+        <v>25.0734</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.1</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2224</v>
+        <v>0.243</v>
       </c>
       <c r="J198" t="n">
-        <v>6.4496</v>
+        <v>7.047</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.06</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1491</v>
+        <v>0.1589</v>
       </c>
       <c r="J199" t="n">
-        <v>4.3239</v>
+        <v>4.6081</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.8</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3868</v>
+        <v>-0.2406</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.2172</v>
+        <v>-6.9774</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5738</v>
+        <v>-0.3754</v>
       </c>
       <c r="J201" t="n">
-        <v>-16.6402</v>
+        <v>-10.8866</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.31</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8445</v>
+        <v>0.8329</v>
       </c>
       <c r="J202" t="n">
-        <v>21.957</v>
+        <v>21.6554</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.16</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4615</v>
+        <v>0.4708</v>
       </c>
       <c r="J203" t="n">
-        <v>11.999</v>
+        <v>12.2408</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2349</v>
+        <v>0.2861</v>
       </c>
       <c r="J204" t="n">
-        <v>6.1074</v>
+        <v>7.4386</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.09</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2349</v>
+        <v>0.2861</v>
       </c>
       <c r="J205" t="n">
-        <v>6.1074</v>
+        <v>7.4386</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.09</v>
       </c>
       <c r="I206" t="n">
-        <v>0.2349</v>
+        <v>0.2861</v>
       </c>
       <c r="J206" t="n">
-        <v>6.1074</v>
+        <v>7.4386</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.24</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4823</v>
+        <v>0.5609</v>
       </c>
       <c r="J207" t="n">
-        <v>12.5398</v>
+        <v>14.5834</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.11</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2894</v>
+        <v>0.3053</v>
       </c>
       <c r="J208" t="n">
-        <v>7.5244</v>
+        <v>7.9378</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2299</v>
+        <v>-0.1539</v>
       </c>
       <c r="J209" t="n">
-        <v>-5.9774</v>
+        <v>-4.0014</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.7</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4947</v>
+        <v>-0.3218</v>
       </c>
       <c r="J210" t="n">
-        <v>-12.8622</v>
+        <v>-8.3668</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.49</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7603</v>
+        <v>-0.5165</v>
       </c>
       <c r="J211" t="n">
-        <v>-19.7678</v>
+        <v>-13.429</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.16</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3265</v>
+        <v>0.2799</v>
       </c>
       <c r="J212" t="n">
-        <v>9.141999999999999</v>
+        <v>7.8372</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2471</v>
+        <v>0.2052</v>
       </c>
       <c r="J213" t="n">
-        <v>6.9188</v>
+        <v>5.7456</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1329</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.7212</v>
+        <v>-2.1084</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.95</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1329</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J215" t="n">
-        <v>-3.7212</v>
+        <v>-2.1084</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3822</v>
+        <v>-0.2383</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.7016</v>
+        <v>-6.6724</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.27</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4383</v>
+        <v>0.3748</v>
       </c>
       <c r="J217" t="n">
-        <v>12.2724</v>
+        <v>10.4944</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.26</v>
       </c>
       <c r="I218" t="n">
-        <v>0.4246</v>
+        <v>0.3627</v>
       </c>
       <c r="J218" t="n">
-        <v>11.8888</v>
+        <v>10.1556</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.21</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3533</v>
+        <v>0.3016</v>
       </c>
       <c r="J219" t="n">
-        <v>9.8924</v>
+        <v>8.444800000000001</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0538</v>
+        <v>-0.0116</v>
       </c>
       <c r="J220" t="n">
-        <v>-1.5064</v>
+        <v>-0.3248</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.9</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2602</v>
+        <v>-0.1481</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.2856</v>
+        <v>-4.1468</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.95</v>
       </c>
       <c r="I222" t="n">
-        <v>1.9161</v>
+        <v>1.6178</v>
       </c>
       <c r="J222" t="n">
-        <v>40.2381</v>
+        <v>33.9738</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.72</v>
       </c>
       <c r="I223" t="n">
-        <v>1.5266</v>
+        <v>1.3556</v>
       </c>
       <c r="J223" t="n">
-        <v>32.0586</v>
+        <v>28.4676</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.4</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.9595</v>
       </c>
       <c r="J224" t="n">
-        <v>17.8563</v>
+        <v>20.1495</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.12</v>
       </c>
       <c r="I225" t="n">
-        <v>0.202</v>
+        <v>0.301</v>
       </c>
       <c r="J225" t="n">
-        <v>4.242</v>
+        <v>6.321</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.08</v>
       </c>
       <c r="I226" t="n">
-        <v>0.0941</v>
+        <v>0.1873</v>
       </c>
       <c r="J226" t="n">
-        <v>1.9761</v>
+        <v>3.9333</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.91</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0636</v>
+        <v>-0.0796</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.3356</v>
+        <v>-1.6716</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.84</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1817</v>
+        <v>-0.1605</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.8157</v>
+        <v>-3.3705</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.72</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3828</v>
+        <v>-0.2811</v>
       </c>
       <c r="J229" t="n">
-        <v>-8.0388</v>
+        <v>-5.9031</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.6</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5815</v>
+        <v>-0.3915</v>
       </c>
       <c r="J230" t="n">
-        <v>-12.2115</v>
+        <v>-8.221500000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.5</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7157</v>
+        <v>-0.485</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.0297</v>
+        <v>-10.185</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.44</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6787</v>
+        <v>0.8344</v>
       </c>
       <c r="J232" t="n">
-        <v>18.3249</v>
+        <v>22.5288</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.27</v>
       </c>
       <c r="I233" t="n">
-        <v>0.4653</v>
+        <v>0.549</v>
       </c>
       <c r="J233" t="n">
-        <v>12.5631</v>
+        <v>14.823</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.207</v>
+        <v>-0.1166</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.589</v>
+        <v>-3.1482</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2577</v>
+        <v>-0.1504</v>
       </c>
       <c r="J235" t="n">
-        <v>-6.9579</v>
+        <v>-4.0608</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.71</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5152</v>
+        <v>-0.3318</v>
       </c>
       <c r="J236" t="n">
-        <v>-13.9104</v>
+        <v>-8.958600000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.56</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3542</v>
+        <v>1.2255</v>
       </c>
       <c r="J237" t="n">
-        <v>36.5634</v>
+        <v>33.0885</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.41</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0513</v>
+        <v>1.0286</v>
       </c>
       <c r="J238" t="n">
-        <v>28.3851</v>
+        <v>27.7722</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.26</v>
       </c>
       <c r="I239" t="n">
-        <v>0.7126</v>
+        <v>0.708</v>
       </c>
       <c r="J239" t="n">
-        <v>19.2402</v>
+        <v>19.116</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.82</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6747</v>
+        <v>-0.6162</v>
       </c>
       <c r="J240" t="n">
-        <v>-18.2169</v>
+        <v>-16.6374</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6989</v>
+        <v>-0.6424</v>
       </c>
       <c r="J241" t="n">
-        <v>-18.8703</v>
+        <v>-17.3448</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.16</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3071</v>
+        <v>0.3512</v>
       </c>
       <c r="J242" t="n">
-        <v>8.598800000000001</v>
+        <v>9.833600000000001</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.14</v>
       </c>
       <c r="I243" t="n">
-        <v>0.2756</v>
+        <v>0.3136</v>
       </c>
       <c r="J243" t="n">
-        <v>7.7168</v>
+        <v>8.780799999999999</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.01</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0074</v>
+        <v>0.0315</v>
       </c>
       <c r="J244" t="n">
-        <v>0.2072</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.01</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0074</v>
+        <v>0.0315</v>
       </c>
       <c r="J245" t="n">
-        <v>0.2072</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.92</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.2076</v>
+        <v>-0.1169</v>
       </c>
       <c r="J246" t="n">
-        <v>-5.8128</v>
+        <v>-3.2732</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.52</v>
       </c>
       <c r="I247" t="n">
-        <v>1.3248</v>
+        <v>1.2032</v>
       </c>
       <c r="J247" t="n">
-        <v>37.0944</v>
+        <v>33.6896</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.03</v>
       </c>
       <c r="I248" t="n">
-        <v>0.0769</v>
+        <v>0.1148</v>
       </c>
       <c r="J248" t="n">
-        <v>2.1532</v>
+        <v>3.2144</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0677</v>
+        <v>-0.0173</v>
       </c>
       <c r="J249" t="n">
-        <v>-1.8956</v>
+        <v>-0.4844</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.99</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1279</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.5812</v>
+        <v>-2.016</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5698</v>
+        <v>-0.5111</v>
       </c>
       <c r="J251" t="n">
-        <v>-15.9544</v>
+        <v>-14.3108</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.0461</v>
+        <v>-0.0622</v>
       </c>
       <c r="J252" t="n">
-        <v>-1.1525</v>
+        <v>-1.555</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.91</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1015</v>
+        <v>-0.0988</v>
       </c>
       <c r="J253" t="n">
-        <v>-2.5375</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.79</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.3219</v>
+        <v>-0.2245</v>
       </c>
       <c r="J254" t="n">
-        <v>-8.047499999999999</v>
+        <v>-5.6125</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.75</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3918</v>
+        <v>-0.2624</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.795</v>
+        <v>-6.56</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.59</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.6198</v>
+        <v>-0.4135</v>
       </c>
       <c r="J256" t="n">
-        <v>-15.495</v>
+        <v>-10.3375</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.63</v>
       </c>
       <c r="I257" t="n">
-        <v>0.8297</v>
+        <v>0.7492</v>
       </c>
       <c r="J257" t="n">
-        <v>20.7425</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.35</v>
       </c>
       <c r="I258" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.4474</v>
       </c>
       <c r="J258" t="n">
-        <v>12.5125</v>
+        <v>11.185</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2578</v>
+        <v>0.2638</v>
       </c>
       <c r="J259" t="n">
-        <v>6.445</v>
+        <v>6.595</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.11</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1357</v>
+        <v>0.1587</v>
       </c>
       <c r="J260" t="n">
-        <v>3.3925</v>
+        <v>3.9675</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.04</v>
       </c>
       <c r="I261" t="n">
-        <v>0.015</v>
+        <v>0.0521</v>
       </c>
       <c r="J261" t="n">
-        <v>0.375</v>
+        <v>1.3025</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.25</v>
       </c>
       <c r="I262" t="n">
-        <v>0.7542</v>
+        <v>0.722</v>
       </c>
       <c r="J262" t="n">
-        <v>22.626</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.17</v>
       </c>
       <c r="I263" t="n">
-        <v>0.5533</v>
+        <v>0.5194</v>
       </c>
       <c r="J263" t="n">
-        <v>16.599</v>
+        <v>15.582</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.08</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2883</v>
+        <v>0.2739</v>
       </c>
       <c r="J264" t="n">
-        <v>8.648999999999999</v>
+        <v>8.217000000000001</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.96</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.2369</v>
+        <v>-0.1801</v>
       </c>
       <c r="J265" t="n">
-        <v>-7.107</v>
+        <v>-5.403</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.84</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5891</v>
+        <v>-0.533</v>
       </c>
       <c r="J266" t="n">
-        <v>-17.673</v>
+        <v>-15.99</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.48</v>
       </c>
       <c r="I267" t="n">
-        <v>0.7559</v>
+        <v>0.9412</v>
       </c>
       <c r="J267" t="n">
-        <v>22.677</v>
+        <v>28.236</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.16</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3402</v>
+        <v>0.3781</v>
       </c>
       <c r="J268" t="n">
-        <v>10.206</v>
+        <v>11.343</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.75</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.444</v>
+        <v>-0.2831</v>
       </c>
       <c r="J269" t="n">
-        <v>-13.32</v>
+        <v>-8.493</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.73</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4715</v>
+        <v>-0.3024</v>
       </c>
       <c r="J270" t="n">
-        <v>-14.145</v>
+        <v>-9.071999999999999</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.66</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5639</v>
+        <v>-0.3689</v>
       </c>
       <c r="J271" t="n">
-        <v>-16.917</v>
+        <v>-11.067</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.57</v>
       </c>
       <c r="I272" t="n">
-        <v>1.4011</v>
+        <v>1.255</v>
       </c>
       <c r="J272" t="n">
-        <v>42.033</v>
+        <v>37.65</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.23</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6714</v>
+        <v>0.6518</v>
       </c>
       <c r="J273" t="n">
-        <v>20.142</v>
+        <v>19.554</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.1</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2882</v>
+        <v>0.3204</v>
       </c>
       <c r="J274" t="n">
-        <v>8.646000000000001</v>
+        <v>9.612</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.87</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.5312</v>
+        <v>-0.4672</v>
       </c>
       <c r="J275" t="n">
-        <v>-15.936</v>
+        <v>-14.016</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6592</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="J276" t="n">
-        <v>-19.776</v>
+        <v>-18.069</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.22</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4325</v>
+        <v>0.4965</v>
       </c>
       <c r="J277" t="n">
-        <v>12.975</v>
+        <v>14.895</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.11</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2666</v>
+        <v>0.2835</v>
       </c>
       <c r="J278" t="n">
-        <v>7.998</v>
+        <v>8.505000000000001</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.86</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.2753</v>
+        <v>-0.1707</v>
       </c>
       <c r="J279" t="n">
-        <v>-8.259</v>
+        <v>-5.121</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.8</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3687</v>
+        <v>-0.2321</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.061</v>
+        <v>-6.963</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.72</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.482</v>
+        <v>-0.3103</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.46</v>
+        <v>-9.308999999999999</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.14</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3418</v>
+        <v>0.3723</v>
       </c>
       <c r="J282" t="n">
-        <v>9.2286</v>
+        <v>10.0521</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.08</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2434</v>
+        <v>0.2455</v>
       </c>
       <c r="J283" t="n">
-        <v>6.5718</v>
+        <v>6.6285</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.86</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2413</v>
+        <v>-0.1631</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.5151</v>
+        <v>-4.4037</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.68</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5189</v>
+        <v>-0.3392</v>
       </c>
       <c r="J285" t="n">
-        <v>-14.0103</v>
+        <v>-9.1584</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.59</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6363</v>
+        <v>-0.4235</v>
       </c>
       <c r="J286" t="n">
-        <v>-17.1801</v>
+        <v>-11.4345</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.65</v>
       </c>
       <c r="I287" t="n">
-        <v>1.4913</v>
+        <v>1.3188</v>
       </c>
       <c r="J287" t="n">
-        <v>40.2651</v>
+        <v>35.6076</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.48</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1612</v>
+        <v>1.1064</v>
       </c>
       <c r="J288" t="n">
-        <v>31.3524</v>
+        <v>29.8728</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.27</v>
       </c>
       <c r="I289" t="n">
-        <v>0.6911</v>
+        <v>0.715</v>
       </c>
       <c r="J289" t="n">
-        <v>18.6597</v>
+        <v>19.305</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.01</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0798</v>
+        <v>-0.0041</v>
       </c>
       <c r="J290" t="n">
-        <v>-2.1546</v>
+        <v>-0.1107</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.7397</v>
+        <v>-0.6848</v>
       </c>
       <c r="J291" t="n">
-        <v>-19.9719</v>
+        <v>-18.4896</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.82</v>
       </c>
       <c r="I292" t="n">
-        <v>0.9906</v>
+        <v>0.9121</v>
       </c>
       <c r="J292" t="n">
-        <v>22.7838</v>
+        <v>20.9783</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.6</v>
       </c>
       <c r="I293" t="n">
-        <v>0.7587</v>
+        <v>0.6928</v>
       </c>
       <c r="J293" t="n">
-        <v>17.4501</v>
+        <v>15.9344</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.39</v>
       </c>
       <c r="I294" t="n">
-        <v>0.491</v>
+        <v>0.4776</v>
       </c>
       <c r="J294" t="n">
-        <v>11.293</v>
+        <v>10.9848</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.19</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2236</v>
+        <v>0.2479</v>
       </c>
       <c r="J295" t="n">
-        <v>5.1428</v>
+        <v>5.7017</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.05</v>
       </c>
       <c r="I296" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0522</v>
       </c>
       <c r="J296" t="n">
-        <v>0.2139</v>
+        <v>1.2006</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.16</v>
       </c>
       <c r="I297" t="n">
-        <v>0.463</v>
+        <v>0.4212</v>
       </c>
       <c r="J297" t="n">
-        <v>10.649</v>
+        <v>9.6876</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.87</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1085</v>
+        <v>-0.1133</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.4955</v>
+        <v>-2.6059</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.6199</v>
+        <v>-0.4208</v>
       </c>
       <c r="J299" t="n">
-        <v>-14.2577</v>
+        <v>-9.6784</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.41</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.8183</v>
+        <v>-0.5617</v>
       </c>
       <c r="J300" t="n">
-        <v>-18.8209</v>
+        <v>-12.9191</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.33</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.9161</v>
+        <v>-0.6369</v>
       </c>
       <c r="J301" t="n">
-        <v>-21.0703</v>
+        <v>-14.6487</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.35</v>
       </c>
       <c r="I302" t="n">
-        <v>0.6294</v>
+        <v>0.7663</v>
       </c>
       <c r="J302" t="n">
-        <v>16.3644</v>
+        <v>19.9238</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.12</v>
+        <v>-0.0997</v>
       </c>
       <c r="J303" t="n">
-        <v>-3.12</v>
+        <v>-2.5922</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.77</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3924</v>
+        <v>-0.2532</v>
       </c>
       <c r="J304" t="n">
-        <v>-10.2024</v>
+        <v>-6.5832</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.68</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.5199</v>
+        <v>-0.3398</v>
       </c>
       <c r="J305" t="n">
-        <v>-13.5174</v>
+        <v>-8.8348</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.65</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.5599</v>
+        <v>-0.3681</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.5574</v>
+        <v>-9.570600000000001</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.92</v>
       </c>
       <c r="I307" t="n">
-        <v>1.954</v>
+        <v>1.6531</v>
       </c>
       <c r="J307" t="n">
-        <v>50.804</v>
+        <v>42.9806</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.36</v>
       </c>
       <c r="I308" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9236</v>
       </c>
       <c r="J308" t="n">
-        <v>23.8914</v>
+        <v>24.0136</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.97</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.267</v>
+        <v>-0.1865</v>
       </c>
       <c r="J309" t="n">
-        <v>-6.942</v>
+        <v>-4.849</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.267</v>
+        <v>-0.1865</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.942</v>
+        <v>-4.849</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.87</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5615</v>
+        <v>-0.4928</v>
       </c>
       <c r="J311" t="n">
-        <v>-14.599</v>
+        <v>-12.8128</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.09</v>
       </c>
       <c r="I312" t="n">
-        <v>0.2452</v>
+        <v>0.2523</v>
       </c>
       <c r="J312" t="n">
-        <v>6.3752</v>
+        <v>6.5598</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.03</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1315</v>
+        <v>0.1134</v>
       </c>
       <c r="J313" t="n">
-        <v>3.419</v>
+        <v>2.9484</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.92</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1409</v>
+        <v>-0.1035</v>
       </c>
       <c r="J314" t="n">
-        <v>-3.6634</v>
+        <v>-2.691</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.88</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2275</v>
+        <v>-0.1462</v>
       </c>
       <c r="J315" t="n">
-        <v>-5.915</v>
+        <v>-3.8012</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.63</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.5934</v>
+        <v>-0.3914</v>
       </c>
       <c r="J316" t="n">
-        <v>-15.4284</v>
+        <v>-10.1764</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.65</v>
       </c>
       <c r="I317" t="n">
-        <v>1.5114</v>
+        <v>1.3306</v>
       </c>
       <c r="J317" t="n">
-        <v>39.2964</v>
+        <v>34.5956</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.5</v>
       </c>
       <c r="I318" t="n">
-        <v>1.2222</v>
+        <v>1.1415</v>
       </c>
       <c r="J318" t="n">
-        <v>31.7772</v>
+        <v>29.679</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.19</v>
       </c>
       <c r="I319" t="n">
-        <v>0.4924</v>
+        <v>0.5366</v>
       </c>
       <c r="J319" t="n">
-        <v>12.8024</v>
+        <v>13.9516</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.83</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.6576</v>
+        <v>-0.5967</v>
       </c>
       <c r="J320" t="n">
-        <v>-17.0976</v>
+        <v>-15.5142</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.83</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.6576</v>
+        <v>-0.5967</v>
       </c>
       <c r="J321" t="n">
-        <v>-17.0976</v>
+        <v>-15.5142</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>0.85</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.1515</v>
+        <v>-0.1423</v>
       </c>
       <c r="J322" t="n">
-        <v>-3.7875</v>
+        <v>-3.5575</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.79</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.248</v>
+        <v>-0.2074</v>
       </c>
       <c r="J323" t="n">
-        <v>-6.2</v>
+        <v>-5.185</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.78</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.264</v>
+        <v>-0.2178</v>
       </c>
       <c r="J324" t="n">
-        <v>-6.6</v>
+        <v>-5.445</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.63</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.359</v>
       </c>
       <c r="J325" t="n">
-        <v>-13.1425</v>
+        <v>-8.975</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.38</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.8594000000000001</v>
+        <v>-0.5928</v>
       </c>
       <c r="J326" t="n">
-        <v>-21.485</v>
+        <v>-14.82</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.68</v>
       </c>
       <c r="I327" t="n">
-        <v>1.463</v>
+        <v>1.3134</v>
       </c>
       <c r="J327" t="n">
-        <v>36.575</v>
+        <v>32.835</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.53</v>
       </c>
       <c r="I328" t="n">
-        <v>1.171</v>
+        <v>1.1362</v>
       </c>
       <c r="J328" t="n">
-        <v>29.275</v>
+        <v>28.405</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.49</v>
       </c>
       <c r="I329" t="n">
-        <v>1.0867</v>
+        <v>1.0884</v>
       </c>
       <c r="J329" t="n">
-        <v>27.1675</v>
+        <v>27.21</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.27</v>
       </c>
       <c r="I330" t="n">
-        <v>0.5693</v>
+        <v>0.6813</v>
       </c>
       <c r="J330" t="n">
-        <v>14.2325</v>
+        <v>17.0325</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>1.18</v>
       </c>
       <c r="I331" t="n">
-        <v>0.3587</v>
+        <v>0.4636</v>
       </c>
       <c r="J331" t="n">
-        <v>8.967499999999999</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.41</v>
       </c>
       <c r="I332" t="n">
-        <v>1.0565</v>
+        <v>1.0312</v>
       </c>
       <c r="J332" t="n">
-        <v>44.373</v>
+        <v>43.3104</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.37</v>
       </c>
       <c r="I333" t="n">
-        <v>0.9707</v>
+        <v>0.9616</v>
       </c>
       <c r="J333" t="n">
-        <v>40.7694</v>
+        <v>40.3872</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.21</v>
       </c>
       <c r="I334" t="n">
-        <v>0.592</v>
+        <v>0.5909</v>
       </c>
       <c r="J334" t="n">
-        <v>24.864</v>
+        <v>24.8178</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.2</v>
       </c>
       <c r="I335" t="n">
-        <v>0.5651</v>
+        <v>0.5666</v>
       </c>
       <c r="J335" t="n">
-        <v>23.7342</v>
+        <v>23.7972</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.62</v>
       </c>
       <c r="I336" t="n">
-        <v>-1.1167</v>
+        <v>-1.1069</v>
       </c>
       <c r="J336" t="n">
-        <v>-46.9014</v>
+        <v>-46.4898</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.11</v>
       </c>
       <c r="I337" t="n">
-        <v>0.2697</v>
+        <v>0.2861</v>
       </c>
       <c r="J337" t="n">
-        <v>11.3274</v>
+        <v>12.0162</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.09</v>
       </c>
       <c r="I338" t="n">
-        <v>0.236</v>
+        <v>0.2443</v>
       </c>
       <c r="J338" t="n">
-        <v>9.912000000000001</v>
+        <v>10.2606</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.85</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.2888</v>
+        <v>-0.1802</v>
       </c>
       <c r="J339" t="n">
-        <v>-12.1296</v>
+        <v>-7.5684</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.3361</v>
+        <v>-0.211</v>
       </c>
       <c r="J340" t="n">
-        <v>-14.1162</v>
+        <v>-8.862</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.8</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3664</v>
+        <v>-0.2311</v>
       </c>
       <c r="J341" t="n">
-        <v>-15.3888</v>
+        <v>-9.706200000000001</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.42</v>
       </c>
       <c r="I342" t="n">
-        <v>1.018</v>
+        <v>1.0192</v>
       </c>
       <c r="J342" t="n">
-        <v>27.486</v>
+        <v>27.5184</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.4</v>
       </c>
       <c r="I343" t="n">
-        <v>0.9748</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="J343" t="n">
-        <v>26.3196</v>
+        <v>26.6328</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.37</v>
       </c>
       <c r="I344" t="n">
-        <v>0.9083</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="J344" t="n">
-        <v>24.5241</v>
+        <v>25.0803</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.35</v>
       </c>
       <c r="I345" t="n">
-        <v>0.8626</v>
+        <v>0.8862</v>
       </c>
       <c r="J345" t="n">
-        <v>23.2902</v>
+        <v>23.9274</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.85</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.6271</v>
+        <v>-0.5614</v>
       </c>
       <c r="J346" t="n">
-        <v>-16.9317</v>
+        <v>-15.1578</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.99</v>
       </c>
       <c r="I347" t="n">
-        <v>0.0587</v>
+        <v>0.0149</v>
       </c>
       <c r="J347" t="n">
-        <v>1.5849</v>
+        <v>0.4023</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.8</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.3085</v>
+        <v>-0.2158</v>
       </c>
       <c r="J348" t="n">
-        <v>-8.329499999999999</v>
+        <v>-5.8266</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.77</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.3632</v>
+        <v>-0.2443</v>
       </c>
       <c r="J349" t="n">
-        <v>-9.8064</v>
+        <v>-6.5961</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.77</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.3632</v>
+        <v>-0.2443</v>
       </c>
       <c r="J350" t="n">
-        <v>-9.8064</v>
+        <v>-6.5961</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.4856</v>
+        <v>-0.3206</v>
       </c>
       <c r="J351" t="n">
-        <v>-13.1112</v>
+        <v>-8.6562</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5604/event_5604_evp_summary.xlsx
+++ b/database/event/5604/event_5604_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.814</v>
+        <v>3.7568</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0906</v>
+        <v>1.0743</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0838</v>
+        <v>1.086</v>
       </c>
       <c r="E2" t="n">
-        <v>3.814</v>
+        <v>3.7568</v>
       </c>
       <c r="F2" t="n">
-        <v>3.814</v>
+        <v>3.7568</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.015</v>
+        <v>5.4975</v>
       </c>
       <c r="I2" t="n">
-        <v>6.9231</v>
+        <v>6.7385</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9231</v>
+        <v>6.7385</v>
       </c>
       <c r="N2" t="n">
         <v>405</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.6413</v>
+        <v>3.5097</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0413</v>
+        <v>1.0036</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0059</v>
+        <v>0.9735</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6413</v>
+        <v>3.5097</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6413</v>
+        <v>3.5097</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6358</v>
+        <v>4.9567</v>
       </c>
       <c r="I3" t="n">
-        <v>6.1468</v>
+        <v>5.923</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>6.1468</v>
+        <v>5.923</v>
       </c>
       <c r="N3" t="n">
         <v>347</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.3747</v>
+        <v>3.2386</v>
       </c>
       <c r="C4" t="n">
-        <v>0.965</v>
+        <v>0.9261</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8855</v>
+        <v>0.8501</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3747</v>
+        <v>3.2386</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3747</v>
+        <v>3.2386</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.0505</v>
+        <v>4.3634</v>
       </c>
       <c r="I4" t="n">
-        <v>5.5916</v>
+        <v>5.3484</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.5916</v>
+        <v>5.3484</v>
       </c>
       <c r="N4" t="n">
         <v>257</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.3407</v>
+        <v>3.2061</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9553</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8701</v>
+        <v>0.8353</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3407</v>
+        <v>3.2061</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3407</v>
+        <v>3.2061</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9758</v>
+        <v>4.2923</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4885</v>
+        <v>5.2612</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4885</v>
+        <v>5.2612</v>
       </c>
       <c r="N5" t="n">
         <v>257</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.2637</v>
+        <v>3.0175</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9333</v>
+        <v>0.8629</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8354</v>
+        <v>0.7494</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2637</v>
+        <v>3.0175</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2637</v>
+        <v>3.0175</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8067</v>
+        <v>3.8794</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2959</v>
+        <v>4.1871</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2959</v>
+        <v>4.1871</v>
       </c>
       <c r="N6" t="n">
         <v>187</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.9982</v>
+        <v>2.7997</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8006</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7155</v>
+        <v>0.6503</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9982</v>
+        <v>2.7997</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9982</v>
+        <v>2.7997</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2239</v>
+        <v>3.4027</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6382</v>
+        <v>4.1708</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>187</v>
+        <v>405</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6382</v>
+        <v>4.1708</v>
       </c>
       <c r="N7" t="n">
-        <v>187</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9466</v>
+        <v>2.7401</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8426</v>
+        <v>0.7836</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6922</v>
+        <v>0.6231</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9466</v>
+        <v>2.7401</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9466</v>
+        <v>2.7401</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1105</v>
+        <v>3.2723</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2939</v>
+        <v>3.5318</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>405</v>
+        <v>187</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2939</v>
+        <v>3.5318</v>
       </c>
       <c r="N8" t="n">
-        <v>405</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9425</v>
+        <v>2.7296</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8414</v>
+        <v>0.7806</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6904</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9425</v>
+        <v>2.7296</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9425</v>
+        <v>2.7296</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1016</v>
+        <v>3.2494</v>
       </c>
       <c r="I9" t="n">
-        <v>4.1125</v>
+        <v>3.8828</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1125</v>
+        <v>3.8828</v>
       </c>
       <c r="N9" t="n">
         <v>347</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9061</v>
+        <v>2.6835</v>
       </c>
       <c r="C10" t="n">
-        <v>0.831</v>
+        <v>0.7674</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.5974</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9061</v>
+        <v>2.6835</v>
       </c>
       <c r="F10" t="n">
-        <v>2.9061</v>
+        <v>2.6835</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0215</v>
+        <v>3.1484</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6961</v>
+        <v>3.5755</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6961</v>
+        <v>3.5755</v>
       </c>
       <c r="N10" t="n">
         <v>252</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6938</v>
+        <v>2.5661</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7703</v>
+        <v>0.7338</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6938</v>
+        <v>2.5661</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6938</v>
+        <v>2.5661</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.6938</v>
+        <v>2.8914</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5718</v>
+        <v>3.4551</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5718</v>
+        <v>3.4551</v>
       </c>
       <c r="N11" t="n">
         <v>347</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6716</v>
+        <v>2.5289</v>
       </c>
       <c r="C12" t="n">
-        <v>0.764</v>
+        <v>0.7232</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5681</v>
+        <v>0.527</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6716</v>
+        <v>2.5289</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6716</v>
+        <v>2.5289</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6716</v>
+        <v>2.8101</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8959</v>
+        <v>3.4444</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>178</v>
+        <v>405</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8959</v>
+        <v>3.4444</v>
       </c>
       <c r="N12" t="n">
-        <v>178</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5805</v>
+        <v>2.4592</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7379</v>
+        <v>0.7032</v>
       </c>
       <c r="D13" t="n">
-        <v>0.527</v>
+        <v>0.4953</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5805</v>
+        <v>2.4592</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5805</v>
+        <v>2.4592</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5805</v>
+        <v>2.6576</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5623</v>
+        <v>2.7963</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>405</v>
+        <v>178</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5623</v>
+        <v>2.7963</v>
       </c>
       <c r="N13" t="n">
-        <v>405</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0473</v>
+        <v>2.2838</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5854</v>
+        <v>0.6531</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2862</v>
+        <v>0.4154</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0473</v>
+        <v>2.2838</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0473</v>
+        <v>2.2838</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0473</v>
+        <v>2.2838</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8262</v>
+        <v>2.7993</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8262</v>
+        <v>2.7993</v>
       </c>
       <c r="N14" t="n">
         <v>257</v>
@@ -1090,231 +1090,231 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6117</v>
+        <v>1.6448</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4609</v>
+        <v>0.4703</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0896</v>
+        <v>0.1245</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6117</v>
+        <v>1.6448</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6117</v>
+        <v>1.6448</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6117</v>
+        <v>1.6448</v>
       </c>
       <c r="I15" t="n">
-        <v>1.747</v>
+        <v>1.9655</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>178</v>
+        <v>347</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.747</v>
+        <v>1.9655</v>
       </c>
       <c r="N15" t="n">
-        <v>178</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>Ax1Le</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5998</v>
+        <v>1.5685</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4575</v>
+        <v>0.4485</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0842</v>
+        <v>0.0898</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5998</v>
+        <v>1.5685</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5998</v>
+        <v>1.5685</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5998</v>
+        <v>1.5685</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1212</v>
+        <v>1.9226</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>347</v>
+        <v>257</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1212</v>
+        <v>1.9226</v>
       </c>
       <c r="N16" t="n">
-        <v>347</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ax1Le</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4809</v>
+        <v>1.5473</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4235</v>
+        <v>0.4425</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0305</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4809</v>
+        <v>1.5473</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4809</v>
+        <v>1.5473</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4809</v>
+        <v>1.5473</v>
       </c>
       <c r="I17" t="n">
-        <v>2.0444</v>
+        <v>1.8966</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>257</v>
+        <v>405</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.0444</v>
+        <v>1.8966</v>
       </c>
       <c r="N17" t="n">
-        <v>257</v>
+        <v>405</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4588</v>
+        <v>1.5251</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4172</v>
+        <v>0.4361</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0206</v>
+        <v>0.0701</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4588</v>
+        <v>1.5251</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4588</v>
+        <v>1.5251</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4588</v>
+        <v>1.5251</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5813</v>
+        <v>1.6047</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.5813</v>
+        <v>1.6047</v>
       </c>
       <c r="N18" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4344</v>
+        <v>1.4739</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4102</v>
+        <v>0.4215</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0095</v>
+        <v>0.0467</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4344</v>
+        <v>1.4739</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4344</v>
+        <v>1.4739</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4344</v>
+        <v>1.4739</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9802</v>
+        <v>1.5508</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>405</v>
+        <v>160</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9802</v>
+        <v>1.5508</v>
       </c>
       <c r="N19" t="n">
-        <v>405</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.417</v>
+        <v>1.4025</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4052</v>
+        <v>0.4011</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0017</v>
+        <v>0.0142</v>
       </c>
       <c r="E20" t="n">
-        <v>1.417</v>
+        <v>1.4025</v>
       </c>
       <c r="F20" t="n">
-        <v>1.417</v>
+        <v>1.4025</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.417</v>
+        <v>1.4025</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7333</v>
+        <v>1.5928</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.7333</v>
+        <v>1.5928</v>
       </c>
       <c r="N20" t="n">
         <v>252</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2958</v>
+        <v>1.3242</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3705</v>
+        <v>0.3787</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.053</v>
+        <v>-0.0214</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2958</v>
+        <v>1.3242</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2958</v>
+        <v>1.3242</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2958</v>
+        <v>1.3242</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5851</v>
+        <v>1.5038</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5851</v>
+        <v>1.5038</v>
       </c>
       <c r="N21" t="n">
         <v>252</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.148</v>
+        <v>1.0986</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3283</v>
+        <v>0.3142</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1197</v>
+        <v>-0.1241</v>
       </c>
       <c r="E22" t="n">
-        <v>1.148</v>
+        <v>1.0986</v>
       </c>
       <c r="F22" t="n">
-        <v>1.148</v>
+        <v>1.0986</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.148</v>
+        <v>1.0986</v>
       </c>
       <c r="I22" t="n">
-        <v>1.148</v>
+        <v>1.0986</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.148</v>
+        <v>1.0986</v>
       </c>
       <c r="N22" t="n">
         <v>124</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9175</v>
+        <v>0.9557</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2624</v>
+        <v>0.2733</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2238</v>
+        <v>-0.1891</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9175</v>
+        <v>0.9557</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9175</v>
+        <v>0.9557</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9175</v>
+        <v>0.9557</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0354</v>
+        <v>1.0315</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0354</v>
+        <v>1.0315</v>
       </c>
       <c r="N23" t="n">
         <v>187</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8678</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2482</v>
+        <v>0.2377</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2462</v>
+        <v>-0.2459</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8678</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8678</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8678</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9406</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9406</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>178</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4866</v>
+        <v>0.4953</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1391</v>
+        <v>0.1416</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4183</v>
+        <v>-0.3987</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4866</v>
+        <v>0.4953</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4866</v>
+        <v>0.4953</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4866</v>
+        <v>0.4953</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5491</v>
+        <v>0.5346</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5491</v>
+        <v>0.5346</v>
       </c>
       <c r="N25" t="n">
         <v>187</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3643</v>
+        <v>0.3381</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1042</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4736</v>
+        <v>-0.4703</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3643</v>
+        <v>0.3381</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3643</v>
+        <v>0.3381</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3643</v>
+        <v>0.3381</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3643</v>
+        <v>0.3557</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3643</v>
+        <v>0.3557</v>
       </c>
       <c r="N26" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3497</v>
+        <v>0.3279</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4801</v>
+        <v>-0.4749</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3497</v>
+        <v>0.3279</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3497</v>
+        <v>0.3279</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3497</v>
+        <v>0.3279</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3791</v>
+        <v>0.3279</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3791</v>
+        <v>0.3279</v>
       </c>
       <c r="N27" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2005</v>
+        <v>0.136</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0573</v>
+        <v>0.0389</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5475</v>
+        <v>-0.5623</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2005</v>
+        <v>0.136</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2005</v>
+        <v>0.136</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2005</v>
+        <v>0.136</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2173</v>
+        <v>0.1431</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2173</v>
+        <v>0.1431</v>
       </c>
       <c r="N28" t="n">
         <v>160</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.032</v>
+        <v>-0.066</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0092</v>
+        <v>-0.0189</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6525</v>
+        <v>-0.6542</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.032</v>
+        <v>-0.066</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.032</v>
+        <v>-0.066</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.032</v>
+        <v>-0.066</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0392</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0392</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="N29" t="n">
         <v>252</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1917</v>
+        <v>-0.2317</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0548</v>
+        <v>-0.0663</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7246</v>
+        <v>-0.7297</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1917</v>
+        <v>-0.2317</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1917</v>
+        <v>-0.2317</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1917</v>
+        <v>-0.2317</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1917</v>
+        <v>-0.2317</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1917</v>
+        <v>-0.2317</v>
       </c>
       <c r="N30" t="n">
         <v>124</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2817</v>
+        <v>-0.3307</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0806</v>
+        <v>-0.0946</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7652</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2817</v>
+        <v>-0.3307</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2817</v>
+        <v>-0.3307</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2817</v>
+        <v>-0.3307</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3054</v>
+        <v>-0.348</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3054</v>
+        <v>-0.348</v>
       </c>
       <c r="N31" t="n">
         <v>160</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3816</v>
+        <v>-0.431</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1091</v>
+        <v>-0.1232</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8103</v>
+        <v>-0.8204</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3816</v>
+        <v>-0.431</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3816</v>
+        <v>-0.431</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3816</v>
+        <v>-0.431</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4136</v>
+        <v>-0.4535</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4136</v>
+        <v>-0.4535</v>
       </c>
       <c r="N32" t="n">
         <v>160</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4074</v>
+        <v>-0.4485</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1165</v>
+        <v>-0.1283</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8219</v>
+        <v>-0.8284</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4074</v>
+        <v>-0.4485</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4074</v>
+        <v>-0.4485</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4074</v>
+        <v>-0.4485</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4074</v>
+        <v>-0.4485</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4074</v>
+        <v>-0.4485</v>
       </c>
       <c r="N33" t="n">
         <v>124</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6197</v>
+        <v>-0.6559</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1772</v>
+        <v>-0.1876</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.9228</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6197</v>
+        <v>-0.6559</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6197</v>
+        <v>-0.6559</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6197</v>
+        <v>-0.6559</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6197</v>
+        <v>-0.6559</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6197</v>
+        <v>-0.6559</v>
       </c>
       <c r="N34" t="n">
         <v>124</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.884</v>
+        <v>-0.9877</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2528</v>
+        <v>-0.2824</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0371</v>
+        <v>-1.0738</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.884</v>
+        <v>-0.9877</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.884</v>
+        <v>-0.9877</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.884</v>
+        <v>-0.9877</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2203</v>
+        <v>-1.2107</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2203</v>
+        <v>-1.2107</v>
       </c>
       <c r="N35" t="n">
         <v>405</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2544</v>
+        <v>-1.2496</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3587</v>
+        <v>-0.3573</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2043</v>
+        <v>-1.193</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2544</v>
+        <v>-1.2496</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2544</v>
+        <v>-1.2496</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2544</v>
+        <v>-1.2496</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.7317</v>
+        <v>-1.5317</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.7317</v>
+        <v>-1.5317</v>
       </c>
       <c r="N36" t="n">
         <v>257</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3333</v>
+        <v>-1.3448</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3813</v>
+        <v>-0.3846</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2399</v>
+        <v>-1.2364</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3333</v>
+        <v>-1.3448</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3333</v>
+        <v>-1.3448</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3333</v>
+        <v>-1.3448</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.4452</v>
+        <v>-1.415</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.4452</v>
+        <v>-1.415</v>
       </c>
       <c r="N37" t="n">
         <v>178</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3613</v>
+        <v>-1.4275</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3893</v>
+        <v>-0.4082</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2526</v>
+        <v>-1.274</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3613</v>
+        <v>-1.4275</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3613</v>
+        <v>-1.4275</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3613</v>
+        <v>-1.4275</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5363</v>
+        <v>-1.5407</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5363</v>
+        <v>-1.5407</v>
       </c>
       <c r="N38" t="n">
         <v>187</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5304</v>
+        <v>-1.5826</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4376</v>
+        <v>-0.4526</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3289</v>
+        <v>-1.3446</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5304</v>
+        <v>-1.5826</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5304</v>
+        <v>-1.5826</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5304</v>
+        <v>-1.5826</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.8721</v>
+        <v>-1.7973</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.8721</v>
+        <v>-1.7973</v>
       </c>
       <c r="N39" t="n">
         <v>252</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9014</v>
+        <v>-1.9829</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5437</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4964</v>
+        <v>-1.5269</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9014</v>
+        <v>-1.9829</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9014</v>
+        <v>-1.9829</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9014</v>
+        <v>-1.9829</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.061</v>
+        <v>-2.0864</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.061</v>
+        <v>-2.0864</v>
       </c>
       <c r="N40" t="n">
         <v>178</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.1663</v>
+        <v>-3.3999</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9054</v>
+        <v>-0.9722</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0674</v>
+        <v>-2.1719</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.1663</v>
+        <v>-3.3999</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.1663</v>
+        <v>-3.3999</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.1663</v>
+        <v>-3.3999</v>
       </c>
       <c r="I41" t="n">
-        <v>-4.1984</v>
+        <v>-4.0627</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-4.1984</v>
+        <v>-4.0627</v>
       </c>
       <c r="N41" t="n">
         <v>347</v>
@@ -2429,10 +2429,10 @@
         <v>1.31</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.8229</v>
       </c>
       <c r="J2" t="n">
-        <v>24.8528</v>
+        <v>23.0412</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5603</v>
+        <v>0.5349</v>
       </c>
       <c r="J3" t="n">
-        <v>15.6884</v>
+        <v>14.9772</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3705</v>
+        <v>0.3634</v>
       </c>
       <c r="J4" t="n">
-        <v>10.374</v>
+        <v>10.1752</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3255</v>
+        <v>-0.3191</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.114000000000001</v>
+        <v>-8.934799999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1444</v>
+        <v>-1.0415</v>
       </c>
       <c r="J6" t="n">
-        <v>-32.0432</v>
+        <v>-29.162</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6076</v>
+        <v>0.5903</v>
       </c>
       <c r="J7" t="n">
-        <v>17.0128</v>
+        <v>16.5284</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4848</v>
+        <v>0.478</v>
       </c>
       <c r="J8" t="n">
-        <v>13.5744</v>
+        <v>13.384</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.1011</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5424</v>
+        <v>-2.8308</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.87</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1698</v>
+        <v>-0.1825</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.7544</v>
+        <v>-5.11</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.79</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.252</v>
+        <v>-0.2646</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.056</v>
+        <v>-7.4088</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2931</v>
+        <v>1.2682</v>
       </c>
       <c r="J12" t="n">
-        <v>34.9137</v>
+        <v>34.2414</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.32</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.7847</v>
       </c>
       <c r="J13" t="n">
-        <v>22.3317</v>
+        <v>21.1869</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.27</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7143</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>19.2861</v>
+        <v>18.495</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>0.036</v>
+        <v>0.0597</v>
       </c>
       <c r="J15" t="n">
-        <v>0.972</v>
+        <v>1.6119</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.99</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1149</v>
+        <v>-0.1014</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.1023</v>
+        <v>-2.7378</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5012</v>
+        <v>0.4797</v>
       </c>
       <c r="J17" t="n">
-        <v>13.5324</v>
+        <v>12.9519</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1302</v>
+        <v>-0.1467</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.5154</v>
+        <v>-3.9609</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.83</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1911</v>
+        <v>-0.2087</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.1597</v>
+        <v>-5.6349</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.7</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3175</v>
+        <v>-0.333</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.5725</v>
+        <v>-8.991</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.63</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3836</v>
+        <v>-0.3966</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.3572</v>
+        <v>-10.7082</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.34</v>
       </c>
       <c r="I22" t="n">
-        <v>0.903</v>
+        <v>0.8458</v>
       </c>
       <c r="J22" t="n">
-        <v>22.575</v>
+        <v>21.145</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.32</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8569</v>
+        <v>0.8054</v>
       </c>
       <c r="J23" t="n">
-        <v>21.4225</v>
+        <v>20.135</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.08</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2576</v>
+        <v>0.2655</v>
       </c>
       <c r="J24" t="n">
-        <v>6.44</v>
+        <v>6.6375</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.02</v>
       </c>
       <c r="I25" t="n">
-        <v>0.061</v>
+        <v>0.0771</v>
       </c>
       <c r="J25" t="n">
-        <v>1.525</v>
+        <v>1.9275</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.97</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1681</v>
+        <v>-0.1618</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.2025</v>
+        <v>-4.045</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7681</v>
+        <v>0.7287</v>
       </c>
       <c r="J27" t="n">
-        <v>19.2025</v>
+        <v>18.2175</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1315</v>
+        <v>0.1358</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2875</v>
+        <v>3.395</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2211</v>
+        <v>-0.2363</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.5275</v>
+        <v>-5.9075</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.77</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2608</v>
+        <v>-0.2756</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.52</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.68</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3474</v>
+        <v>-0.3599</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.685</v>
+        <v>-8.9975</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.52</v>
       </c>
       <c r="I32" t="n">
-        <v>0.732</v>
+        <v>0.7094</v>
       </c>
       <c r="J32" t="n">
-        <v>21.228</v>
+        <v>20.5726</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3897</v>
+        <v>0.3937</v>
       </c>
       <c r="J33" t="n">
-        <v>11.3013</v>
+        <v>11.4173</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.93</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1067</v>
+        <v>-0.1166</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.0943</v>
+        <v>-3.3814</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1298</v>
+        <v>-0.1407</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.7642</v>
+        <v>-4.0803</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3429</v>
+        <v>-0.3529</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.944100000000001</v>
+        <v>-10.2341</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.62</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7758</v>
       </c>
       <c r="J37" t="n">
-        <v>22.9912</v>
+        <v>22.4982</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.11</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1798</v>
+        <v>0.1945</v>
       </c>
       <c r="J38" t="n">
-        <v>5.2142</v>
+        <v>5.6405</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1081</v>
+        <v>0.1212</v>
       </c>
       <c r="J39" t="n">
-        <v>3.1349</v>
+        <v>3.5148</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1186</v>
+        <v>-0.129</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.4394</v>
+        <v>-3.741</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4264</v>
+        <v>-0.4335</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.3656</v>
+        <v>-12.5715</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.27</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7598</v>
+        <v>0.7165</v>
       </c>
       <c r="J42" t="n">
-        <v>22.0342</v>
+        <v>20.7785</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.23</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6302</v>
       </c>
       <c r="J43" t="n">
-        <v>19.1922</v>
+        <v>18.2758</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.19</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5616</v>
+        <v>0.541</v>
       </c>
       <c r="J44" t="n">
-        <v>16.2864</v>
+        <v>15.689</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.221</v>
+        <v>-0.2167</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.409</v>
+        <v>-6.2843</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6465</v>
+        <v>-0.6052</v>
       </c>
       <c r="J46" t="n">
-        <v>-18.7485</v>
+        <v>-17.5508</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8924</v>
+        <v>0.8438</v>
       </c>
       <c r="J47" t="n">
-        <v>25.8796</v>
+        <v>24.4702</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.2</v>
       </c>
       <c r="I48" t="n">
-        <v>0.442</v>
+        <v>0.4361</v>
       </c>
       <c r="J48" t="n">
-        <v>12.818</v>
+        <v>12.6469</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.96</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0623</v>
+        <v>-0.0718</v>
       </c>
       <c r="J49" t="n">
-        <v>-1.8067</v>
+        <v>-2.0822</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.72</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3161</v>
+        <v>-0.3283</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.1669</v>
+        <v>-9.5207</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.61</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.419</v>
+        <v>-0.4276</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.151</v>
+        <v>-12.4004</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.44</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8962</v>
+        <v>0.8418</v>
       </c>
       <c r="J52" t="n">
-        <v>24.1974</v>
+        <v>22.7286</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0153</v>
+        <v>0.0109</v>
       </c>
       <c r="J53" t="n">
-        <v>0.4131</v>
+        <v>0.2943</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.82</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2093</v>
+        <v>-0.2249</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.6511</v>
+        <v>-6.0723</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.68</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3457</v>
+        <v>-0.3586</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.3339</v>
+        <v>-9.6822</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.66</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3646</v>
+        <v>-0.3767</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.844200000000001</v>
+        <v>-10.1709</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.44</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0802</v>
+        <v>1.033</v>
       </c>
       <c r="J57" t="n">
-        <v>29.1654</v>
+        <v>27.891</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5486</v>
+        <v>0.532</v>
       </c>
       <c r="J58" t="n">
-        <v>14.8122</v>
+        <v>14.364</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.15</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4481</v>
+        <v>0.441</v>
       </c>
       <c r="J59" t="n">
-        <v>12.0987</v>
+        <v>11.907</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.02</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0641</v>
+        <v>0.0793</v>
       </c>
       <c r="J60" t="n">
-        <v>1.7307</v>
+        <v>2.1411</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4715</v>
+        <v>-0.4458</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.7305</v>
+        <v>-12.0366</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.48</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6135</v>
+        <v>0.6137</v>
       </c>
       <c r="J62" t="n">
-        <v>17.7915</v>
+        <v>17.7973</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2369</v>
+        <v>0.2537</v>
       </c>
       <c r="J63" t="n">
-        <v>6.8701</v>
+        <v>7.3573</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.12</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1857</v>
+        <v>0.2025</v>
       </c>
       <c r="J64" t="n">
-        <v>5.3853</v>
+        <v>5.8725</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.12</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1857</v>
+        <v>0.2025</v>
       </c>
       <c r="J65" t="n">
-        <v>5.3853</v>
+        <v>5.8725</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2038</v>
+        <v>-0.2138</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.9102</v>
+        <v>-6.2002</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.16</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2867</v>
+        <v>0.2913</v>
       </c>
       <c r="J67" t="n">
-        <v>8.314299999999999</v>
+        <v>8.447699999999999</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.01</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0333</v>
+        <v>0.0372</v>
       </c>
       <c r="J68" t="n">
-        <v>0.9657</v>
+        <v>1.0788</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0604</v>
+        <v>-0.0703</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.7516</v>
+        <v>-2.0387</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.09660000000000001</v>
+        <v>-0.1089</v>
       </c>
       <c r="J70" t="n">
-        <v>-2.8014</v>
+        <v>-3.1581</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2647</v>
+        <v>-0.2786</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.6763</v>
+        <v>-8.0794</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.2</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4433</v>
+        <v>0.4371</v>
       </c>
       <c r="J72" t="n">
-        <v>15.9588</v>
+        <v>15.7356</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.07</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1868</v>
+        <v>0.1939</v>
       </c>
       <c r="J73" t="n">
-        <v>6.7248</v>
+        <v>6.9804</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0016</v>
+        <v>0.0011</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0576</v>
+        <v>0.0396</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.92</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1102</v>
+        <v>-0.1225</v>
       </c>
       <c r="J75" t="n">
-        <v>-3.9672</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.74</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2964</v>
+        <v>-0.3091</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.6704</v>
+        <v>-11.1276</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.33</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9082</v>
+        <v>0.8456</v>
       </c>
       <c r="J77" t="n">
-        <v>32.6952</v>
+        <v>30.4416</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.16</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4882</v>
+        <v>0.4742</v>
       </c>
       <c r="J78" t="n">
-        <v>17.5752</v>
+        <v>17.0712</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.15</v>
       </c>
       <c r="I79" t="n">
-        <v>0.462</v>
+        <v>0.4505</v>
       </c>
       <c r="J79" t="n">
-        <v>16.632</v>
+        <v>16.218</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2177</v>
+        <v>-0.2144</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.8372</v>
+        <v>-7.7184</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.79</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6691</v>
+        <v>-0.6258</v>
       </c>
       <c r="J81" t="n">
-        <v>-24.0876</v>
+        <v>-22.5288</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6508</v>
+        <v>0.613</v>
       </c>
       <c r="J82" t="n">
-        <v>19.524</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3805</v>
+        <v>0.3703</v>
       </c>
       <c r="J83" t="n">
-        <v>11.415</v>
+        <v>11.109</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.02</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0954</v>
+        <v>0.1007</v>
       </c>
       <c r="J84" t="n">
-        <v>2.862</v>
+        <v>3.021</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.9</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3466</v>
+        <v>-0.3404</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.398</v>
+        <v>-10.212</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.8219</v>
+        <v>-0.7644</v>
       </c>
       <c r="J86" t="n">
-        <v>-24.657</v>
+        <v>-22.932</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.33</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6635</v>
+        <v>0.6403</v>
       </c>
       <c r="J87" t="n">
-        <v>19.905</v>
+        <v>19.209</v>
       </c>
     </row>
     <row r="88">
@@ -5909,10 +5909,10 @@
         <v>0.99</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.0216</v>
+        <v>-0.026</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.648</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1791</v>
+        <v>-0.1922</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.373</v>
+        <v>-5.766</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.72</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3188</v>
+        <v>-0.3304</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.564</v>
+        <v>-9.912000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3497</v>
+        <v>0.3417</v>
       </c>
       <c r="J92" t="n">
-        <v>8.043100000000001</v>
+        <v>7.8591</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2707</v>
+        <v>0.2665</v>
       </c>
       <c r="J93" t="n">
-        <v>6.2261</v>
+        <v>6.1295</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.63</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3798</v>
+        <v>-0.3936</v>
       </c>
       <c r="J94" t="n">
-        <v>-8.7354</v>
+        <v>-9.0528</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.61</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3985</v>
+        <v>-0.4115</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.1655</v>
+        <v>-9.464499999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.58</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4264</v>
+        <v>-0.4381</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.8072</v>
+        <v>-10.0763</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.78</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8929</v>
+        <v>0.8776</v>
       </c>
       <c r="J97" t="n">
-        <v>20.5367</v>
+        <v>20.1848</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.5</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6034</v>
+        <v>0.6097</v>
       </c>
       <c r="J98" t="n">
-        <v>13.8782</v>
+        <v>14.0231</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.27</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3544</v>
+        <v>0.3723</v>
       </c>
       <c r="J99" t="n">
-        <v>8.151199999999999</v>
+        <v>8.562900000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.05</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0631</v>
+        <v>0.0827</v>
       </c>
       <c r="J100" t="n">
-        <v>1.4513</v>
+        <v>1.9021</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.96</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0963</v>
       </c>
       <c r="J101" t="n">
-        <v>-2.1574</v>
+        <v>-2.2149</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.79</v>
       </c>
       <c r="I102" t="n">
-        <v>1.483</v>
+        <v>1.4696</v>
       </c>
       <c r="J102" t="n">
-        <v>34.109</v>
+        <v>33.8008</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.4</v>
       </c>
       <c r="I103" t="n">
-        <v>0.99</v>
+        <v>0.9357</v>
       </c>
       <c r="J103" t="n">
-        <v>22.77</v>
+        <v>21.5211</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.24</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6445</v>
+        <v>0.6231</v>
       </c>
       <c r="J104" t="n">
-        <v>14.8235</v>
+        <v>14.3313</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.18</v>
       </c>
       <c r="I105" t="n">
-        <v>0.5001</v>
+        <v>0.4935</v>
       </c>
       <c r="J105" t="n">
-        <v>11.5023</v>
+        <v>11.3505</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.7</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9376</v>
+        <v>-0.8542</v>
       </c>
       <c r="J106" t="n">
-        <v>-21.5648</v>
+        <v>-19.6466</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3325</v>
+        <v>0.3201</v>
       </c>
       <c r="J107" t="n">
-        <v>7.6475</v>
+        <v>7.3623</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.8</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2175</v>
+        <v>-0.2357</v>
       </c>
       <c r="J108" t="n">
-        <v>-5.0025</v>
+        <v>-5.4211</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.75</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2658</v>
+        <v>-0.2834</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.1134</v>
+        <v>-6.5182</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.73</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.285</v>
+        <v>-0.3021</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.555</v>
+        <v>-6.9483</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.72</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2946</v>
+        <v>-0.3115</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.7758</v>
+        <v>-7.1645</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.26</v>
       </c>
       <c r="I112" t="n">
-        <v>0.434</v>
+        <v>0.4295</v>
       </c>
       <c r="J112" t="n">
-        <v>11.718</v>
+        <v>11.5965</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.97</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0462</v>
+        <v>-0.0553</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.2474</v>
+        <v>-1.4931</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0716</v>
+        <v>-0.0828</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.9332</v>
+        <v>-2.2356</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.84</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1922</v>
+        <v>-0.2071</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.1894</v>
+        <v>-5.5917</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.72</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3111</v>
+        <v>-0.3244</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.399699999999999</v>
+        <v>-8.758800000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.6</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7294</v>
+        <v>0.7237</v>
       </c>
       <c r="J117" t="n">
-        <v>19.6938</v>
+        <v>19.5399</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.4</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5112</v>
+        <v>0.52</v>
       </c>
       <c r="J118" t="n">
-        <v>13.8024</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.15</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2188</v>
+        <v>0.2371</v>
       </c>
       <c r="J119" t="n">
-        <v>5.9076</v>
+        <v>6.4017</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.99</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0408</v>
+        <v>-0.0409</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.1016</v>
+        <v>-1.1043</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.91</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.145</v>
+        <v>-0.1525</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.915</v>
+        <v>-4.1175</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.81</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5344</v>
+        <v>1.5192</v>
       </c>
       <c r="J122" t="n">
-        <v>38.36</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.24</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6586</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="J123" t="n">
-        <v>16.465</v>
+        <v>15.815</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3072</v>
+        <v>0.3134</v>
       </c>
       <c r="J124" t="n">
-        <v>7.68</v>
+        <v>7.835</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.189</v>
+        <v>0.2031</v>
       </c>
       <c r="J125" t="n">
-        <v>4.725</v>
+        <v>5.0775</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.9443</v>
+        <v>-0.8629</v>
       </c>
       <c r="J126" t="n">
-        <v>-23.6075</v>
+        <v>-21.5725</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7559</v>
+        <v>0.717</v>
       </c>
       <c r="J127" t="n">
-        <v>18.8975</v>
+        <v>17.925</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1815</v>
+        <v>0.1845</v>
       </c>
       <c r="J128" t="n">
-        <v>4.5375</v>
+        <v>4.6125</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.87</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1582</v>
+        <v>-0.1735</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.955</v>
+        <v>-4.3375</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.67</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3556</v>
+        <v>-0.3681</v>
       </c>
       <c r="J130" t="n">
-        <v>-8.890000000000001</v>
+        <v>-9.202500000000001</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.66</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.365</v>
+        <v>-0.3771</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.125</v>
+        <v>-9.4275</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.34</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9067</v>
+        <v>0.8484</v>
       </c>
       <c r="J132" t="n">
-        <v>24.4809</v>
+        <v>22.9068</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6463</v>
+        <v>0.6194</v>
       </c>
       <c r="J133" t="n">
-        <v>17.4501</v>
+        <v>16.7238</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3169</v>
+        <v>0.3201</v>
       </c>
       <c r="J134" t="n">
-        <v>8.5563</v>
+        <v>8.6427</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.04</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1351</v>
+        <v>0.1489</v>
       </c>
       <c r="J135" t="n">
-        <v>3.6477</v>
+        <v>4.0203</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1655</v>
+        <v>-0.16</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.4685</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.15</v>
       </c>
       <c r="I137" t="n">
-        <v>0.36</v>
+        <v>0.3572</v>
       </c>
       <c r="J137" t="n">
-        <v>9.720000000000001</v>
+        <v>9.644399999999999</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2597</v>
+        <v>0.2621</v>
       </c>
       <c r="J138" t="n">
-        <v>7.0119</v>
+        <v>7.0767</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1267</v>
+        <v>0.1323</v>
       </c>
       <c r="J139" t="n">
-        <v>3.4209</v>
+        <v>3.5721</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.01</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0465</v>
+        <v>0.0496</v>
       </c>
       <c r="J140" t="n">
-        <v>1.2555</v>
+        <v>1.3392</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.46</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5506</v>
+        <v>-0.553</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.8662</v>
+        <v>-14.931</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.36</v>
       </c>
       <c r="I142" t="n">
-        <v>0.9333</v>
+        <v>0.8757</v>
       </c>
       <c r="J142" t="n">
-        <v>24.2658</v>
+        <v>22.7682</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.8206</v>
+        <v>0.776</v>
       </c>
       <c r="J143" t="n">
-        <v>21.3356</v>
+        <v>20.176</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.22</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6097</v>
+        <v>0.5893</v>
       </c>
       <c r="J144" t="n">
-        <v>15.8522</v>
+        <v>15.3218</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4902</v>
+        <v>0.4813</v>
       </c>
       <c r="J145" t="n">
-        <v>12.7452</v>
+        <v>12.5138</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.87</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4849</v>
+        <v>-0.4553</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.6074</v>
+        <v>-11.8378</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.2</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4768</v>
+        <v>0.4617</v>
       </c>
       <c r="J147" t="n">
-        <v>12.3968</v>
+        <v>12.0042</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1165</v>
+        <v>0.1178</v>
       </c>
       <c r="J148" t="n">
-        <v>3.029</v>
+        <v>3.0628</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.02</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0896</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="J149" t="n">
-        <v>2.3296</v>
+        <v>2.3504</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.77</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2565</v>
+        <v>-0.2722</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.669</v>
+        <v>-7.0772</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.48</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5275</v>
+        <v>-0.5321</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.715</v>
+        <v>-13.8346</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.61</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3136</v>
+        <v>1.2821</v>
       </c>
       <c r="J152" t="n">
-        <v>36.7808</v>
+        <v>35.8988</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.24</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6829</v>
+        <v>0.6495</v>
       </c>
       <c r="J153" t="n">
-        <v>19.1212</v>
+        <v>18.186</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.14</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4298</v>
+        <v>0.4226</v>
       </c>
       <c r="J154" t="n">
-        <v>12.0344</v>
+        <v>11.8328</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.75</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7197</v>
       </c>
       <c r="J155" t="n">
-        <v>-21.7476</v>
+        <v>-20.1516</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.7197</v>
       </c>
       <c r="J156" t="n">
-        <v>-21.7476</v>
+        <v>-20.1516</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6354</v>
       </c>
       <c r="J157" t="n">
-        <v>18.5024</v>
+        <v>17.7912</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.02</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0699</v>
+        <v>0.0762</v>
       </c>
       <c r="J158" t="n">
-        <v>1.9572</v>
+        <v>2.1336</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.96</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0613</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.7164</v>
+        <v>-1.988</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.85</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1854</v>
+        <v>-0.1995</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.1912</v>
+        <v>-5.586</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.74</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2954</v>
+        <v>-0.3084</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.2712</v>
+        <v>-8.635199999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.84</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.1586</v>
+        <v>-0.1812</v>
       </c>
       <c r="J162" t="n">
-        <v>-2.8548</v>
+        <v>-3.2616</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.79</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2118</v>
+        <v>-0.2336</v>
       </c>
       <c r="J163" t="n">
-        <v>-3.8124</v>
+        <v>-4.2048</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.75</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2518</v>
+        <v>-0.2728</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.5324</v>
+        <v>-4.9104</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.61</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3809</v>
+        <v>-0.3977</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.8562</v>
+        <v>-7.1586</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.54</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4463</v>
+        <v>-0.4597</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.0334</v>
+        <v>-8.2746</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.88</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5337</v>
+        <v>1.5318</v>
       </c>
       <c r="J167" t="n">
-        <v>27.6066</v>
+        <v>27.5724</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.51</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1072</v>
+        <v>1.0767</v>
       </c>
       <c r="J168" t="n">
-        <v>19.9296</v>
+        <v>19.3806</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.5</v>
       </c>
       <c r="I169" t="n">
-        <v>1.0955</v>
+        <v>1.0637</v>
       </c>
       <c r="J169" t="n">
-        <v>19.719</v>
+        <v>19.1466</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.44</v>
       </c>
       <c r="I170" t="n">
-        <v>1.0219</v>
+        <v>0.9776</v>
       </c>
       <c r="J170" t="n">
-        <v>18.3942</v>
+        <v>17.5968</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1216</v>
+        <v>0.1559</v>
       </c>
       <c r="J171" t="n">
-        <v>2.1888</v>
+        <v>2.8062</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.28</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5729</v>
+        <v>0.5588</v>
       </c>
       <c r="J172" t="n">
-        <v>17.187</v>
+        <v>16.764</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.12</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2801</v>
+        <v>0.2862</v>
       </c>
       <c r="J173" t="n">
-        <v>8.403</v>
+        <v>8.586</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.04</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1118</v>
+        <v>0.1215</v>
       </c>
       <c r="J174" t="n">
-        <v>3.354</v>
+        <v>3.645</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0658</v>
+        <v>-0.0745</v>
       </c>
       <c r="J175" t="n">
-        <v>-1.974</v>
+        <v>-2.235</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3105</v>
+        <v>-0.3221</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.315</v>
+        <v>-9.663</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.23</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6796</v>
+        <v>0.6425</v>
       </c>
       <c r="J177" t="n">
-        <v>20.388</v>
+        <v>19.275</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.14</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4459</v>
+        <v>0.4337</v>
       </c>
       <c r="J178" t="n">
-        <v>13.377</v>
+        <v>13.011</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.08</v>
       </c>
       <c r="I179" t="n">
-        <v>0.278</v>
+        <v>0.2793</v>
       </c>
       <c r="J179" t="n">
-        <v>8.34</v>
+        <v>8.379</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2183</v>
+        <v>0.2231</v>
       </c>
       <c r="J180" t="n">
-        <v>6.549</v>
+        <v>6.693</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.7</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8857</v>
+        <v>-0.8175</v>
       </c>
       <c r="J181" t="n">
-        <v>-26.571</v>
+        <v>-24.525</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9554</v>
+        <v>0.9003</v>
       </c>
       <c r="J182" t="n">
-        <v>26.7512</v>
+        <v>25.2084</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.28</v>
       </c>
       <c r="I183" t="n">
-        <v>0.7358</v>
+        <v>0.7044</v>
       </c>
       <c r="J183" t="n">
-        <v>20.6024</v>
+        <v>19.7232</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.623</v>
+        <v>0.6035</v>
       </c>
       <c r="J184" t="n">
-        <v>17.444</v>
+        <v>16.898</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5515</v>
+        <v>0.5394</v>
       </c>
       <c r="J185" t="n">
-        <v>15.442</v>
+        <v>15.1032</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.17</v>
       </c>
       <c r="I186" t="n">
-        <v>0.4771</v>
+        <v>0.4723</v>
       </c>
       <c r="J186" t="n">
-        <v>13.3588</v>
+        <v>13.2244</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.04</v>
       </c>
       <c r="I187" t="n">
-        <v>0.1696</v>
+        <v>0.1636</v>
       </c>
       <c r="J187" t="n">
-        <v>4.7488</v>
+        <v>4.5808</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.91</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1042</v>
+        <v>-0.121</v>
       </c>
       <c r="J188" t="n">
-        <v>-2.9176</v>
+        <v>-3.388</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.9</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1157</v>
+        <v>-0.1327</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.2396</v>
+        <v>-3.7156</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.65</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3615</v>
+        <v>-0.376</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.122</v>
+        <v>-10.528</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3803</v>
+        <v>-0.394</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.6484</v>
+        <v>-11.032</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.24</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7117</v>
+        <v>0.6696</v>
       </c>
       <c r="J192" t="n">
-        <v>20.6393</v>
+        <v>19.4184</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5579</v>
+        <v>0.5333</v>
       </c>
       <c r="J193" t="n">
-        <v>16.1791</v>
+        <v>15.4657</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.16</v>
       </c>
       <c r="I194" t="n">
-        <v>0.5051</v>
+        <v>0.486</v>
       </c>
       <c r="J194" t="n">
-        <v>14.6479</v>
+        <v>14.094</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3563</v>
+        <v>-0.3472</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.3327</v>
+        <v>-10.0688</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.65</v>
       </c>
       <c r="I196" t="n">
-        <v>-1.0029</v>
+        <v>-0.9197</v>
       </c>
       <c r="J196" t="n">
-        <v>-29.0841</v>
+        <v>-26.6713</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.45</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8646</v>
+        <v>0.8208</v>
       </c>
       <c r="J197" t="n">
-        <v>25.0734</v>
+        <v>23.8032</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.1</v>
       </c>
       <c r="I198" t="n">
-        <v>0.243</v>
+        <v>0.25</v>
       </c>
       <c r="J198" t="n">
-        <v>7.047</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.06</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1589</v>
+        <v>0.1681</v>
       </c>
       <c r="J199" t="n">
-        <v>4.6081</v>
+        <v>4.8749</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.8</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2406</v>
+        <v>-0.2537</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.9774</v>
+        <v>-7.3573</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3754</v>
+        <v>-0.3852</v>
       </c>
       <c r="J201" t="n">
-        <v>-10.8866</v>
+        <v>-11.1708</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.31</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8329</v>
+        <v>0.7845</v>
       </c>
       <c r="J202" t="n">
-        <v>21.6554</v>
+        <v>20.397</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.16</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4708</v>
+        <v>0.4623</v>
       </c>
       <c r="J203" t="n">
-        <v>12.2408</v>
+        <v>12.0198</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2861</v>
+        <v>0.2922</v>
       </c>
       <c r="J204" t="n">
-        <v>7.4386</v>
+        <v>7.5972</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.09</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2861</v>
+        <v>0.2922</v>
       </c>
       <c r="J205" t="n">
-        <v>7.4386</v>
+        <v>7.5972</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.09</v>
       </c>
       <c r="I206" t="n">
-        <v>0.2861</v>
+        <v>0.2922</v>
       </c>
       <c r="J206" t="n">
-        <v>7.4386</v>
+        <v>7.5972</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.24</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5609</v>
+        <v>0.5373</v>
       </c>
       <c r="J207" t="n">
-        <v>14.5834</v>
+        <v>13.9698</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.11</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3053</v>
+        <v>0.3002</v>
       </c>
       <c r="J208" t="n">
-        <v>7.9378</v>
+        <v>7.8052</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1539</v>
+        <v>-0.1703</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.0014</v>
+        <v>-4.4278</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.7</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3218</v>
+        <v>-0.3364</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.3668</v>
+        <v>-8.7464</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.49</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5165</v>
+        <v>-0.522</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.429</v>
+        <v>-13.572</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.16</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2799</v>
+        <v>0.2862</v>
       </c>
       <c r="J212" t="n">
-        <v>7.8372</v>
+        <v>8.0136</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2052</v>
+        <v>0.2138</v>
       </c>
       <c r="J213" t="n">
-        <v>5.7456</v>
+        <v>5.9864</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0856</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.1084</v>
+        <v>-2.3968</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.95</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0856</v>
       </c>
       <c r="J215" t="n">
-        <v>-2.1084</v>
+        <v>-2.3968</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2383</v>
+        <v>-0.2519</v>
       </c>
       <c r="J216" t="n">
-        <v>-6.6724</v>
+        <v>-7.0532</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.27</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3748</v>
+        <v>0.3875</v>
       </c>
       <c r="J217" t="n">
-        <v>10.4944</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.26</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3627</v>
+        <v>0.3759</v>
       </c>
       <c r="J218" t="n">
-        <v>10.1556</v>
+        <v>10.5252</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.21</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3016</v>
+        <v>0.3168</v>
       </c>
       <c r="J219" t="n">
-        <v>8.444800000000001</v>
+        <v>8.8704</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0116</v>
+        <v>-0.0089</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.3248</v>
+        <v>-0.2492</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.9</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1481</v>
+        <v>-0.1577</v>
       </c>
       <c r="J221" t="n">
-        <v>-4.1468</v>
+        <v>-4.4156</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.95</v>
       </c>
       <c r="I222" t="n">
-        <v>1.6178</v>
+        <v>1.6192</v>
       </c>
       <c r="J222" t="n">
-        <v>33.9738</v>
+        <v>34.0032</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.72</v>
       </c>
       <c r="I223" t="n">
-        <v>1.3556</v>
+        <v>1.3428</v>
       </c>
       <c r="J223" t="n">
-        <v>28.4676</v>
+        <v>28.1988</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.4</v>
       </c>
       <c r="I224" t="n">
-        <v>0.9595</v>
+        <v>0.9114</v>
       </c>
       <c r="J224" t="n">
-        <v>20.1495</v>
+        <v>19.1394</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.12</v>
       </c>
       <c r="I225" t="n">
-        <v>0.301</v>
+        <v>0.3216</v>
       </c>
       <c r="J225" t="n">
-        <v>6.321</v>
+        <v>6.7536</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.08</v>
       </c>
       <c r="I226" t="n">
-        <v>0.1873</v>
+        <v>0.2165</v>
       </c>
       <c r="J226" t="n">
-        <v>3.9333</v>
+        <v>4.5465</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.91</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.0796</v>
+        <v>-0.1018</v>
       </c>
       <c r="J227" t="n">
-        <v>-1.6716</v>
+        <v>-2.1378</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.84</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1605</v>
+        <v>-0.1827</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.3705</v>
+        <v>-3.8367</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.72</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2811</v>
+        <v>-0.3012</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.9031</v>
+        <v>-6.3252</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.6</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3915</v>
+        <v>-0.4076</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.221500000000001</v>
+        <v>-8.5596</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.5</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.485</v>
+        <v>-0.4958</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.185</v>
+        <v>-10.4118</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.44</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8344</v>
+        <v>0.796</v>
       </c>
       <c r="J232" t="n">
-        <v>22.5288</v>
+        <v>21.492</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.27</v>
       </c>
       <c r="I233" t="n">
-        <v>0.549</v>
+        <v>0.5381</v>
       </c>
       <c r="J233" t="n">
-        <v>14.823</v>
+        <v>14.5287</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1166</v>
+        <v>-0.1275</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.1482</v>
+        <v>-3.4425</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1504</v>
+        <v>-0.1622</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.0608</v>
+        <v>-4.3794</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.71</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3318</v>
+        <v>-0.3424</v>
       </c>
       <c r="J236" t="n">
-        <v>-8.958600000000001</v>
+        <v>-9.2448</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.56</v>
       </c>
       <c r="I237" t="n">
-        <v>1.2255</v>
+        <v>1.1928</v>
       </c>
       <c r="J237" t="n">
-        <v>33.0885</v>
+        <v>32.2056</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.41</v>
       </c>
       <c r="I238" t="n">
-        <v>1.0286</v>
+        <v>0.9735</v>
       </c>
       <c r="J238" t="n">
-        <v>27.7722</v>
+        <v>26.2845</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.26</v>
       </c>
       <c r="I239" t="n">
-        <v>0.708</v>
+        <v>0.6761</v>
       </c>
       <c r="J239" t="n">
-        <v>19.116</v>
+        <v>18.2547</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.82</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.6162</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="J240" t="n">
-        <v>-16.6374</v>
+        <v>-15.5007</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.6424</v>
+        <v>-0.5975</v>
       </c>
       <c r="J241" t="n">
-        <v>-17.3448</v>
+        <v>-16.1325</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.16</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3512</v>
+        <v>0.3547</v>
       </c>
       <c r="J242" t="n">
-        <v>9.833600000000001</v>
+        <v>9.9316</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.14</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3136</v>
+        <v>0.3192</v>
       </c>
       <c r="J243" t="n">
-        <v>8.780799999999999</v>
+        <v>8.9376</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.01</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0315</v>
+        <v>0.039</v>
       </c>
       <c r="J244" t="n">
-        <v>0.882</v>
+        <v>1.092</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.01</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0315</v>
+        <v>0.039</v>
       </c>
       <c r="J245" t="n">
-        <v>0.882</v>
+        <v>1.092</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.92</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1169</v>
+        <v>-0.1276</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.2732</v>
+        <v>-3.5728</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.52</v>
       </c>
       <c r="I247" t="n">
-        <v>1.2032</v>
+        <v>1.1637</v>
       </c>
       <c r="J247" t="n">
-        <v>33.6896</v>
+        <v>32.5836</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.03</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1148</v>
+        <v>0.1251</v>
       </c>
       <c r="J248" t="n">
-        <v>3.2144</v>
+        <v>3.5028</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0173</v>
+        <v>-0.0118</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.4844</v>
+        <v>-0.3304</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.99</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J250" t="n">
-        <v>-2.016</v>
+        <v>-1.9992</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5111</v>
+        <v>-0.4847</v>
       </c>
       <c r="J251" t="n">
-        <v>-14.3108</v>
+        <v>-13.5716</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.0622</v>
+        <v>-0.079</v>
       </c>
       <c r="J252" t="n">
-        <v>-1.555</v>
+        <v>-1.975</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.91</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.0988</v>
+        <v>-0.1168</v>
       </c>
       <c r="J253" t="n">
-        <v>-2.47</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.79</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2245</v>
+        <v>-0.2433</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.6125</v>
+        <v>-6.0825</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.75</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2624</v>
+        <v>-0.2808</v>
       </c>
       <c r="J255" t="n">
-        <v>-6.56</v>
+        <v>-7.02</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.59</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4135</v>
+        <v>-0.4263</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.3375</v>
+        <v>-10.6575</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.63</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7492</v>
+        <v>0.7438</v>
       </c>
       <c r="J257" t="n">
-        <v>18.73</v>
+        <v>18.595</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.35</v>
       </c>
       <c r="I258" t="n">
-        <v>0.4474</v>
+        <v>0.461</v>
       </c>
       <c r="J258" t="n">
-        <v>11.185</v>
+        <v>11.525</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2638</v>
+        <v>0.2829</v>
       </c>
       <c r="J259" t="n">
-        <v>6.595</v>
+        <v>7.0725</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.11</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1587</v>
+        <v>0.1787</v>
       </c>
       <c r="J260" t="n">
-        <v>3.9675</v>
+        <v>4.4675</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.04</v>
       </c>
       <c r="I261" t="n">
-        <v>0.0521</v>
+        <v>0.0696</v>
       </c>
       <c r="J261" t="n">
-        <v>1.3025</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.25</v>
       </c>
       <c r="I262" t="n">
-        <v>0.722</v>
+        <v>0.6813</v>
       </c>
       <c r="J262" t="n">
-        <v>21.66</v>
+        <v>20.439</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.17</v>
       </c>
       <c r="I263" t="n">
-        <v>0.5194</v>
+        <v>0.5012</v>
       </c>
       <c r="J263" t="n">
-        <v>15.582</v>
+        <v>15.036</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.08</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2739</v>
+        <v>0.2765</v>
       </c>
       <c r="J264" t="n">
-        <v>8.217000000000001</v>
+        <v>8.295</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.96</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1801</v>
+        <v>-0.1796</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.403</v>
+        <v>-5.388</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.84</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.533</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="J266" t="n">
-        <v>-15.99</v>
+        <v>-15.165</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.48</v>
       </c>
       <c r="I267" t="n">
-        <v>0.9412</v>
+        <v>0.8864</v>
       </c>
       <c r="J267" t="n">
-        <v>28.236</v>
+        <v>26.592</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.16</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3781</v>
+        <v>0.3744</v>
       </c>
       <c r="J268" t="n">
-        <v>11.343</v>
+        <v>11.232</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.75</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2831</v>
+        <v>-0.2969</v>
       </c>
       <c r="J269" t="n">
-        <v>-8.493</v>
+        <v>-8.907</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.73</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3024</v>
+        <v>-0.3158</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.071999999999999</v>
+        <v>-9.474</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.66</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3689</v>
+        <v>-0.3801</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.067</v>
+        <v>-11.403</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.57</v>
       </c>
       <c r="I272" t="n">
-        <v>1.255</v>
+        <v>1.2212</v>
       </c>
       <c r="J272" t="n">
-        <v>37.65</v>
+        <v>36.636</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.23</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6518</v>
+        <v>0.6232</v>
       </c>
       <c r="J273" t="n">
-        <v>19.554</v>
+        <v>18.696</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.1</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3204</v>
+        <v>0.3225</v>
       </c>
       <c r="J274" t="n">
-        <v>9.612</v>
+        <v>9.675000000000001</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.87</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4672</v>
+        <v>-0.4428</v>
       </c>
       <c r="J275" t="n">
-        <v>-14.016</v>
+        <v>-13.284</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.5643</v>
       </c>
       <c r="J276" t="n">
-        <v>-18.069</v>
+        <v>-16.929</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.22</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4965</v>
+        <v>0.4832</v>
       </c>
       <c r="J277" t="n">
-        <v>14.895</v>
+        <v>14.496</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.11</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2835</v>
+        <v>0.2841</v>
       </c>
       <c r="J278" t="n">
-        <v>8.505000000000001</v>
+        <v>8.523</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.86</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1707</v>
+        <v>-0.1857</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.121</v>
+        <v>-5.571</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.8</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2321</v>
+        <v>-0.247</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.963</v>
+        <v>-7.41</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.72</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3103</v>
+        <v>-0.3238</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.308999999999999</v>
+        <v>-9.714</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.14</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3723</v>
+        <v>0.3622</v>
       </c>
       <c r="J282" t="n">
-        <v>10.0521</v>
+        <v>9.779400000000001</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.08</v>
       </c>
       <c r="I283" t="n">
-        <v>0.2455</v>
+        <v>0.242</v>
       </c>
       <c r="J283" t="n">
-        <v>6.6285</v>
+        <v>6.534</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.86</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1631</v>
+        <v>-0.1798</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.4037</v>
+        <v>-4.8546</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.68</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3392</v>
+        <v>-0.3535</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.1584</v>
+        <v>-9.544499999999999</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.59</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4235</v>
+        <v>-0.4342</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.4345</v>
+        <v>-11.7234</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.65</v>
       </c>
       <c r="I287" t="n">
-        <v>1.3188</v>
+        <v>1.2953</v>
       </c>
       <c r="J287" t="n">
-        <v>35.6076</v>
+        <v>34.9731</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.48</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1064</v>
+        <v>1.0681</v>
       </c>
       <c r="J288" t="n">
-        <v>29.8728</v>
+        <v>28.8387</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.27</v>
       </c>
       <c r="I289" t="n">
-        <v>0.715</v>
+        <v>0.6855</v>
       </c>
       <c r="J289" t="n">
-        <v>19.305</v>
+        <v>18.5085</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.01</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0041</v>
+        <v>0.019</v>
       </c>
       <c r="J290" t="n">
-        <v>-0.1107</v>
+        <v>0.513</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6848</v>
+        <v>-0.6322</v>
       </c>
       <c r="J291" t="n">
-        <v>-18.4896</v>
+        <v>-17.0694</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.82</v>
       </c>
       <c r="I292" t="n">
-        <v>0.9121</v>
+        <v>0.8984</v>
       </c>
       <c r="J292" t="n">
-        <v>20.9783</v>
+        <v>20.6632</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.6</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6928</v>
+        <v>0.6957</v>
       </c>
       <c r="J293" t="n">
-        <v>15.9344</v>
+        <v>16.0011</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.39</v>
       </c>
       <c r="I294" t="n">
-        <v>0.4776</v>
+        <v>0.4926</v>
       </c>
       <c r="J294" t="n">
-        <v>10.9848</v>
+        <v>11.3298</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.19</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2479</v>
+        <v>0.2709</v>
       </c>
       <c r="J295" t="n">
-        <v>5.7017</v>
+        <v>6.2307</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.05</v>
       </c>
       <c r="I296" t="n">
-        <v>0.0522</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="J296" t="n">
-        <v>1.2006</v>
+        <v>1.7112</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.16</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4212</v>
+        <v>0.3932</v>
       </c>
       <c r="J297" t="n">
-        <v>9.6876</v>
+        <v>9.0436</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.87</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1133</v>
+        <v>-0.1387</v>
       </c>
       <c r="J298" t="n">
-        <v>-2.6059</v>
+        <v>-3.1901</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.4208</v>
+        <v>-0.4367</v>
       </c>
       <c r="J299" t="n">
-        <v>-9.6784</v>
+        <v>-10.0441</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.41</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5617</v>
+        <v>-0.5683</v>
       </c>
       <c r="J300" t="n">
-        <v>-12.9191</v>
+        <v>-13.0709</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.33</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6369</v>
+        <v>-0.6378</v>
       </c>
       <c r="J301" t="n">
-        <v>-14.6487</v>
+        <v>-14.6694</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.35</v>
       </c>
       <c r="I302" t="n">
-        <v>0.7663</v>
+        <v>0.722</v>
       </c>
       <c r="J302" t="n">
-        <v>19.9238</v>
+        <v>18.772</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.0997</v>
+        <v>-0.1145</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.5922</v>
+        <v>-2.977</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.77</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2532</v>
+        <v>-0.2696</v>
       </c>
       <c r="J304" t="n">
-        <v>-6.5832</v>
+        <v>-7.0096</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.68</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3398</v>
+        <v>-0.3539</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.8348</v>
+        <v>-9.2014</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.65</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3681</v>
+        <v>-0.3812</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.570600000000001</v>
+        <v>-9.911199999999999</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.92</v>
       </c>
       <c r="I307" t="n">
-        <v>1.6531</v>
+        <v>1.6452</v>
       </c>
       <c r="J307" t="n">
-        <v>42.9806</v>
+        <v>42.7752</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.36</v>
       </c>
       <c r="I308" t="n">
-        <v>0.9236</v>
+        <v>0.8685</v>
       </c>
       <c r="J308" t="n">
-        <v>24.0136</v>
+        <v>22.581</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.97</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1865</v>
+        <v>-0.1747</v>
       </c>
       <c r="J309" t="n">
-        <v>-4.849</v>
+        <v>-4.5422</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1865</v>
+        <v>-0.1747</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.849</v>
+        <v>-4.5422</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.87</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4928</v>
+        <v>-0.4608</v>
       </c>
       <c r="J311" t="n">
-        <v>-12.8128</v>
+        <v>-11.9808</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.09</v>
       </c>
       <c r="I312" t="n">
-        <v>0.2523</v>
+        <v>0.252</v>
       </c>
       <c r="J312" t="n">
-        <v>6.5598</v>
+        <v>6.552</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.03</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1134</v>
+        <v>0.1156</v>
       </c>
       <c r="J313" t="n">
-        <v>2.9484</v>
+        <v>3.0056</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.92</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1035</v>
+        <v>-0.1174</v>
       </c>
       <c r="J314" t="n">
-        <v>-2.691</v>
+        <v>-3.0524</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.88</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1462</v>
+        <v>-0.1616</v>
       </c>
       <c r="J315" t="n">
-        <v>-3.8012</v>
+        <v>-4.2016</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.63</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3914</v>
+        <v>-0.4027</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.1764</v>
+        <v>-10.4702</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.65</v>
       </c>
       <c r="I317" t="n">
-        <v>1.3306</v>
+        <v>1.3058</v>
       </c>
       <c r="J317" t="n">
-        <v>34.5956</v>
+        <v>33.9508</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.5</v>
       </c>
       <c r="I318" t="n">
-        <v>1.1415</v>
+        <v>1.1042</v>
       </c>
       <c r="J318" t="n">
-        <v>29.679</v>
+        <v>28.7092</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.19</v>
       </c>
       <c r="I319" t="n">
-        <v>0.5366</v>
+        <v>0.5239</v>
       </c>
       <c r="J319" t="n">
-        <v>13.9516</v>
+        <v>13.6214</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.83</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5967</v>
+        <v>-0.5554</v>
       </c>
       <c r="J320" t="n">
-        <v>-15.5142</v>
+        <v>-14.4404</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.83</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5967</v>
+        <v>-0.5554</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.5142</v>
+        <v>-14.4404</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>0.85</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.1423</v>
+        <v>-0.1662</v>
       </c>
       <c r="J322" t="n">
-        <v>-3.5575</v>
+        <v>-4.155</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.79</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.2074</v>
+        <v>-0.2302</v>
       </c>
       <c r="J323" t="n">
-        <v>-5.185</v>
+        <v>-5.755</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.78</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2178</v>
+        <v>-0.2404</v>
       </c>
       <c r="J324" t="n">
-        <v>-5.445</v>
+        <v>-6.01</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.63</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.359</v>
+        <v>-0.3775</v>
       </c>
       <c r="J325" t="n">
-        <v>-8.975</v>
+        <v>-9.4375</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.38</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5928</v>
+        <v>-0.5968</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.82</v>
+        <v>-14.92</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.68</v>
       </c>
       <c r="I327" t="n">
-        <v>1.3134</v>
+        <v>1.2971</v>
       </c>
       <c r="J327" t="n">
-        <v>32.835</v>
+        <v>32.4275</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.53</v>
       </c>
       <c r="I328" t="n">
-        <v>1.1362</v>
+        <v>1.1071</v>
       </c>
       <c r="J328" t="n">
-        <v>28.405</v>
+        <v>27.6775</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.49</v>
       </c>
       <c r="I329" t="n">
-        <v>1.0884</v>
+        <v>1.0545</v>
       </c>
       <c r="J329" t="n">
-        <v>27.21</v>
+        <v>26.3625</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.27</v>
       </c>
       <c r="I330" t="n">
-        <v>0.6813</v>
+        <v>0.6624</v>
       </c>
       <c r="J330" t="n">
-        <v>17.0325</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>1.18</v>
       </c>
       <c r="I331" t="n">
-        <v>0.4636</v>
+        <v>0.4682</v>
       </c>
       <c r="J331" t="n">
-        <v>11.59</v>
+        <v>11.705</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.41</v>
       </c>
       <c r="I332" t="n">
-        <v>1.0312</v>
+        <v>0.976</v>
       </c>
       <c r="J332" t="n">
-        <v>43.3104</v>
+        <v>40.992</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.37</v>
       </c>
       <c r="I333" t="n">
-        <v>0.9616</v>
+        <v>0.9013</v>
       </c>
       <c r="J333" t="n">
-        <v>40.3872</v>
+        <v>37.8546</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.21</v>
       </c>
       <c r="I334" t="n">
-        <v>0.5909</v>
+        <v>0.5714</v>
       </c>
       <c r="J334" t="n">
-        <v>24.8178</v>
+        <v>23.9988</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.2</v>
       </c>
       <c r="I335" t="n">
-        <v>0.5666</v>
+        <v>0.5496</v>
       </c>
       <c r="J335" t="n">
-        <v>23.7972</v>
+        <v>23.0832</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.62</v>
       </c>
       <c r="I336" t="n">
-        <v>-1.1069</v>
+        <v>-1.0043</v>
       </c>
       <c r="J336" t="n">
-        <v>-46.4898</v>
+        <v>-42.1806</v>
       </c>
     </row>
     <row r="337">
@@ -15869,10 +15869,10 @@
         <v>1.09</v>
       </c>
       <c r="I338" t="n">
-        <v>0.2443</v>
+        <v>0.2461</v>
       </c>
       <c r="J338" t="n">
-        <v>10.2606</v>
+        <v>10.3362</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.85</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1802</v>
+        <v>-0.1955</v>
       </c>
       <c r="J339" t="n">
-        <v>-7.5684</v>
+        <v>-8.211</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.211</v>
+        <v>-0.2263</v>
       </c>
       <c r="J340" t="n">
-        <v>-8.862</v>
+        <v>-9.5046</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.8</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2311</v>
+        <v>-0.2462</v>
       </c>
       <c r="J341" t="n">
-        <v>-9.706200000000001</v>
+        <v>-10.3404</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.42</v>
       </c>
       <c r="I342" t="n">
-        <v>1.0192</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="J342" t="n">
-        <v>27.5184</v>
+        <v>26.1414</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.4</v>
       </c>
       <c r="I343" t="n">
-        <v>0.9864000000000001</v>
+        <v>0.9327</v>
       </c>
       <c r="J343" t="n">
-        <v>26.6328</v>
+        <v>25.1829</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.37</v>
       </c>
       <c r="I344" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.8764</v>
       </c>
       <c r="J344" t="n">
-        <v>25.0803</v>
+        <v>23.6628</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.35</v>
       </c>
       <c r="I345" t="n">
-        <v>0.8862</v>
+        <v>0.838</v>
       </c>
       <c r="J345" t="n">
-        <v>23.9274</v>
+        <v>22.626</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.85</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5614</v>
+        <v>-0.5201</v>
       </c>
       <c r="J346" t="n">
-        <v>-15.1578</v>
+        <v>-14.0427</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.99</v>
       </c>
       <c r="I347" t="n">
-        <v>0.0149</v>
+        <v>-0.003</v>
       </c>
       <c r="J347" t="n">
-        <v>0.4023</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.8</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.2158</v>
+        <v>-0.2345</v>
       </c>
       <c r="J348" t="n">
-        <v>-5.8266</v>
+        <v>-6.3315</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.77</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.2443</v>
+        <v>-0.2627</v>
       </c>
       <c r="J349" t="n">
-        <v>-6.5961</v>
+        <v>-7.0929</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.77</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2443</v>
+        <v>-0.2627</v>
       </c>
       <c r="J350" t="n">
-        <v>-6.5961</v>
+        <v>-7.0929</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3206</v>
+        <v>-0.3372</v>
       </c>
       <c r="J351" t="n">
-        <v>-8.6562</v>
+        <v>-9.1044</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5604/event_5604_evp_summary.xlsx
+++ b/database/event/5604/event_5604_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.7568</v>
+        <v>3.4938</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0743</v>
+        <v>0.9991</v>
       </c>
       <c r="D2" t="n">
-        <v>1.086</v>
+        <v>0.9858</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7568</v>
+        <v>3.4938</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7568</v>
+        <v>3.4938</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4975</v>
+        <v>5.0565</v>
       </c>
       <c r="I2" t="n">
-        <v>6.7385</v>
+        <v>6.2442</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7385</v>
+        <v>6.2442</v>
       </c>
       <c r="N2" t="n">
         <v>405</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.5097</v>
+        <v>3.359</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0036</v>
+        <v>0.9605</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9735</v>
+        <v>0.9244</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5097</v>
+        <v>3.359</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5097</v>
+        <v>3.359</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9567</v>
+        <v>4.7478</v>
       </c>
       <c r="I3" t="n">
-        <v>5.923</v>
+        <v>5.7104</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -575,7 +575,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5.923</v>
+        <v>5.7104</v>
       </c>
       <c r="N3" t="n">
         <v>347</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.2386</v>
+        <v>3.1297</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9261</v>
+        <v>0.895</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8501</v>
+        <v>0.8199</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2386</v>
+        <v>3.1297</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2386</v>
+        <v>3.1297</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3634</v>
+        <v>4.2223</v>
       </c>
       <c r="I4" t="n">
-        <v>5.3484</v>
+        <v>5.214</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.3484</v>
+        <v>5.214</v>
       </c>
       <c r="N4" t="n">
         <v>257</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.2061</v>
+        <v>3.0549</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.8736</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8353</v>
+        <v>0.7859</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2061</v>
+        <v>3.0549</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2061</v>
+        <v>3.0549</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2923</v>
+        <v>4.0509</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2612</v>
+        <v>5.0023</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2612</v>
+        <v>5.0023</v>
       </c>
       <c r="N5" t="n">
         <v>257</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0175</v>
+        <v>2.9259</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8629</v>
+        <v>0.8367</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7494</v>
+        <v>0.7271</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0175</v>
+        <v>2.9259</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0175</v>
+        <v>2.9259</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8794</v>
+        <v>3.7552</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1871</v>
+        <v>4.0643</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1871</v>
+        <v>4.0643</v>
       </c>
       <c r="N6" t="n">
         <v>187</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7997</v>
+        <v>2.6704</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8006</v>
+        <v>0.7635999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6503</v>
+        <v>0.6107</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7997</v>
+        <v>2.6704</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7997</v>
+        <v>2.6704</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4027</v>
+        <v>3.1697</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1708</v>
+        <v>3.9141</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.1708</v>
+        <v>3.9141</v>
       </c>
       <c r="N7" t="n">
         <v>405</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.7401</v>
+        <v>2.6362</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7836</v>
+        <v>0.7538</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6231</v>
+        <v>0.5951</v>
       </c>
       <c r="E8" t="n">
-        <v>2.7401</v>
+        <v>2.6362</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7401</v>
+        <v>2.6362</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2723</v>
+        <v>3.0911</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5318</v>
+        <v>3.7178</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>187</v>
+        <v>347</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5318</v>
+        <v>3.7178</v>
       </c>
       <c r="N8" t="n">
-        <v>187</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.7296</v>
+        <v>2.6361</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7806</v>
+        <v>0.7538</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.5951</v>
       </c>
       <c r="E9" t="n">
-        <v>2.7296</v>
+        <v>2.6361</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7296</v>
+        <v>2.6361</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2494</v>
+        <v>3.0909</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8828</v>
+        <v>3.3454</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>347</v>
+        <v>187</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8828</v>
+        <v>3.3454</v>
       </c>
       <c r="N9" t="n">
-        <v>347</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6835</v>
+        <v>2.6082</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7674</v>
+        <v>0.7458</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5974</v>
+        <v>0.5824</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6835</v>
+        <v>2.6082</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6835</v>
+        <v>2.6082</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1484</v>
+        <v>3.0271</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5755</v>
+        <v>3.4538</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5755</v>
+        <v>3.4538</v>
       </c>
       <c r="N10" t="n">
         <v>252</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5661</v>
+        <v>2.5069</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7338</v>
+        <v>0.7169</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5362</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5661</v>
+        <v>2.5069</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5661</v>
+        <v>2.5069</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8914</v>
+        <v>2.7949</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4551</v>
+        <v>3.4513</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>347</v>
+        <v>405</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4551</v>
+        <v>3.4513</v>
       </c>
       <c r="N11" t="n">
-        <v>347</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5289</v>
+        <v>2.5021</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7232</v>
+        <v>0.7155</v>
       </c>
       <c r="D12" t="n">
-        <v>0.527</v>
+        <v>0.534</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5289</v>
+        <v>2.5021</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5289</v>
+        <v>2.5021</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8101</v>
+        <v>2.7839</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4444</v>
+        <v>3.3483</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>405</v>
+        <v>347</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4444</v>
+        <v>3.3483</v>
       </c>
       <c r="N12" t="n">
-        <v>405</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13">
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4592</v>
+        <v>2.3909</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7032</v>
+        <v>0.6837</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4953</v>
+        <v>0.4834</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4592</v>
+        <v>2.3909</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4592</v>
+        <v>2.3909</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6576</v>
+        <v>2.5292</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7963</v>
+        <v>2.6661</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7963</v>
+        <v>2.6661</v>
       </c>
       <c r="N13" t="n">
         <v>178</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2838</v>
+        <v>2.2661</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6531</v>
+        <v>0.648</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4154</v>
+        <v>0.4265</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2838</v>
+        <v>2.2661</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2838</v>
+        <v>2.2661</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2838</v>
+        <v>2.2661</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7993</v>
+        <v>2.7984</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7993</v>
+        <v>2.7984</v>
       </c>
       <c r="N14" t="n">
         <v>257</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6448</v>
+        <v>1.5616</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4703</v>
+        <v>0.4466</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1245</v>
+        <v>0.1056</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6448</v>
+        <v>1.5616</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6448</v>
+        <v>1.5616</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6448</v>
+        <v>1.5616</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9655</v>
+        <v>1.8781</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9655</v>
+        <v>1.8781</v>
       </c>
       <c r="N15" t="n">
         <v>347</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5685</v>
+        <v>1.5219</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4485</v>
+        <v>0.4352</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0898</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5685</v>
+        <v>1.5219</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5685</v>
+        <v>1.5219</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5685</v>
+        <v>1.5219</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9226</v>
+        <v>1.8793</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9226</v>
+        <v>1.8793</v>
       </c>
       <c r="N16" t="n">
         <v>257</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5473</v>
+        <v>1.4904</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4425</v>
+        <v>0.4262</v>
       </c>
       <c r="D17" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0732</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5473</v>
+        <v>1.4904</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5473</v>
+        <v>1.4904</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5473</v>
+        <v>1.4904</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8966</v>
+        <v>1.8405</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8966</v>
+        <v>1.8405</v>
       </c>
       <c r="N17" t="n">
         <v>405</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5251</v>
+        <v>1.4835</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4361</v>
+        <v>0.4242</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0701</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5251</v>
+        <v>1.4835</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5251</v>
+        <v>1.4835</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5251</v>
+        <v>1.4835</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6047</v>
+        <v>1.5638</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6047</v>
+        <v>1.5638</v>
       </c>
       <c r="N18" t="n">
         <v>178</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4739</v>
+        <v>1.3206</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4215</v>
+        <v>0.3776</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0467</v>
+        <v>-0.0042</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4739</v>
+        <v>1.3206</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4739</v>
+        <v>1.3206</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4739</v>
+        <v>1.3206</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5508</v>
+        <v>1.5068</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>160</v>
+        <v>252</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5508</v>
+        <v>1.5068</v>
       </c>
       <c r="N19" t="n">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4025</v>
+        <v>1.24</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4011</v>
+        <v>0.3546</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0142</v>
+        <v>-0.0409</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4025</v>
+        <v>1.24</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4025</v>
+        <v>1.24</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4025</v>
+        <v>1.24</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5928</v>
+        <v>1.3072</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5928</v>
+        <v>1.3072</v>
       </c>
       <c r="N20" t="n">
-        <v>252</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.3242</v>
+        <v>1.2254</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3787</v>
+        <v>0.3504</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0214</v>
+        <v>-0.0476</v>
       </c>
       <c r="E21" t="n">
-        <v>1.3242</v>
+        <v>1.2254</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3242</v>
+        <v>1.2254</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.3242</v>
+        <v>1.2254</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5038</v>
+        <v>1.3981</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5038</v>
+        <v>1.3981</v>
       </c>
       <c r="N21" t="n">
         <v>252</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0986</v>
+        <v>0.9581</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3142</v>
+        <v>0.274</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1241</v>
+        <v>-0.1693</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0986</v>
+        <v>0.9581</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0986</v>
+        <v>0.9581</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0986</v>
+        <v>0.9581</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0986</v>
+        <v>0.9581</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0986</v>
+        <v>0.9581</v>
       </c>
       <c r="N22" t="n">
         <v>124</v>
@@ -1458,93 +1458,93 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9557</v>
+        <v>0.836</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2733</v>
+        <v>0.2391</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1891</v>
+        <v>-0.225</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9557</v>
+        <v>0.836</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9557</v>
+        <v>0.836</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9557</v>
+        <v>0.836</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0315</v>
+        <v>0.8813</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0315</v>
+        <v>0.8813</v>
       </c>
       <c r="N23" t="n">
-        <v>187</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8138</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2377</v>
+        <v>0.2327</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2459</v>
+        <v>-0.2351</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8138</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8138</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8138</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8808</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8808</v>
       </c>
       <c r="N24" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4953</v>
+        <v>0.4871</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1416</v>
+        <v>0.1393</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3987</v>
+        <v>-0.3839</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4953</v>
+        <v>0.4871</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4953</v>
+        <v>0.4871</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4953</v>
+        <v>0.4871</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5346</v>
+        <v>0.5272</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5346</v>
+        <v>0.5272</v>
       </c>
       <c r="N25" t="n">
         <v>187</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>oBo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3381</v>
+        <v>0.2784</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0796</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4703</v>
+        <v>-0.479</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3381</v>
+        <v>0.2784</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3381</v>
+        <v>0.2784</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3381</v>
+        <v>0.2784</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3557</v>
+        <v>0.2784</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3557</v>
+        <v>0.2784</v>
       </c>
       <c r="N26" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oBo</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3279</v>
+        <v>0.233</v>
       </c>
       <c r="C27" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4749</v>
+        <v>-0.4996</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3279</v>
+        <v>0.233</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3279</v>
+        <v>0.233</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3279</v>
+        <v>0.233</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3279</v>
+        <v>0.2456</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3279</v>
+        <v>0.2456</v>
       </c>
       <c r="N27" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.136</v>
+        <v>0.0963</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0389</v>
+        <v>0.0275</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5623</v>
+        <v>-0.5619</v>
       </c>
       <c r="E28" t="n">
-        <v>0.136</v>
+        <v>0.0963</v>
       </c>
       <c r="F28" t="n">
-        <v>0.136</v>
+        <v>0.0963</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.136</v>
+        <v>0.0963</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1431</v>
+        <v>0.1016</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1431</v>
+        <v>0.1016</v>
       </c>
       <c r="N28" t="n">
         <v>160</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.066</v>
+        <v>0.0068</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0189</v>
+        <v>0.0019</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6542</v>
+        <v>-0.6027</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.066</v>
+        <v>0.0068</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.066</v>
+        <v>0.0068</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.066</v>
+        <v>0.0068</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.0078</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.0078</v>
       </c>
       <c r="N29" t="n">
         <v>252</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2317</v>
+        <v>-0.2256</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0663</v>
+        <v>-0.0645</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7297</v>
+        <v>-0.7086</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2317</v>
+        <v>-0.2256</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2317</v>
+        <v>-0.2256</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2317</v>
+        <v>-0.2256</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2317</v>
+        <v>-0.2256</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2317</v>
+        <v>-0.2256</v>
       </c>
       <c r="N30" t="n">
         <v>124</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3307</v>
+        <v>-0.4122</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0946</v>
+        <v>-0.1179</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.7936</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3307</v>
+        <v>-0.4122</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3307</v>
+        <v>-0.4122</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3307</v>
+        <v>-0.4122</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.348</v>
+        <v>-0.4345</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.348</v>
+        <v>-0.4345</v>
       </c>
       <c r="N31" t="n">
         <v>160</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.431</v>
+        <v>-0.4494</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1232</v>
+        <v>-0.1285</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8204</v>
+        <v>-0.8105</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.431</v>
+        <v>-0.4494</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.431</v>
+        <v>-0.4494</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.431</v>
+        <v>-0.4494</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4535</v>
+        <v>-0.4494</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4535</v>
+        <v>-0.4494</v>
       </c>
       <c r="N32" t="n">
-        <v>160</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4485</v>
+        <v>-0.4792</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1283</v>
+        <v>-0.137</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8284</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4485</v>
+        <v>-0.4792</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4485</v>
+        <v>-0.4792</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4485</v>
+        <v>-0.4792</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4485</v>
+        <v>-0.5051</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4485</v>
+        <v>-0.5051</v>
       </c>
       <c r="N33" t="n">
-        <v>124</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6559</v>
+        <v>-0.6116</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1876</v>
+        <v>-0.1749</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9228</v>
+        <v>-0.8844</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6559</v>
+        <v>-0.6116</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6559</v>
+        <v>-0.6116</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6559</v>
+        <v>-0.6116</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6559</v>
+        <v>-0.6116</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6559</v>
+        <v>-0.6116</v>
       </c>
       <c r="N34" t="n">
         <v>124</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.9877</v>
+        <v>-0.9968</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2824</v>
+        <v>-0.285</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0738</v>
+        <v>-1.0599</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.9877</v>
+        <v>-0.9968</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9877</v>
+        <v>-0.9968</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.9877</v>
+        <v>-0.9968</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.2107</v>
+        <v>-1.2309</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.2107</v>
+        <v>-1.2309</v>
       </c>
       <c r="N35" t="n">
         <v>405</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>interz</t>
+          <t>k1to</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2496</v>
+        <v>-1.2533</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3573</v>
+        <v>-0.3584</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.193</v>
+        <v>-1.1767</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2496</v>
+        <v>-1.2533</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2496</v>
+        <v>-1.2533</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2496</v>
+        <v>-1.2533</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.5317</v>
+        <v>-1.3212</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>257</v>
+        <v>178</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.5317</v>
+        <v>-1.3212</v>
       </c>
       <c r="N36" t="n">
-        <v>257</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>k1to</t>
+          <t>interz</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3448</v>
+        <v>-1.2541</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3846</v>
+        <v>-0.3586</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2364</v>
+        <v>-1.1771</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3448</v>
+        <v>-1.2541</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3448</v>
+        <v>-1.2541</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3448</v>
+        <v>-1.2541</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.415</v>
+        <v>-1.5486</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>178</v>
+        <v>257</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.415</v>
+        <v>-1.5486</v>
       </c>
       <c r="N37" t="n">
-        <v>178</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.4275</v>
+        <v>-1.3795</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4082</v>
+        <v>-0.3945</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.274</v>
+        <v>-1.2342</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.4275</v>
+        <v>-1.3795</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4275</v>
+        <v>-1.3795</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4275</v>
+        <v>-1.3795</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5407</v>
+        <v>-1.4931</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5407</v>
+        <v>-1.4931</v>
       </c>
       <c r="N38" t="n">
         <v>187</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5826</v>
+        <v>-1.5489</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4526</v>
+        <v>-0.4429</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.3446</v>
+        <v>-1.3114</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5826</v>
+        <v>-1.5489</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5826</v>
+        <v>-1.5489</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5826</v>
+        <v>-1.5489</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7973</v>
+        <v>-1.7672</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7973</v>
+        <v>-1.7672</v>
       </c>
       <c r="N39" t="n">
         <v>252</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9829</v>
+        <v>-1.9098</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5461</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5269</v>
+        <v>-1.4758</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9829</v>
+        <v>-1.9098</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9829</v>
+        <v>-1.9098</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9829</v>
+        <v>-1.9098</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.0864</v>
+        <v>-2.0132</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0864</v>
+        <v>-2.0132</v>
       </c>
       <c r="N40" t="n">
         <v>178</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.3999</v>
+        <v>-3.1999</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9722</v>
+        <v>-0.915</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.1719</v>
+        <v>-2.0635</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.3999</v>
+        <v>-3.1999</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.3999</v>
+        <v>-3.1999</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-3.3999</v>
+        <v>-3.1999</v>
       </c>
       <c r="I41" t="n">
-        <v>-4.0627</v>
+        <v>-3.8486</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-4.0627</v>
+        <v>-3.8486</v>
       </c>
       <c r="N41" t="n">
         <v>347</v>
@@ -2429,10 +2429,10 @@
         <v>1.31</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8229</v>
+        <v>0.799</v>
       </c>
       <c r="J2" t="n">
-        <v>23.0412</v>
+        <v>22.372</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.18</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5349</v>
+        <v>0.4938</v>
       </c>
       <c r="J3" t="n">
-        <v>14.9772</v>
+        <v>13.8264</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3634</v>
+        <v>0.3215</v>
       </c>
       <c r="J4" t="n">
-        <v>10.1752</v>
+        <v>9.002000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3191</v>
+        <v>-0.2775</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.934799999999999</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0415</v>
+        <v>-1.0434</v>
       </c>
       <c r="J6" t="n">
-        <v>-29.162</v>
+        <v>-29.2152</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5903</v>
+        <v>0.5309</v>
       </c>
       <c r="J7" t="n">
-        <v>16.5284</v>
+        <v>14.8652</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.23</v>
       </c>
       <c r="I8" t="n">
-        <v>0.478</v>
+        <v>0.4192</v>
       </c>
       <c r="J8" t="n">
-        <v>13.384</v>
+        <v>11.7376</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1011</v>
+        <v>-0.0839</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.8308</v>
+        <v>-2.3492</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.87</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1825</v>
+        <v>-0.1619</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.11</v>
+        <v>-4.5332</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.79</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2646</v>
+        <v>-0.2452</v>
       </c>
       <c r="J11" t="n">
-        <v>-7.4088</v>
+        <v>-6.8656</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2682</v>
+        <v>1.2862</v>
       </c>
       <c r="J12" t="n">
-        <v>34.2414</v>
+        <v>34.7274</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.32</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7847</v>
+        <v>0.7613</v>
       </c>
       <c r="J13" t="n">
-        <v>21.1869</v>
+        <v>20.5551</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.27</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="J14" t="n">
-        <v>18.495</v>
+        <v>17.739</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0597</v>
+        <v>0.0435</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6119</v>
+        <v>1.1745</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.99</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1014</v>
+        <v>-0.0808</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.7378</v>
+        <v>-2.1816</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4797</v>
+        <v>0.427</v>
       </c>
       <c r="J17" t="n">
-        <v>12.9519</v>
+        <v>11.529</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.89</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1467</v>
+        <v>-0.1302</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.9609</v>
+        <v>-3.5154</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.83</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2087</v>
+        <v>-0.19</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.6349</v>
+        <v>-5.13</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.7</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.333</v>
+        <v>-0.3168</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.991</v>
+        <v>-8.553599999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.63</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3966</v>
+        <v>-0.3849</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.7082</v>
+        <v>-10.3923</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.34</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8458</v>
+        <v>0.8233</v>
       </c>
       <c r="J22" t="n">
-        <v>21.145</v>
+        <v>20.5825</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.32</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8054</v>
+        <v>0.7798</v>
       </c>
       <c r="J23" t="n">
-        <v>20.135</v>
+        <v>19.495</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.08</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2655</v>
+        <v>0.233</v>
       </c>
       <c r="J24" t="n">
-        <v>6.6375</v>
+        <v>5.825</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.02</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0771</v>
+        <v>0.0605</v>
       </c>
       <c r="J25" t="n">
-        <v>1.9275</v>
+        <v>1.5125</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.97</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1618</v>
+        <v>-0.1302</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.045</v>
+        <v>-3.255</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7287</v>
+        <v>0.6773</v>
       </c>
       <c r="J27" t="n">
-        <v>18.2175</v>
+        <v>16.9325</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1358</v>
+        <v>0.1027</v>
       </c>
       <c r="J28" t="n">
-        <v>3.395</v>
+        <v>2.5675</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2363</v>
+        <v>-0.2162</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.9075</v>
+        <v>-5.405</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.77</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2756</v>
+        <v>-0.2564</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.89</v>
+        <v>-6.41</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.68</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3599</v>
+        <v>-0.3456</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.9975</v>
+        <v>-8.640000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.52</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7094</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>20.5726</v>
+        <v>21.8805</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3937</v>
+        <v>0.3898</v>
       </c>
       <c r="J33" t="n">
-        <v>11.4173</v>
+        <v>11.3042</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.93</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1166</v>
+        <v>-0.0982</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.3814</v>
+        <v>-2.8478</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1407</v>
+        <v>-0.1211</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.0803</v>
+        <v>-3.5119</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.7</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3529</v>
+        <v>-0.3391</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.2341</v>
+        <v>-9.8339</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.62</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7758</v>
+        <v>0.7089</v>
       </c>
       <c r="J37" t="n">
-        <v>22.4982</v>
+        <v>20.5581</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.11</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1945</v>
+        <v>0.1518</v>
       </c>
       <c r="J38" t="n">
-        <v>5.6405</v>
+        <v>4.4022</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.06</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1212</v>
+        <v>0.0906</v>
       </c>
       <c r="J39" t="n">
-        <v>3.5148</v>
+        <v>2.6274</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.129</v>
+        <v>-0.1099</v>
       </c>
       <c r="J40" t="n">
-        <v>-3.741</v>
+        <v>-3.1871</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.61</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4335</v>
+        <v>-0.4276</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.5715</v>
+        <v>-12.4004</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.27</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7165</v>
+        <v>0.6841</v>
       </c>
       <c r="J42" t="n">
-        <v>20.7785</v>
+        <v>19.8389</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.23</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6302</v>
+        <v>0.5934</v>
       </c>
       <c r="J43" t="n">
-        <v>18.2758</v>
+        <v>17.2086</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.19</v>
       </c>
       <c r="I44" t="n">
-        <v>0.541</v>
+        <v>0.5014</v>
       </c>
       <c r="J44" t="n">
-        <v>15.689</v>
+        <v>14.5406</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.95</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2167</v>
+        <v>-0.1799</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.2843</v>
+        <v>-5.2171</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6052</v>
+        <v>-0.5677</v>
       </c>
       <c r="J46" t="n">
-        <v>-17.5508</v>
+        <v>-16.4633</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.46</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8438</v>
+        <v>0.7958</v>
       </c>
       <c r="J47" t="n">
-        <v>24.4702</v>
+        <v>23.0782</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.2</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4361</v>
+        <v>0.3785</v>
       </c>
       <c r="J48" t="n">
-        <v>12.6469</v>
+        <v>10.9765</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.96</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0718</v>
+        <v>-0.0578</v>
       </c>
       <c r="J49" t="n">
-        <v>-2.0822</v>
+        <v>-1.6762</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.72</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3283</v>
+        <v>-0.312</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.5207</v>
+        <v>-9.048</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.61</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4276</v>
+        <v>-0.4202</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.4004</v>
+        <v>-12.1858</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.44</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8418</v>
+        <v>0.7991</v>
       </c>
       <c r="J52" t="n">
-        <v>22.7286</v>
+        <v>21.5757</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0109</v>
+        <v>0.0071</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2943</v>
+        <v>0.1917</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.82</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2249</v>
+        <v>-0.2049</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.0723</v>
+        <v>-5.5323</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.68</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3586</v>
+        <v>-0.3441</v>
       </c>
       <c r="J55" t="n">
-        <v>-9.6822</v>
+        <v>-9.290699999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.66</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3767</v>
+        <v>-0.3637</v>
       </c>
       <c r="J56" t="n">
-        <v>-10.1709</v>
+        <v>-9.819900000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.44</v>
       </c>
       <c r="I57" t="n">
-        <v>1.033</v>
+        <v>1.0357</v>
       </c>
       <c r="J57" t="n">
-        <v>27.891</v>
+        <v>27.9639</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.19</v>
       </c>
       <c r="I58" t="n">
-        <v>0.532</v>
+        <v>0.4942</v>
       </c>
       <c r="J58" t="n">
-        <v>14.364</v>
+        <v>13.3434</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.15</v>
       </c>
       <c r="I59" t="n">
-        <v>0.441</v>
+        <v>0.403</v>
       </c>
       <c r="J59" t="n">
-        <v>11.907</v>
+        <v>10.881</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.02</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0793</v>
+        <v>0.0624</v>
       </c>
       <c r="J60" t="n">
-        <v>2.1411</v>
+        <v>1.6848</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4458</v>
+        <v>-0.4038</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.0366</v>
+        <v>-10.9026</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.48</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6137</v>
+        <v>0.5425</v>
       </c>
       <c r="J62" t="n">
-        <v>17.7973</v>
+        <v>15.7325</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.16</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2537</v>
+        <v>0.2051</v>
       </c>
       <c r="J63" t="n">
-        <v>7.3573</v>
+        <v>5.9479</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.12</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2025</v>
+        <v>0.1606</v>
       </c>
       <c r="J64" t="n">
-        <v>5.8725</v>
+        <v>4.6574</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.12</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2025</v>
+        <v>0.1606</v>
       </c>
       <c r="J65" t="n">
-        <v>5.8725</v>
+        <v>4.6574</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2138</v>
+        <v>-0.1939</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.2002</v>
+        <v>-5.6231</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.16</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2913</v>
+        <v>0.2786</v>
       </c>
       <c r="J67" t="n">
-        <v>8.447699999999999</v>
+        <v>8.0794</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.01</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0372</v>
+        <v>0.0279</v>
       </c>
       <c r="J68" t="n">
-        <v>1.0788</v>
+        <v>0.8091</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0703</v>
+        <v>-0.057</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.0387</v>
+        <v>-1.653</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.93</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1089</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>-3.1581</v>
+        <v>-2.6622</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.77</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2786</v>
+        <v>-0.2596</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.0794</v>
+        <v>-7.5284</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.2</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4371</v>
+        <v>0.3795</v>
       </c>
       <c r="J72" t="n">
-        <v>15.7356</v>
+        <v>13.662</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.07</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1939</v>
+        <v>0.1535</v>
       </c>
       <c r="J73" t="n">
-        <v>6.9804</v>
+        <v>5.526</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0011</v>
+        <v>0.0005</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0396</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.92</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.1225</v>
+        <v>-0.1042</v>
       </c>
       <c r="J75" t="n">
-        <v>-4.41</v>
+        <v>-3.7512</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.74</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3091</v>
+        <v>-0.2917</v>
       </c>
       <c r="J76" t="n">
-        <v>-11.1276</v>
+        <v>-10.5012</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.33</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8456</v>
+        <v>0.8227</v>
       </c>
       <c r="J77" t="n">
-        <v>30.4416</v>
+        <v>29.6172</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.16</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4742</v>
+        <v>0.4334</v>
       </c>
       <c r="J78" t="n">
-        <v>17.0712</v>
+        <v>15.6024</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.15</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4505</v>
+        <v>0.4096</v>
       </c>
       <c r="J79" t="n">
-        <v>16.218</v>
+        <v>14.7456</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2144</v>
+        <v>-0.1777</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.7184</v>
+        <v>-6.3972</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.79</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6258</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="J81" t="n">
-        <v>-22.5288</v>
+        <v>-21.2112</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.21</v>
       </c>
       <c r="I82" t="n">
-        <v>0.613</v>
+        <v>0.5749</v>
       </c>
       <c r="J82" t="n">
-        <v>18.39</v>
+        <v>17.247</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.11</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3703</v>
+        <v>0.3276</v>
       </c>
       <c r="J83" t="n">
-        <v>11.109</v>
+        <v>9.827999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.02</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1007</v>
+        <v>0.0772</v>
       </c>
       <c r="J84" t="n">
-        <v>3.021</v>
+        <v>2.316</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.9</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3404</v>
+        <v>-0.2987</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.212</v>
+        <v>-8.961</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7644</v>
+        <v>-0.7359</v>
       </c>
       <c r="J86" t="n">
-        <v>-22.932</v>
+        <v>-22.077</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.33</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6403</v>
+        <v>0.5818</v>
       </c>
       <c r="J87" t="n">
-        <v>19.209</v>
+        <v>17.454</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.17</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3788</v>
+        <v>0.3235</v>
       </c>
       <c r="J88" t="n">
-        <v>11.364</v>
+        <v>9.705</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.99</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.026</v>
+        <v>-0.0186</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.78</v>
+        <v>-0.5580000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.86</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.1922</v>
+        <v>-0.1715</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.766</v>
+        <v>-5.145</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.72</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3304</v>
+        <v>-0.3145</v>
       </c>
       <c r="J91" t="n">
-        <v>-9.912000000000001</v>
+        <v>-9.435</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.17</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3417</v>
+        <v>0.3393</v>
       </c>
       <c r="J92" t="n">
-        <v>7.8591</v>
+        <v>7.8039</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.12</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2665</v>
+        <v>0.2568</v>
       </c>
       <c r="J93" t="n">
-        <v>6.1295</v>
+        <v>5.9064</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.63</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3936</v>
+        <v>-0.3815</v>
       </c>
       <c r="J94" t="n">
-        <v>-9.0528</v>
+        <v>-8.7745</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.61</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4115</v>
+        <v>-0.401</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.464499999999999</v>
+        <v>-9.223000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.58</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4381</v>
+        <v>-0.4301</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.0763</v>
+        <v>-9.892300000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.78</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8776</v>
+        <v>0.8079</v>
       </c>
       <c r="J97" t="n">
-        <v>20.1848</v>
+        <v>18.5817</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.5</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6097</v>
+        <v>0.5392</v>
       </c>
       <c r="J98" t="n">
-        <v>14.0231</v>
+        <v>12.4016</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.27</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3723</v>
+        <v>0.3155</v>
       </c>
       <c r="J99" t="n">
-        <v>8.562900000000001</v>
+        <v>7.2565</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.05</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0827</v>
+        <v>0.0601</v>
       </c>
       <c r="J100" t="n">
-        <v>1.9021</v>
+        <v>1.3823</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.96</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.0963</v>
+        <v>-0.0814</v>
       </c>
       <c r="J101" t="n">
-        <v>-2.2149</v>
+        <v>-1.8722</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.79</v>
       </c>
       <c r="I102" t="n">
-        <v>1.4696</v>
+        <v>1.5008</v>
       </c>
       <c r="J102" t="n">
-        <v>33.8008</v>
+        <v>34.5184</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.4</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9357</v>
+        <v>0.9243</v>
       </c>
       <c r="J103" t="n">
-        <v>21.5211</v>
+        <v>21.2589</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.24</v>
       </c>
       <c r="I104" t="n">
-        <v>0.6231</v>
+        <v>0.5939</v>
       </c>
       <c r="J104" t="n">
-        <v>14.3313</v>
+        <v>13.6597</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.18</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4935</v>
+        <v>0.4616</v>
       </c>
       <c r="J105" t="n">
-        <v>11.3505</v>
+        <v>10.6168</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.7</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8542</v>
+        <v>-0.8411</v>
       </c>
       <c r="J106" t="n">
-        <v>-19.6466</v>
+        <v>-19.3453</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.11</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3201</v>
+        <v>0.2729</v>
       </c>
       <c r="J107" t="n">
-        <v>7.3623</v>
+        <v>6.2767</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.8</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.2357</v>
+        <v>-0.2176</v>
       </c>
       <c r="J108" t="n">
-        <v>-5.4211</v>
+        <v>-5.0048</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.75</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2834</v>
+        <v>-0.2655</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.5182</v>
+        <v>-6.1065</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.73</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3021</v>
+        <v>-0.2848</v>
       </c>
       <c r="J110" t="n">
-        <v>-6.9483</v>
+        <v>-6.5504</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.72</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3115</v>
+        <v>-0.2945</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.1645</v>
+        <v>-6.7735</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.26</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4295</v>
+        <v>0.4312</v>
       </c>
       <c r="J112" t="n">
-        <v>11.5965</v>
+        <v>11.6424</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.97</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0553</v>
+        <v>-0.0442</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.4931</v>
+        <v>-1.1934</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.95</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0828</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J114" t="n">
-        <v>-2.2356</v>
+        <v>-1.8495</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.84</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2071</v>
+        <v>-0.1868</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.5917</v>
+        <v>-5.0436</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.72</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3244</v>
+        <v>-0.3076</v>
       </c>
       <c r="J116" t="n">
-        <v>-8.758800000000001</v>
+        <v>-8.305199999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.6</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7237</v>
+        <v>0.6518</v>
       </c>
       <c r="J117" t="n">
-        <v>19.5399</v>
+        <v>17.5986</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.4</v>
       </c>
       <c r="I118" t="n">
-        <v>0.52</v>
+        <v>0.4513</v>
       </c>
       <c r="J118" t="n">
-        <v>14.04</v>
+        <v>12.1851</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.15</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2371</v>
+        <v>0.1921</v>
       </c>
       <c r="J119" t="n">
-        <v>6.4017</v>
+        <v>5.1867</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.99</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0409</v>
+        <v>-0.0315</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.1043</v>
+        <v>-0.8505</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.91</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1525</v>
+        <v>-0.1334</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.1175</v>
+        <v>-3.6018</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.81</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5192</v>
+        <v>1.5581</v>
       </c>
       <c r="J122" t="n">
-        <v>37.98</v>
+        <v>38.9525</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.24</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6326000000000001</v>
+        <v>0.5994</v>
       </c>
       <c r="J123" t="n">
-        <v>15.815</v>
+        <v>14.985</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3134</v>
+        <v>0.2801</v>
       </c>
       <c r="J124" t="n">
-        <v>7.835</v>
+        <v>7.0025</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1.06</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2031</v>
+        <v>0.1746</v>
       </c>
       <c r="J125" t="n">
-        <v>5.0775</v>
+        <v>4.365</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.8629</v>
+        <v>-0.8482</v>
       </c>
       <c r="J126" t="n">
-        <v>-21.5725</v>
+        <v>-21.205</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.36</v>
       </c>
       <c r="I127" t="n">
-        <v>0.717</v>
+        <v>0.6656</v>
       </c>
       <c r="J127" t="n">
-        <v>17.925</v>
+        <v>16.64</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.06</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1845</v>
+        <v>0.1448</v>
       </c>
       <c r="J128" t="n">
-        <v>4.6125</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.87</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1735</v>
+        <v>-0.154</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.3375</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.67</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3681</v>
+        <v>-0.3543</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.202500000000001</v>
+        <v>-8.8575</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.66</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3771</v>
+        <v>-0.3641</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.4275</v>
+        <v>-9.102499999999999</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.34</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8484</v>
+        <v>0.826</v>
       </c>
       <c r="J132" t="n">
-        <v>22.9068</v>
+        <v>22.302</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.23</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6194</v>
+        <v>0.5837</v>
       </c>
       <c r="J133" t="n">
-        <v>16.7238</v>
+        <v>15.7599</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.3201</v>
+        <v>0.285</v>
       </c>
       <c r="J134" t="n">
-        <v>8.6427</v>
+        <v>7.695</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.04</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1489</v>
+        <v>0.1241</v>
       </c>
       <c r="J135" t="n">
-        <v>4.0203</v>
+        <v>3.3507</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.16</v>
+        <v>-0.1284</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.32</v>
+        <v>-3.4668</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.15</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3572</v>
+        <v>0.3031</v>
       </c>
       <c r="J137" t="n">
-        <v>9.644399999999999</v>
+        <v>8.1837</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.1</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2621</v>
+        <v>0.2144</v>
       </c>
       <c r="J138" t="n">
-        <v>7.0767</v>
+        <v>5.7888</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.04</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1323</v>
+        <v>0.0998</v>
       </c>
       <c r="J139" t="n">
-        <v>3.5721</v>
+        <v>2.6946</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.01</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0496</v>
+        <v>0.0332</v>
       </c>
       <c r="J140" t="n">
-        <v>1.3392</v>
+        <v>0.8964</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.46</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.553</v>
+        <v>-0.5618</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.931</v>
+        <v>-15.1686</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.36</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8757</v>
+        <v>0.8563</v>
       </c>
       <c r="J142" t="n">
-        <v>22.7682</v>
+        <v>22.2638</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.31</v>
       </c>
       <c r="I143" t="n">
-        <v>0.776</v>
+        <v>0.7496</v>
       </c>
       <c r="J143" t="n">
-        <v>20.176</v>
+        <v>19.4896</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.22</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5893</v>
+        <v>0.5552</v>
       </c>
       <c r="J144" t="n">
-        <v>15.3218</v>
+        <v>14.4352</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4813</v>
+        <v>0.4459</v>
       </c>
       <c r="J145" t="n">
-        <v>12.5138</v>
+        <v>11.5934</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.87</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4553</v>
+        <v>-0.4144</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.8378</v>
+        <v>-10.7744</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.2</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4617</v>
+        <v>0.406</v>
       </c>
       <c r="J147" t="n">
-        <v>12.0042</v>
+        <v>10.556</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1178</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>3.0628</v>
+        <v>2.2854</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.02</v>
       </c>
       <c r="I149" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.0654</v>
       </c>
       <c r="J149" t="n">
-        <v>2.3504</v>
+        <v>1.7004</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.77</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2722</v>
+        <v>-0.2531</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.0772</v>
+        <v>-6.5806</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.48</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5321</v>
+        <v>-0.537</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.8346</v>
+        <v>-13.962</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.61</v>
       </c>
       <c r="I152" t="n">
-        <v>1.2821</v>
+        <v>1.3048</v>
       </c>
       <c r="J152" t="n">
-        <v>35.8988</v>
+        <v>36.5344</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.24</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6495</v>
+        <v>0.6138</v>
       </c>
       <c r="J153" t="n">
-        <v>18.186</v>
+        <v>17.1864</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.14</v>
       </c>
       <c r="I154" t="n">
-        <v>0.4226</v>
+        <v>0.3829</v>
       </c>
       <c r="J154" t="n">
-        <v>11.8328</v>
+        <v>10.7212</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.75</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.7197</v>
+        <v>-0.6898</v>
       </c>
       <c r="J155" t="n">
-        <v>-20.1516</v>
+        <v>-19.3144</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7197</v>
+        <v>-0.6898</v>
       </c>
       <c r="J156" t="n">
-        <v>-20.1516</v>
+        <v>-19.3144</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.32</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6354</v>
+        <v>0.5779</v>
       </c>
       <c r="J157" t="n">
-        <v>17.7912</v>
+        <v>16.1812</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.02</v>
       </c>
       <c r="I158" t="n">
-        <v>0.0762</v>
+        <v>0.0541</v>
       </c>
       <c r="J158" t="n">
-        <v>2.1336</v>
+        <v>1.5148</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.96</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0573</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.988</v>
+        <v>-1.6044</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.85</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1995</v>
+        <v>-0.1789</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.586</v>
+        <v>-5.0092</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.74</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3084</v>
+        <v>-0.2909</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.635199999999999</v>
+        <v>-8.145200000000001</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>0.84</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.1812</v>
+        <v>-0.1657</v>
       </c>
       <c r="J162" t="n">
-        <v>-3.2616</v>
+        <v>-2.9826</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.79</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.2336</v>
+        <v>-0.2187</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.2048</v>
+        <v>-3.9366</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.75</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.2728</v>
+        <v>-0.2584</v>
       </c>
       <c r="J164" t="n">
-        <v>-4.9104</v>
+        <v>-4.6512</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.61</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3977</v>
+        <v>-0.3866</v>
       </c>
       <c r="J165" t="n">
-        <v>-7.1586</v>
+        <v>-6.9588</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.54</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4597</v>
+        <v>-0.4535</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.2746</v>
+        <v>-8.163</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.88</v>
       </c>
       <c r="I167" t="n">
-        <v>1.5318</v>
+        <v>1.5655</v>
       </c>
       <c r="J167" t="n">
-        <v>27.5724</v>
+        <v>28.179</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.51</v>
       </c>
       <c r="I168" t="n">
-        <v>1.0767</v>
+        <v>1.0924</v>
       </c>
       <c r="J168" t="n">
-        <v>19.3806</v>
+        <v>19.6632</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.5</v>
       </c>
       <c r="I169" t="n">
-        <v>1.0637</v>
+        <v>1.0784</v>
       </c>
       <c r="J169" t="n">
-        <v>19.1466</v>
+        <v>19.4112</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.44</v>
       </c>
       <c r="I170" t="n">
-        <v>0.9776</v>
+        <v>0.9817</v>
       </c>
       <c r="J170" t="n">
-        <v>17.5968</v>
+        <v>17.6706</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1.06</v>
       </c>
       <c r="I171" t="n">
-        <v>0.1559</v>
+        <v>0.1252</v>
       </c>
       <c r="J171" t="n">
-        <v>2.8062</v>
+        <v>2.2536</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.28</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5588</v>
+        <v>0.4992</v>
       </c>
       <c r="J172" t="n">
-        <v>16.764</v>
+        <v>14.976</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.12</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2862</v>
+        <v>0.2371</v>
       </c>
       <c r="J173" t="n">
-        <v>8.586</v>
+        <v>7.113</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.04</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1215</v>
+        <v>0.0924</v>
       </c>
       <c r="J174" t="n">
-        <v>3.645</v>
+        <v>2.772</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.96</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.0745</v>
+        <v>-0.0597</v>
       </c>
       <c r="J175" t="n">
-        <v>-2.235</v>
+        <v>-1.791</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3221</v>
+        <v>-0.3057</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.663</v>
+        <v>-9.170999999999999</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.23</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6425</v>
+        <v>0.6057</v>
       </c>
       <c r="J177" t="n">
-        <v>19.275</v>
+        <v>18.171</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.14</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4337</v>
+        <v>0.3916</v>
       </c>
       <c r="J178" t="n">
-        <v>13.011</v>
+        <v>11.748</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.08</v>
       </c>
       <c r="I179" t="n">
-        <v>0.2793</v>
+        <v>0.2413</v>
       </c>
       <c r="J179" t="n">
-        <v>8.379</v>
+        <v>7.239</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.06</v>
       </c>
       <c r="I180" t="n">
-        <v>0.2231</v>
+        <v>0.1887</v>
       </c>
       <c r="J180" t="n">
-        <v>6.693</v>
+        <v>5.661</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.7</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8175</v>
+        <v>-0.7946</v>
       </c>
       <c r="J181" t="n">
-        <v>-24.525</v>
+        <v>-23.838</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.38</v>
       </c>
       <c r="I182" t="n">
-        <v>0.9003</v>
+        <v>0.8849</v>
       </c>
       <c r="J182" t="n">
-        <v>25.2084</v>
+        <v>24.7772</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.28</v>
       </c>
       <c r="I183" t="n">
-        <v>0.7044</v>
+        <v>0.6774</v>
       </c>
       <c r="J183" t="n">
-        <v>19.7232</v>
+        <v>18.9672</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.23</v>
       </c>
       <c r="I184" t="n">
-        <v>0.6035</v>
+        <v>0.5732</v>
       </c>
       <c r="J184" t="n">
-        <v>16.898</v>
+        <v>16.0496</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5394</v>
+        <v>0.5077</v>
       </c>
       <c r="J185" t="n">
-        <v>15.1032</v>
+        <v>14.2156</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.17</v>
       </c>
       <c r="I186" t="n">
-        <v>0.4723</v>
+        <v>0.4398</v>
       </c>
       <c r="J186" t="n">
-        <v>13.2244</v>
+        <v>12.3144</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.04</v>
       </c>
       <c r="I187" t="n">
-        <v>0.1636</v>
+        <v>0.1296</v>
       </c>
       <c r="J187" t="n">
-        <v>4.5808</v>
+        <v>3.6288</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.91</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.121</v>
+        <v>-0.106</v>
       </c>
       <c r="J188" t="n">
-        <v>-3.388</v>
+        <v>-2.968</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.9</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1327</v>
+        <v>-0.1172</v>
       </c>
       <c r="J189" t="n">
-        <v>-3.7156</v>
+        <v>-3.2816</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.65</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.376</v>
+        <v>-0.3626</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.528</v>
+        <v>-10.1528</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.63</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.394</v>
+        <v>-0.382</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.032</v>
+        <v>-10.696</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.24</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6696</v>
+        <v>0.6342</v>
       </c>
       <c r="J192" t="n">
-        <v>19.4184</v>
+        <v>18.3918</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.18</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5333</v>
+        <v>0.4921</v>
       </c>
       <c r="J193" t="n">
-        <v>15.4657</v>
+        <v>14.2709</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.16</v>
       </c>
       <c r="I194" t="n">
-        <v>0.486</v>
+        <v>0.4439</v>
       </c>
       <c r="J194" t="n">
-        <v>14.094</v>
+        <v>12.8731</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.9</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.3472</v>
+        <v>-0.3048</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.0688</v>
+        <v>-8.8392</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.65</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.9197</v>
+        <v>-0.9069</v>
       </c>
       <c r="J196" t="n">
-        <v>-26.6713</v>
+        <v>-26.3001</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.45</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8208</v>
+        <v>0.7699</v>
       </c>
       <c r="J197" t="n">
-        <v>23.8032</v>
+        <v>22.3271</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.1</v>
       </c>
       <c r="I198" t="n">
-        <v>0.25</v>
+        <v>0.204</v>
       </c>
       <c r="J198" t="n">
-        <v>7.25</v>
+        <v>5.916</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.06</v>
       </c>
       <c r="I199" t="n">
-        <v>0.1681</v>
+        <v>0.1316</v>
       </c>
       <c r="J199" t="n">
-        <v>4.8749</v>
+        <v>3.8164</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.8</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2537</v>
+        <v>-0.2339</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.3573</v>
+        <v>-6.7831</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3852</v>
+        <v>-0.3737</v>
       </c>
       <c r="J201" t="n">
-        <v>-11.1708</v>
+        <v>-10.8373</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.31</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7845</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="J202" t="n">
-        <v>20.397</v>
+        <v>19.6976</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.16</v>
       </c>
       <c r="I203" t="n">
-        <v>0.4623</v>
+        <v>0.425</v>
       </c>
       <c r="J203" t="n">
-        <v>12.0198</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.09</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2922</v>
+        <v>0.2586</v>
       </c>
       <c r="J204" t="n">
-        <v>7.5972</v>
+        <v>6.7236</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.09</v>
       </c>
       <c r="I205" t="n">
-        <v>0.2922</v>
+        <v>0.2586</v>
       </c>
       <c r="J205" t="n">
-        <v>7.5972</v>
+        <v>6.7236</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.09</v>
       </c>
       <c r="I206" t="n">
-        <v>0.2922</v>
+        <v>0.2586</v>
       </c>
       <c r="J206" t="n">
-        <v>7.5972</v>
+        <v>6.7236</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.24</v>
       </c>
       <c r="I207" t="n">
-        <v>0.5373</v>
+        <v>0.4827</v>
       </c>
       <c r="J207" t="n">
-        <v>13.9698</v>
+        <v>12.5502</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.11</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3002</v>
+        <v>0.2509</v>
       </c>
       <c r="J208" t="n">
-        <v>7.8052</v>
+        <v>6.5234</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.87</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1703</v>
+        <v>-0.1518</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.4278</v>
+        <v>-3.9468</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.7</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3364</v>
+        <v>-0.3203</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.7464</v>
+        <v>-8.3278</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.49</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.522</v>
+        <v>-0.5252</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.572</v>
+        <v>-13.6552</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.16</v>
       </c>
       <c r="I212" t="n">
-        <v>0.2862</v>
+        <v>0.2731</v>
       </c>
       <c r="J212" t="n">
-        <v>8.0136</v>
+        <v>7.6468</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2138</v>
+        <v>0.1974</v>
       </c>
       <c r="J213" t="n">
-        <v>5.9864</v>
+        <v>5.5272</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.95</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0856</v>
+        <v>-0.0701</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.3968</v>
+        <v>-1.9628</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.95</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0856</v>
+        <v>-0.0701</v>
       </c>
       <c r="J215" t="n">
-        <v>-2.3968</v>
+        <v>-1.9628</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.8</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2519</v>
+        <v>-0.232</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.0532</v>
+        <v>-6.496</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.27</v>
       </c>
       <c r="I217" t="n">
-        <v>0.3875</v>
+        <v>0.3254</v>
       </c>
       <c r="J217" t="n">
-        <v>10.85</v>
+        <v>9.1112</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.26</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3759</v>
+        <v>0.3147</v>
       </c>
       <c r="J218" t="n">
-        <v>10.5252</v>
+        <v>8.8116</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.21</v>
       </c>
       <c r="I219" t="n">
-        <v>0.3168</v>
+        <v>0.2607</v>
       </c>
       <c r="J219" t="n">
-        <v>8.8704</v>
+        <v>7.2996</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0089</v>
+        <v>-0.0066</v>
       </c>
       <c r="J220" t="n">
-        <v>-0.2492</v>
+        <v>-0.1848</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.9</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.1577</v>
+        <v>-0.1378</v>
       </c>
       <c r="J221" t="n">
-        <v>-4.4156</v>
+        <v>-3.8584</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.95</v>
       </c>
       <c r="I222" t="n">
-        <v>1.6192</v>
+        <v>1.6599</v>
       </c>
       <c r="J222" t="n">
-        <v>34.0032</v>
+        <v>34.8579</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.72</v>
       </c>
       <c r="I223" t="n">
-        <v>1.3428</v>
+        <v>1.3652</v>
       </c>
       <c r="J223" t="n">
-        <v>28.1988</v>
+        <v>28.6692</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.4</v>
       </c>
       <c r="I224" t="n">
-        <v>0.9114</v>
+        <v>0.9067</v>
       </c>
       <c r="J224" t="n">
-        <v>19.1394</v>
+        <v>19.0407</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.12</v>
       </c>
       <c r="I225" t="n">
-        <v>0.3216</v>
+        <v>0.2886</v>
       </c>
       <c r="J225" t="n">
-        <v>6.7536</v>
+        <v>6.0606</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.08</v>
       </c>
       <c r="I226" t="n">
-        <v>0.2165</v>
+        <v>0.1844</v>
       </c>
       <c r="J226" t="n">
-        <v>4.5465</v>
+        <v>3.8724</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.91</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1018</v>
+        <v>-0.0862</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.1378</v>
+        <v>-1.8102</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.84</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1827</v>
+        <v>-0.1672</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.8367</v>
+        <v>-3.5112</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.72</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3012</v>
+        <v>-0.2867</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.3252</v>
+        <v>-6.0207</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.6</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4076</v>
+        <v>-0.397</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.5596</v>
+        <v>-8.337</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.5</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4958</v>
+        <v>-0.4936</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.4118</v>
+        <v>-10.3656</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.44</v>
       </c>
       <c r="I232" t="n">
-        <v>0.796</v>
+        <v>0.7423</v>
       </c>
       <c r="J232" t="n">
-        <v>21.492</v>
+        <v>20.0421</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.27</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5381</v>
+        <v>0.4784</v>
       </c>
       <c r="J233" t="n">
-        <v>14.5287</v>
+        <v>12.9168</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.92</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1275</v>
+        <v>-0.1085</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.4425</v>
+        <v>-2.9295</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.89</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1622</v>
+        <v>-0.1419</v>
       </c>
       <c r="J235" t="n">
-        <v>-4.3794</v>
+        <v>-3.8313</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.71</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3424</v>
+        <v>-0.3276</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.2448</v>
+        <v>-8.8452</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.56</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1928</v>
+        <v>1.2079</v>
       </c>
       <c r="J237" t="n">
-        <v>32.2056</v>
+        <v>32.6133</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.41</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9735</v>
+        <v>0.9657</v>
       </c>
       <c r="J238" t="n">
-        <v>26.2845</v>
+        <v>26.0739</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.26</v>
       </c>
       <c r="I239" t="n">
-        <v>0.6761</v>
+        <v>0.644</v>
       </c>
       <c r="J239" t="n">
-        <v>18.2547</v>
+        <v>17.388</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.82</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5369</v>
       </c>
       <c r="J240" t="n">
-        <v>-15.5007</v>
+        <v>-14.4963</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5975</v>
+        <v>-0.5614</v>
       </c>
       <c r="J241" t="n">
-        <v>-16.1325</v>
+        <v>-15.1578</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.16</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3547</v>
+        <v>0.3012</v>
       </c>
       <c r="J242" t="n">
-        <v>9.9316</v>
+        <v>8.4336</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.14</v>
       </c>
       <c r="I243" t="n">
-        <v>0.3192</v>
+        <v>0.268</v>
       </c>
       <c r="J243" t="n">
-        <v>8.9376</v>
+        <v>7.504</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.01</v>
       </c>
       <c r="I244" t="n">
-        <v>0.039</v>
+        <v>0.0272</v>
       </c>
       <c r="J244" t="n">
-        <v>1.092</v>
+        <v>0.7616000000000001</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.01</v>
       </c>
       <c r="I245" t="n">
-        <v>0.039</v>
+        <v>0.0272</v>
       </c>
       <c r="J245" t="n">
-        <v>1.092</v>
+        <v>0.7616000000000001</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.92</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.1276</v>
+        <v>-0.1086</v>
       </c>
       <c r="J246" t="n">
-        <v>-3.5728</v>
+        <v>-3.0408</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.52</v>
       </c>
       <c r="I247" t="n">
-        <v>1.1637</v>
+        <v>1.18</v>
       </c>
       <c r="J247" t="n">
-        <v>32.5836</v>
+        <v>33.04</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.03</v>
       </c>
       <c r="I248" t="n">
-        <v>0.1251</v>
+        <v>0.1018</v>
       </c>
       <c r="J248" t="n">
-        <v>3.5028</v>
+        <v>2.8504</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.0118</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="J249" t="n">
-        <v>-0.3304</v>
+        <v>-0.2212</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.99</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0518</v>
       </c>
       <c r="J250" t="n">
-        <v>-1.9992</v>
+        <v>-1.4504</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.85</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4847</v>
+        <v>-0.4426</v>
       </c>
       <c r="J251" t="n">
-        <v>-13.5716</v>
+        <v>-12.3928</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.079</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="J252" t="n">
-        <v>-1.975</v>
+        <v>-1.655</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.91</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1168</v>
+        <v>-0.1022</v>
       </c>
       <c r="J253" t="n">
-        <v>-2.92</v>
+        <v>-2.555</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.79</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2433</v>
+        <v>-0.2259</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.0825</v>
+        <v>-5.6475</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.75</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2808</v>
+        <v>-0.2634</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.02</v>
+        <v>-6.585</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.59</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4263</v>
+        <v>-0.4171</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.6575</v>
+        <v>-10.4275</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.63</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7438</v>
+        <v>0.6718</v>
       </c>
       <c r="J257" t="n">
-        <v>18.595</v>
+        <v>16.795</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.35</v>
       </c>
       <c r="I258" t="n">
-        <v>0.461</v>
+        <v>0.3963</v>
       </c>
       <c r="J258" t="n">
-        <v>11.525</v>
+        <v>9.907500000000001</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.19</v>
       </c>
       <c r="I259" t="n">
-        <v>0.2829</v>
+        <v>0.2336</v>
       </c>
       <c r="J259" t="n">
-        <v>7.0725</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.11</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1787</v>
+        <v>0.1417</v>
       </c>
       <c r="J260" t="n">
-        <v>4.4675</v>
+        <v>3.5425</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>1.04</v>
       </c>
       <c r="I261" t="n">
-        <v>0.0696</v>
+        <v>0.0499</v>
       </c>
       <c r="J261" t="n">
-        <v>1.74</v>
+        <v>1.2475</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.25</v>
       </c>
       <c r="I262" t="n">
-        <v>0.6813</v>
+        <v>0.6466</v>
       </c>
       <c r="J262" t="n">
-        <v>20.439</v>
+        <v>19.398</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.17</v>
       </c>
       <c r="I263" t="n">
-        <v>0.5012</v>
+        <v>0.4601</v>
       </c>
       <c r="J263" t="n">
-        <v>15.036</v>
+        <v>13.803</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.08</v>
       </c>
       <c r="I264" t="n">
-        <v>0.2765</v>
+        <v>0.2396</v>
       </c>
       <c r="J264" t="n">
-        <v>8.295</v>
+        <v>7.188</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.96</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1796</v>
+        <v>-0.1458</v>
       </c>
       <c r="J265" t="n">
-        <v>-5.388</v>
+        <v>-4.374</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.84</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.4636</v>
       </c>
       <c r="J266" t="n">
-        <v>-15.165</v>
+        <v>-13.908</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.48</v>
       </c>
       <c r="I267" t="n">
-        <v>0.8864</v>
+        <v>0.8442</v>
       </c>
       <c r="J267" t="n">
-        <v>26.592</v>
+        <v>25.326</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.16</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3744</v>
+        <v>0.3194</v>
       </c>
       <c r="J268" t="n">
-        <v>11.232</v>
+        <v>9.582000000000001</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.75</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2969</v>
+        <v>-0.2786</v>
       </c>
       <c r="J269" t="n">
-        <v>-8.907</v>
+        <v>-8.358000000000001</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.73</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3158</v>
+        <v>-0.2985</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.474</v>
+        <v>-8.955</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.66</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3801</v>
+        <v>-0.3676</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.403</v>
+        <v>-11.028</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.57</v>
       </c>
       <c r="I272" t="n">
-        <v>1.2212</v>
+        <v>1.2392</v>
       </c>
       <c r="J272" t="n">
-        <v>36.636</v>
+        <v>37.176</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.23</v>
       </c>
       <c r="I273" t="n">
-        <v>0.6232</v>
+        <v>0.587</v>
       </c>
       <c r="J273" t="n">
-        <v>18.696</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.1</v>
       </c>
       <c r="I274" t="n">
-        <v>0.3225</v>
+        <v>0.2864</v>
       </c>
       <c r="J274" t="n">
-        <v>9.675000000000001</v>
+        <v>8.592000000000001</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.87</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4428</v>
+        <v>-0.4005</v>
       </c>
       <c r="J275" t="n">
-        <v>-13.284</v>
+        <v>-12.015</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.82</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5643</v>
+        <v>-0.5255</v>
       </c>
       <c r="J276" t="n">
-        <v>-16.929</v>
+        <v>-15.765</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.22</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4832</v>
+        <v>0.4256</v>
       </c>
       <c r="J277" t="n">
-        <v>14.496</v>
+        <v>12.768</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.11</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2841</v>
+        <v>0.2347</v>
       </c>
       <c r="J278" t="n">
-        <v>8.523</v>
+        <v>7.041</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.86</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1857</v>
+        <v>-0.1656</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.571</v>
+        <v>-4.968</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.8</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.247</v>
+        <v>-0.2271</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.41</v>
+        <v>-6.813</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.72</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3238</v>
+        <v>-0.307</v>
       </c>
       <c r="J281" t="n">
-        <v>-9.714</v>
+        <v>-9.210000000000001</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.14</v>
       </c>
       <c r="I282" t="n">
-        <v>0.3622</v>
+        <v>0.3103</v>
       </c>
       <c r="J282" t="n">
-        <v>9.779400000000001</v>
+        <v>8.3781</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.08</v>
       </c>
       <c r="I283" t="n">
-        <v>0.242</v>
+        <v>0.1975</v>
       </c>
       <c r="J283" t="n">
-        <v>6.534</v>
+        <v>5.3325</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.86</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1798</v>
+        <v>-0.1614</v>
       </c>
       <c r="J284" t="n">
-        <v>-4.8546</v>
+        <v>-4.3578</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.68</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3535</v>
+        <v>-0.3385</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.544499999999999</v>
+        <v>-9.1395</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.59</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4342</v>
+        <v>-0.4263</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.7234</v>
+        <v>-11.5101</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.65</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2953</v>
+        <v>1.3148</v>
       </c>
       <c r="J287" t="n">
-        <v>34.9731</v>
+        <v>35.4996</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.48</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0681</v>
+        <v>1.0764</v>
       </c>
       <c r="J288" t="n">
-        <v>28.8387</v>
+        <v>29.0628</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.27</v>
       </c>
       <c r="I289" t="n">
-        <v>0.6855</v>
+        <v>0.6573</v>
       </c>
       <c r="J289" t="n">
-        <v>18.5085</v>
+        <v>17.7471</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.01</v>
       </c>
       <c r="I290" t="n">
-        <v>0.019</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J290" t="n">
-        <v>0.513</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.8</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6322</v>
+        <v>-0.6</v>
       </c>
       <c r="J291" t="n">
-        <v>-17.0694</v>
+        <v>-16.2</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.82</v>
       </c>
       <c r="I292" t="n">
-        <v>0.8984</v>
+        <v>0.8289</v>
       </c>
       <c r="J292" t="n">
-        <v>20.6632</v>
+        <v>19.0647</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.6</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6957</v>
+        <v>0.6247</v>
       </c>
       <c r="J293" t="n">
-        <v>16.0011</v>
+        <v>14.3681</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.39</v>
       </c>
       <c r="I294" t="n">
-        <v>0.4926</v>
+        <v>0.4295</v>
       </c>
       <c r="J294" t="n">
-        <v>11.3298</v>
+        <v>9.878500000000001</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.19</v>
       </c>
       <c r="I295" t="n">
-        <v>0.2709</v>
+        <v>0.2241</v>
       </c>
       <c r="J295" t="n">
-        <v>6.2307</v>
+        <v>5.1543</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>1.05</v>
       </c>
       <c r="I296" t="n">
-        <v>0.07439999999999999</v>
+        <v>0.052</v>
       </c>
       <c r="J296" t="n">
-        <v>1.7112</v>
+        <v>1.196</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.16</v>
       </c>
       <c r="I297" t="n">
-        <v>0.3932</v>
+        <v>0.4202</v>
       </c>
       <c r="J297" t="n">
-        <v>9.0436</v>
+        <v>9.6646</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>0.87</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.1387</v>
+        <v>-0.1216</v>
       </c>
       <c r="J298" t="n">
-        <v>-3.1901</v>
+        <v>-2.7968</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.4367</v>
+        <v>-0.4288</v>
       </c>
       <c r="J299" t="n">
-        <v>-10.0441</v>
+        <v>-9.862399999999999</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.41</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.5683</v>
+        <v>-0.5755</v>
       </c>
       <c r="J300" t="n">
-        <v>-13.0709</v>
+        <v>-13.2365</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.33</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.6378</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="J301" t="n">
-        <v>-14.6694</v>
+        <v>-15.1064</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.35</v>
       </c>
       <c r="I302" t="n">
-        <v>0.722</v>
+        <v>0.6753</v>
       </c>
       <c r="J302" t="n">
-        <v>18.772</v>
+        <v>17.5578</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.92</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1145</v>
+        <v>-0.0992</v>
       </c>
       <c r="J303" t="n">
-        <v>-2.977</v>
+        <v>-2.5792</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.77</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.2696</v>
+        <v>-0.2507</v>
       </c>
       <c r="J304" t="n">
-        <v>-7.0096</v>
+        <v>-6.5182</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.68</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3539</v>
+        <v>-0.3389</v>
       </c>
       <c r="J305" t="n">
-        <v>-9.2014</v>
+        <v>-8.811400000000001</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.65</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.3812</v>
+        <v>-0.3682</v>
       </c>
       <c r="J306" t="n">
-        <v>-9.911199999999999</v>
+        <v>-9.5732</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.92</v>
       </c>
       <c r="I307" t="n">
-        <v>1.6452</v>
+        <v>1.6956</v>
       </c>
       <c r="J307" t="n">
-        <v>42.7752</v>
+        <v>44.0856</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.36</v>
       </c>
       <c r="I308" t="n">
-        <v>0.8685</v>
+        <v>0.8495</v>
       </c>
       <c r="J308" t="n">
-        <v>22.581</v>
+        <v>22.087</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.97</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1747</v>
+        <v>-0.1435</v>
       </c>
       <c r="J309" t="n">
-        <v>-4.5422</v>
+        <v>-3.731</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.97</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1747</v>
+        <v>-0.1435</v>
       </c>
       <c r="J310" t="n">
-        <v>-4.5422</v>
+        <v>-3.731</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.87</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.4608</v>
+        <v>-0.4208</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.9808</v>
+        <v>-10.9408</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.09</v>
       </c>
       <c r="I312" t="n">
-        <v>0.252</v>
+        <v>0.2055</v>
       </c>
       <c r="J312" t="n">
-        <v>6.552</v>
+        <v>5.343</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.03</v>
       </c>
       <c r="I313" t="n">
-        <v>0.1156</v>
+        <v>0.0859</v>
       </c>
       <c r="J313" t="n">
-        <v>3.0056</v>
+        <v>2.2334</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.92</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.1174</v>
+        <v>-0.101</v>
       </c>
       <c r="J314" t="n">
-        <v>-3.0524</v>
+        <v>-2.626</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.88</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.1616</v>
+        <v>-0.1428</v>
       </c>
       <c r="J315" t="n">
-        <v>-4.2016</v>
+        <v>-3.7128</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.63</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4027</v>
+        <v>-0.3919</v>
       </c>
       <c r="J316" t="n">
-        <v>-10.4702</v>
+        <v>-10.1894</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.65</v>
       </c>
       <c r="I317" t="n">
-        <v>1.3058</v>
+        <v>1.3266</v>
       </c>
       <c r="J317" t="n">
-        <v>33.9508</v>
+        <v>34.4916</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.5</v>
       </c>
       <c r="I318" t="n">
-        <v>1.1042</v>
+        <v>1.1156</v>
       </c>
       <c r="J318" t="n">
-        <v>28.7092</v>
+        <v>29.0056</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.19</v>
       </c>
       <c r="I319" t="n">
-        <v>0.5239</v>
+        <v>0.4895</v>
       </c>
       <c r="J319" t="n">
-        <v>13.6214</v>
+        <v>12.727</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.83</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.5554</v>
+        <v>-0.5179</v>
       </c>
       <c r="J320" t="n">
-        <v>-14.4404</v>
+        <v>-13.4654</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.83</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5554</v>
+        <v>-0.5179</v>
       </c>
       <c r="J321" t="n">
-        <v>-14.4404</v>
+        <v>-13.4654</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>0.85</v>
       </c>
       <c r="I322" t="n">
-        <v>-0.1662</v>
+        <v>-0.1501</v>
       </c>
       <c r="J322" t="n">
-        <v>-4.155</v>
+        <v>-3.7525</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>0.79</v>
       </c>
       <c r="I323" t="n">
-        <v>-0.2302</v>
+        <v>-0.2156</v>
       </c>
       <c r="J323" t="n">
-        <v>-5.755</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>0.78</v>
       </c>
       <c r="I324" t="n">
-        <v>-0.2404</v>
+        <v>-0.2259</v>
       </c>
       <c r="J324" t="n">
-        <v>-6.01</v>
+        <v>-5.6475</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>0.63</v>
       </c>
       <c r="I325" t="n">
-        <v>-0.3775</v>
+        <v>-0.3657</v>
       </c>
       <c r="J325" t="n">
-        <v>-9.4375</v>
+        <v>-9.1425</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.38</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.5968</v>
+        <v>-0.6088</v>
       </c>
       <c r="J326" t="n">
-        <v>-14.92</v>
+        <v>-15.22</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.68</v>
       </c>
       <c r="I327" t="n">
-        <v>1.2971</v>
+        <v>1.3171</v>
       </c>
       <c r="J327" t="n">
-        <v>32.4275</v>
+        <v>32.9275</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1.53</v>
       </c>
       <c r="I328" t="n">
-        <v>1.1071</v>
+        <v>1.1225</v>
       </c>
       <c r="J328" t="n">
-        <v>27.6775</v>
+        <v>28.0625</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>1.49</v>
       </c>
       <c r="I329" t="n">
-        <v>1.0545</v>
+        <v>1.0663</v>
       </c>
       <c r="J329" t="n">
-        <v>26.3625</v>
+        <v>26.6575</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>1.27</v>
       </c>
       <c r="I330" t="n">
-        <v>0.6624</v>
+        <v>0.6407</v>
       </c>
       <c r="J330" t="n">
-        <v>16.56</v>
+        <v>16.0175</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>1.18</v>
       </c>
       <c r="I331" t="n">
-        <v>0.4682</v>
+        <v>0.4381</v>
       </c>
       <c r="J331" t="n">
-        <v>11.705</v>
+        <v>10.9525</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.41</v>
       </c>
       <c r="I332" t="n">
-        <v>0.976</v>
+        <v>0.9685</v>
       </c>
       <c r="J332" t="n">
-        <v>40.992</v>
+        <v>40.677</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.37</v>
       </c>
       <c r="I333" t="n">
-        <v>0.9013</v>
+        <v>0.8837</v>
       </c>
       <c r="J333" t="n">
-        <v>37.8546</v>
+        <v>37.1154</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>1.21</v>
       </c>
       <c r="I334" t="n">
-        <v>0.5714</v>
+        <v>0.5356</v>
       </c>
       <c r="J334" t="n">
-        <v>23.9988</v>
+        <v>22.4952</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>1.2</v>
       </c>
       <c r="I335" t="n">
-        <v>0.5496</v>
+        <v>0.5135</v>
       </c>
       <c r="J335" t="n">
-        <v>23.0832</v>
+        <v>21.567</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.62</v>
       </c>
       <c r="I336" t="n">
-        <v>-1.0043</v>
+        <v>-1.0057</v>
       </c>
       <c r="J336" t="n">
-        <v>-42.1806</v>
+        <v>-42.2394</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.11</v>
       </c>
       <c r="I337" t="n">
-        <v>0.2861</v>
+        <v>0.2366</v>
       </c>
       <c r="J337" t="n">
-        <v>12.0162</v>
+        <v>9.937200000000001</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.09</v>
       </c>
       <c r="I338" t="n">
-        <v>0.2461</v>
+        <v>0.1999</v>
       </c>
       <c r="J338" t="n">
-        <v>10.3362</v>
+        <v>8.395799999999999</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>0.85</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.1955</v>
+        <v>-0.1754</v>
       </c>
       <c r="J339" t="n">
-        <v>-8.211</v>
+        <v>-7.3668</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>0.82</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.2263</v>
+        <v>-0.2061</v>
       </c>
       <c r="J340" t="n">
-        <v>-9.5046</v>
+        <v>-8.6562</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.8</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2462</v>
+        <v>-0.2263</v>
       </c>
       <c r="J341" t="n">
-        <v>-10.3404</v>
+        <v>-9.5046</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.42</v>
       </c>
       <c r="I342" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9618</v>
       </c>
       <c r="J342" t="n">
-        <v>26.1414</v>
+        <v>25.9686</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1.4</v>
       </c>
       <c r="I343" t="n">
-        <v>0.9327</v>
+        <v>0.9216</v>
       </c>
       <c r="J343" t="n">
-        <v>25.1829</v>
+        <v>24.8832</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>1.37</v>
       </c>
       <c r="I344" t="n">
-        <v>0.8764</v>
+        <v>0.8603</v>
       </c>
       <c r="J344" t="n">
-        <v>23.6628</v>
+        <v>23.2281</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>1.35</v>
       </c>
       <c r="I345" t="n">
-        <v>0.838</v>
+        <v>0.8193</v>
       </c>
       <c r="J345" t="n">
-        <v>22.626</v>
+        <v>22.1211</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.85</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.5201</v>
+        <v>-0.4834</v>
       </c>
       <c r="J346" t="n">
-        <v>-14.0427</v>
+        <v>-13.0518</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>0.99</v>
       </c>
       <c r="I347" t="n">
-        <v>-0.003</v>
+        <v>0.0026</v>
       </c>
       <c r="J347" t="n">
-        <v>-0.081</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>0.8</v>
       </c>
       <c r="I348" t="n">
-        <v>-0.2345</v>
+        <v>-0.2169</v>
       </c>
       <c r="J348" t="n">
-        <v>-6.3315</v>
+        <v>-5.8563</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>0.77</v>
       </c>
       <c r="I349" t="n">
-        <v>-0.2627</v>
+        <v>-0.2451</v>
       </c>
       <c r="J349" t="n">
-        <v>-7.0929</v>
+        <v>-6.6177</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>0.77</v>
       </c>
       <c r="I350" t="n">
-        <v>-0.2627</v>
+        <v>-0.2451</v>
       </c>
       <c r="J350" t="n">
-        <v>-7.0929</v>
+        <v>-6.6177</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I351" t="n">
-        <v>-0.3372</v>
+        <v>-0.3215</v>
       </c>
       <c r="J351" t="n">
-        <v>-9.1044</v>
+        <v>-8.6805</v>
       </c>
     </row>
   </sheetData>
